--- a/VHTs_and_Community_Demos_Extract.xlsx
+++ b/VHTs_and_Community_Demos_Extract.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="404">
   <si>
     <t>Entry Index</t>
   </si>
@@ -142,6 +142,9 @@
     <t>KALAPATA P/S</t>
   </si>
   <si>
+    <t>KATHILE P/S</t>
+  </si>
+  <si>
     <t>LOMODOCH P/S</t>
   </si>
   <si>
@@ -211,6 +214,9 @@
     <t>LOKADWARAN P/S</t>
   </si>
   <si>
+    <t>LORENG P/S</t>
+  </si>
+  <si>
     <t>NAPIANANYA P/S</t>
   </si>
   <si>
@@ -289,6 +295,9 @@
     <t>Angarep Village</t>
   </si>
   <si>
+    <t>Angarap</t>
+  </si>
+  <si>
     <t>Apeikar village Namodo</t>
   </si>
   <si>
@@ -307,9 +316,33 @@
     <t>Kitelore</t>
   </si>
   <si>
+    <t>Kanakora</t>
+  </si>
+  <si>
+    <t>Kotirae</t>
+  </si>
+  <si>
+    <t>Namus</t>
+  </si>
+  <si>
+    <t>Kayokong</t>
+  </si>
+  <si>
+    <t>Kakamar center</t>
+  </si>
+  <si>
     <t>Kalapata centre</t>
   </si>
   <si>
+    <t>Nakosowan cell</t>
+  </si>
+  <si>
+    <t>Jerusalem</t>
+  </si>
+  <si>
+    <t>Kathile west cell</t>
+  </si>
+  <si>
     <t>KAILOB</t>
   </si>
   <si>
@@ -439,12 +472,51 @@
     <t>Nyakwae</t>
   </si>
   <si>
+    <t>Kopsang</t>
+  </si>
+  <si>
+    <t>Lookorok</t>
+  </si>
+  <si>
+    <t>Oyapoo</t>
+  </si>
+  <si>
+    <t>Loveless central</t>
+  </si>
+  <si>
+    <t>Nayeeche</t>
+  </si>
+  <si>
+    <t>Nyakwae north</t>
+  </si>
+  <si>
     <t>Napumpum north</t>
   </si>
   <si>
     <t>Nupumpum p/s, kotyang village</t>
   </si>
   <si>
+    <t>Kocil village</t>
+  </si>
+  <si>
+    <t>Kapech village</t>
+  </si>
+  <si>
+    <t>Napumpum trading centre</t>
+  </si>
+  <si>
+    <t>Napumpum Central</t>
+  </si>
+  <si>
+    <t>Trading centre</t>
+  </si>
+  <si>
+    <t>Lokopo village</t>
+  </si>
+  <si>
+    <t>Kopoko</t>
+  </si>
+  <si>
     <t>Nakapelimen</t>
   </si>
   <si>
@@ -565,6 +637,9 @@
     <t>Napongae primary school catchment area</t>
   </si>
   <si>
+    <t>Lokaala/Napongae primary school catchment area</t>
+  </si>
+  <si>
     <t>Natirae primary school catchment area</t>
   </si>
   <si>
@@ -586,6 +661,9 @@
     <t>Loowoi village</t>
   </si>
   <si>
+    <t>Loreng village community trees</t>
+  </si>
+  <si>
     <t>Nakuri village. In the saving group</t>
   </si>
   <si>
@@ -667,6 +745,12 @@
     <t>Alekilek</t>
   </si>
   <si>
+    <t>Kasile B</t>
+  </si>
+  <si>
+    <t>Morusapir B</t>
+  </si>
+  <si>
     <t>Lotede village</t>
   </si>
   <si>
@@ -685,6 +769,15 @@
     <t>Lokarujak</t>
   </si>
   <si>
+    <t>Namoni</t>
+  </si>
+  <si>
+    <t>Kamera</t>
+  </si>
+  <si>
+    <t>Logolei</t>
+  </si>
+  <si>
     <t>Lepeei</t>
   </si>
   <si>
@@ -805,9 +898,33 @@
     <t>ILUKORI PETER</t>
   </si>
   <si>
+    <t>Lowany marko</t>
+  </si>
+  <si>
+    <t>Aryong Alice..0787741876</t>
+  </si>
+  <si>
+    <t>Ilukori peter 0789683823</t>
+  </si>
+  <si>
+    <t>Lowany mariko</t>
+  </si>
+  <si>
+    <t>Ilukori peter</t>
+  </si>
+  <si>
     <t>Lotyang Samuel lobokomoe</t>
   </si>
   <si>
+    <t>Looking Joseph</t>
+  </si>
+  <si>
+    <t>Loiki  Joseph</t>
+  </si>
+  <si>
+    <t>Loiki Joseph</t>
+  </si>
+  <si>
     <t>Lopiran Joseph</t>
   </si>
   <si>
@@ -871,9 +988,24 @@
     <t>Adong lilly grace</t>
   </si>
   <si>
+    <t>Lokiyo John bosco</t>
+  </si>
+  <si>
+    <t>Lopera zakariya</t>
+  </si>
+  <si>
+    <t>Lokiya John bosco</t>
+  </si>
+  <si>
     <t>Longoli John bosco</t>
   </si>
   <si>
+    <t>Akwang patrick</t>
+  </si>
+  <si>
+    <t>Lotimong calvin</t>
+  </si>
+  <si>
     <t>Claudia</t>
   </si>
   <si>
@@ -997,6 +1129,9 @@
     <t>Iriama simon peter and Angella joseph</t>
   </si>
   <si>
+    <t>Iriama Allan stephen and Keke Lucy</t>
+  </si>
+  <si>
     <t>Aleper pius and Nakiru luja</t>
   </si>
   <si>
@@ -1027,12 +1162,18 @@
     <t>Simon</t>
   </si>
   <si>
+    <t>Margret</t>
+  </si>
+  <si>
     <t>Kokoi Catherine and Lodungokori John Bosco</t>
   </si>
   <si>
     <t>Catherine</t>
   </si>
   <si>
+    <t>John Bosco</t>
+  </si>
+  <si>
     <t>Longok Jacinta and lobere william</t>
   </si>
   <si>
@@ -1061,6 +1202,9 @@
   </si>
   <si>
     <t>Amoo Sofia</t>
+  </si>
+  <si>
+    <t>Ngole Paula</t>
   </si>
   <si>
     <t>Lopeyok Martin</t>
@@ -1439,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J191"/>
+  <dimension ref="A1:J225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1491,16 +1635,16 @@
         <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H2" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
       <c r="I2" t="s">
-        <v>344</v>
+        <v>391</v>
       </c>
       <c r="J2">
         <v>152</v>
@@ -1523,16 +1667,16 @@
         <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G3" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H3" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="I3" t="s">
-        <v>344</v>
+        <v>391</v>
       </c>
       <c r="J3">
         <v>176</v>
@@ -1555,16 +1699,16 @@
         <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H4" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="I4" t="s">
-        <v>344</v>
+        <v>391</v>
       </c>
       <c r="J4">
         <v>168</v>
@@ -1587,16 +1731,16 @@
         <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H5" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="I5" t="s">
-        <v>344</v>
+        <v>391</v>
       </c>
       <c r="J5">
         <v>238</v>
@@ -1619,16 +1763,16 @@
         <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H6" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="I6" t="s">
-        <v>344</v>
+        <v>391</v>
       </c>
       <c r="J6">
         <v>222</v>
@@ -1651,16 +1795,16 @@
         <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H7" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="I7" t="s">
-        <v>344</v>
+        <v>391</v>
       </c>
       <c r="J7">
         <v>142</v>
@@ -1683,16 +1827,16 @@
         <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="H8" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="I8" t="s">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="J8">
         <v>83</v>
@@ -1715,16 +1859,16 @@
         <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="H9" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="I9" t="s">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="J9">
         <v>91</v>
@@ -1747,16 +1891,16 @@
         <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="H10" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="I10" t="s">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="J10">
         <v>123</v>
@@ -1779,16 +1923,16 @@
         <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G11" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H11" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="I11" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="J11">
         <v>88</v>
@@ -1811,16 +1955,16 @@
         <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G12" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="H12" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="I12" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J12">
         <v>235</v>
@@ -1843,16 +1987,16 @@
         <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H13" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="I13" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J13">
         <v>136</v>
@@ -1875,16 +2019,16 @@
         <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G14" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H14" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
       <c r="I14" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J14">
         <v>154</v>
@@ -1907,16 +2051,16 @@
         <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G15" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H15" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="I15" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J15">
         <v>161</v>
@@ -1939,16 +2083,16 @@
         <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G16" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H16" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="I16" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J16">
         <v>185</v>
@@ -1971,16 +2115,16 @@
         <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G17" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H17" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="I17" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J17">
         <v>146</v>
@@ -2003,16 +2147,16 @@
         <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G18" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H18" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="I18" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J18">
         <v>174</v>
@@ -2035,16 +2179,16 @@
         <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H19" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="I19" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J19">
         <v>133</v>
@@ -2067,16 +2211,16 @@
         <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H20" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="I20" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J20">
         <v>126</v>
@@ -2099,16 +2243,16 @@
         <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G21" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H21" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="I21" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J21">
         <v>131</v>
@@ -2131,16 +2275,16 @@
         <v>37</v>
       </c>
       <c r="F22" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H22" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
       <c r="I22" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J22">
         <v>151</v>
@@ -2163,16 +2307,16 @@
         <v>37</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G23" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H23" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="I23" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J23">
         <v>144</v>
@@ -2195,16 +2339,16 @@
         <v>37</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H24" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="I24" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J24">
         <v>158</v>
@@ -2227,16 +2371,16 @@
         <v>37</v>
       </c>
       <c r="F25" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G25" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H25" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="I25" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J25">
         <v>128</v>
@@ -2259,16 +2403,16 @@
         <v>37</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G26" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H26" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="I26" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J26">
         <v>176</v>
@@ -2291,16 +2435,16 @@
         <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G27" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H27" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="I27" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J27">
         <v>141</v>
@@ -2308,10 +2452,10 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28">
-        <v>143</v>
+        <v>493</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
         <v>21</v>
@@ -2320,30 +2464,30 @@
         <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H28" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="I28" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J28">
-        <v>146</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29">
-        <v>144</v>
+        <v>494</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C29" t="s">
         <v>21</v>
@@ -2352,30 +2496,30 @@
         <v>29</v>
       </c>
       <c r="E29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H29" t="s">
-        <v>247</v>
+        <v>290</v>
       </c>
       <c r="I29" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J29">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30">
-        <v>153</v>
+        <v>497</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
         <v>21</v>
@@ -2384,27 +2528,27 @@
         <v>29</v>
       </c>
       <c r="E30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
         <v>93</v>
       </c>
       <c r="G30" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H30" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="I30" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J30">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s">
         <v>12</v>
@@ -2419,24 +2563,24 @@
         <v>39</v>
       </c>
       <c r="F31" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H31" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="I31" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J31">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -2451,24 +2595,24 @@
         <v>39</v>
       </c>
       <c r="F32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G32" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="H32" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="I32" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J32">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -2483,24 +2627,24 @@
         <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G33" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H33" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="I33" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J33">
-        <v>161</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
@@ -2515,24 +2659,24 @@
         <v>39</v>
       </c>
       <c r="F34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G34" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="H34" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="I34" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J34">
-        <v>176</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -2547,24 +2691,24 @@
         <v>39</v>
       </c>
       <c r="F35" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G35" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="H35" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="I35" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J35">
-        <v>132</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -2579,120 +2723,120 @@
         <v>39</v>
       </c>
       <c r="F36" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G36" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="H36" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="I36" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="J36">
-        <v>223</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37">
-        <v>436</v>
+        <v>157</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
         <v>29</v>
       </c>
       <c r="E37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F37" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G37" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H37" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="I37" t="s">
-        <v>348</v>
+        <v>394</v>
       </c>
       <c r="J37">
-        <v>60</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38">
-        <v>470</v>
+        <v>169</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
         <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G38" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H38" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="I38" t="s">
-        <v>348</v>
+        <v>394</v>
       </c>
       <c r="J38">
-        <v>82</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39">
-        <v>310</v>
+        <v>170</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
         <v>29</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G39" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H39" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="I39" t="s">
-        <v>348</v>
+        <v>394</v>
       </c>
       <c r="J39">
-        <v>89</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -2704,30 +2848,30 @@
         <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G40" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H40" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="I40" t="s">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="J40">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
         <v>22</v>
@@ -2736,30 +2880,30 @@
         <v>29</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F41" t="s">
         <v>99</v>
       </c>
       <c r="G41" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H41" t="s">
-        <v>265</v>
+        <v>293</v>
       </c>
       <c r="I41" t="s">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="J41">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42">
-        <v>319</v>
+        <v>482</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
         <v>22</v>
@@ -2768,30 +2912,30 @@
         <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F42" t="s">
         <v>100</v>
       </c>
       <c r="G42" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H42" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="I42" t="s">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="J42">
-        <v>113</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43">
-        <v>321</v>
+        <v>485</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
         <v>22</v>
@@ -2800,30 +2944,30 @@
         <v>29</v>
       </c>
       <c r="E43" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F43" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G43" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H43" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="I43" t="s">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="J43">
-        <v>107</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44">
-        <v>324</v>
+        <v>487</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
         <v>22</v>
@@ -2832,475 +2976,475 @@
         <v>29</v>
       </c>
       <c r="E44" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F44" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G44" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H44" t="s">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="I44" t="s">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="J44">
-        <v>117</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
         <v>29</v>
       </c>
       <c r="E45" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F45" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G45" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H45" t="s">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="I45" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J45">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46">
-        <v>83</v>
+        <v>501</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
       </c>
       <c r="E46" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F46" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G46" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H46" t="s">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="I46" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J46">
-        <v>127</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47">
-        <v>84</v>
+        <v>504</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D47" t="s">
         <v>29</v>
       </c>
       <c r="E47" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F47" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G47" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H47" t="s">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="I47" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J47">
-        <v>107</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48">
-        <v>334</v>
+        <v>507</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D48" t="s">
         <v>29</v>
       </c>
       <c r="E48" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F48" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="G48" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H48" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="I48" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J48">
-        <v>118</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49">
-        <v>336</v>
+        <v>513</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D49" t="s">
         <v>29</v>
       </c>
       <c r="E49" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F49" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G49" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H49" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="I49" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J49">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D50" t="s">
         <v>29</v>
       </c>
       <c r="E50" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G50" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H50" t="s">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="I50" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J50">
-        <v>117</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51">
-        <v>339</v>
+        <v>496</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D51" t="s">
         <v>29</v>
       </c>
       <c r="E51" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F51" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G51" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H51" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
       <c r="I51" t="s">
-        <v>349</v>
+        <v>396</v>
       </c>
       <c r="J51">
-        <v>226</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52">
-        <v>85</v>
+        <v>502</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C52" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D52" t="s">
         <v>29</v>
       </c>
       <c r="E52" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F52" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G52" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H52" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="I52" t="s">
-        <v>349</v>
+        <v>396</v>
       </c>
       <c r="J52">
-        <v>162</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53">
-        <v>86</v>
+        <v>510</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D53" t="s">
         <v>29</v>
       </c>
       <c r="E53" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F53" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G53" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H53" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="I53" t="s">
-        <v>349</v>
+        <v>396</v>
       </c>
       <c r="J53">
-        <v>143</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54">
-        <v>87</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D54" t="s">
         <v>29</v>
       </c>
       <c r="E54" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F54" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G54" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H54" t="s">
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="I54" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J54">
-        <v>132</v>
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55">
-        <v>340</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D55" t="s">
         <v>29</v>
       </c>
       <c r="E55" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F55" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G55" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H55" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="I55" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J55">
-        <v>136</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D56" t="s">
         <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F56" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G56" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H56" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="I56" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J56">
-        <v>97</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57">
-        <v>343</v>
+        <v>321</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D57" t="s">
         <v>29</v>
       </c>
       <c r="E57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G57" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H57" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="I57" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J57">
-        <v>244</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D58" t="s">
         <v>29</v>
       </c>
       <c r="E58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F58" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G58" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H58" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
       <c r="I58" t="s">
-        <v>349</v>
+        <v>395</v>
       </c>
       <c r="J58">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B59" t="s">
         <v>11</v>
@@ -3312,27 +3456,27 @@
         <v>29</v>
       </c>
       <c r="E59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F59" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G59" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H59" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I59" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J59">
-        <v>429</v>
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B60" t="s">
         <v>11</v>
@@ -3344,30 +3488,30 @@
         <v>29</v>
       </c>
       <c r="E60" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F60" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G60" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H60" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I60" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J60">
-        <v>478</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="B61" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C61" t="s">
         <v>23</v>
@@ -3376,27 +3520,27 @@
         <v>29</v>
       </c>
       <c r="E61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F61" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G61" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H61" t="s">
-        <v>247</v>
+        <v>307</v>
       </c>
       <c r="I61" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J61">
-        <v>517</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -3408,27 +3552,27 @@
         <v>29</v>
       </c>
       <c r="E62" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F62" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G62" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="H62" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="I62" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J62">
-        <v>148</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -3440,27 +3584,27 @@
         <v>29</v>
       </c>
       <c r="E63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F63" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G63" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H63" t="s">
-        <v>247</v>
+        <v>308</v>
       </c>
       <c r="I63" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J63">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -3472,27 +3616,27 @@
         <v>29</v>
       </c>
       <c r="E64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F64" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G64" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H64" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="I64" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J64">
-        <v>90</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -3504,30 +3648,30 @@
         <v>29</v>
       </c>
       <c r="E65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F65" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G65" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H65" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I65" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J65">
-        <v>136</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66">
-        <v>325</v>
+        <v>85</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C66" t="s">
         <v>23</v>
@@ -3539,27 +3683,27 @@
         <v>46</v>
       </c>
       <c r="F66" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G66" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H66" t="s">
-        <v>276</v>
+        <v>308</v>
       </c>
       <c r="I66" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J66">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67">
-        <v>326</v>
+        <v>86</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C67" t="s">
         <v>23</v>
@@ -3571,27 +3715,27 @@
         <v>46</v>
       </c>
       <c r="F67" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G67" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H67" t="s">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="I67" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J67">
-        <v>59</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68">
-        <v>401</v>
+        <v>87</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C68" t="s">
         <v>23</v>
@@ -3600,30 +3744,30 @@
         <v>29</v>
       </c>
       <c r="E68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F68" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G68" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I68" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J68">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69">
-        <v>406</v>
+        <v>340</v>
       </c>
       <c r="B69" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
@@ -3632,30 +3776,30 @@
         <v>29</v>
       </c>
       <c r="E69" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F69" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G69" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H69" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="I69" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J69">
-        <v>88</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70">
-        <v>408</v>
+        <v>342</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
@@ -3664,30 +3808,30 @@
         <v>29</v>
       </c>
       <c r="E70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F70" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G70" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H70" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
       <c r="I70" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J70">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71">
-        <v>409</v>
+        <v>343</v>
       </c>
       <c r="B71" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C71" t="s">
         <v>23</v>
@@ -3696,30 +3840,30 @@
         <v>29</v>
       </c>
       <c r="E71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F71" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G71" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H71" t="s">
         <v>278</v>
       </c>
       <c r="I71" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J71">
-        <v>102</v>
+        <v>244</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72">
-        <v>410</v>
+        <v>346</v>
       </c>
       <c r="B72" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C72" t="s">
         <v>23</v>
@@ -3728,30 +3872,30 @@
         <v>29</v>
       </c>
       <c r="E72" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F72" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G72" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H72" t="s">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="I72" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J72">
-        <v>77</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73">
-        <v>411</v>
+        <v>94</v>
       </c>
       <c r="B73" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C73" t="s">
         <v>23</v>
@@ -3763,27 +3907,27 @@
         <v>47</v>
       </c>
       <c r="F73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G73" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H73" t="s">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="I73" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J73">
-        <v>72</v>
+        <v>429</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74">
-        <v>412</v>
+        <v>96</v>
       </c>
       <c r="B74" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C74" t="s">
         <v>23</v>
@@ -3795,27 +3939,27 @@
         <v>47</v>
       </c>
       <c r="F74" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G74" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H74" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="I74" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J74">
-        <v>88</v>
+        <v>478</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C75" t="s">
         <v>23</v>
@@ -3824,30 +3968,30 @@
         <v>29</v>
       </c>
       <c r="E75" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F75" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G75" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H75" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I75" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J75">
-        <v>369</v>
+        <v>517</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76">
-        <v>91</v>
+        <v>317</v>
       </c>
       <c r="B76" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -3856,30 +4000,30 @@
         <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F76" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G76" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H76" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I76" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J76">
-        <v>504</v>
+        <v>148</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77">
-        <v>92</v>
+        <v>318</v>
       </c>
       <c r="B77" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C77" t="s">
         <v>23</v>
@@ -3888,27 +4032,27 @@
         <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F77" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G77" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H77" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="I77" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J77">
-        <v>443</v>
+        <v>109</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -3920,27 +4064,27 @@
         <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F78" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G78" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H78" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="I78" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J78">
-        <v>347</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -3952,27 +4096,27 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F79" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G79" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H79" t="s">
-        <v>247</v>
+        <v>314</v>
       </c>
       <c r="I79" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J79">
-        <v>290</v>
+        <v>136</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -3984,27 +4128,27 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F80" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G80" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H80" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="I80" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J80">
-        <v>292</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -4016,1086 +4160,1086 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F81" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G81" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H81" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="I81" t="s">
-        <v>349</v>
+        <v>397</v>
       </c>
       <c r="J81">
-        <v>136</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82">
-        <v>352</v>
+        <v>401</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D82" t="s">
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F82" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G82" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H82" t="s">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="I82" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
       <c r="J82">
-        <v>216</v>
+        <v>134</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83">
-        <v>353</v>
+        <v>406</v>
       </c>
       <c r="B83" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C83" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D83" t="s">
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F83" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G83" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H83" t="s">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="I83" t="s">
-        <v>351</v>
+        <v>397</v>
       </c>
       <c r="J83">
-        <v>306</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84">
-        <v>258</v>
+        <v>408</v>
       </c>
       <c r="B84" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C84" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D84" t="s">
         <v>29</v>
       </c>
       <c r="E84" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F84" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G84" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H84" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="I84" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
       <c r="J84">
-        <v>313</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85">
-        <v>259</v>
+        <v>409</v>
       </c>
       <c r="B85" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D85" t="s">
         <v>29</v>
       </c>
       <c r="E85" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F85" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G85" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H85" t="s">
-        <v>284</v>
+        <v>317</v>
       </c>
       <c r="I85" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
       <c r="J85">
-        <v>298</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86">
-        <v>437</v>
+        <v>410</v>
       </c>
       <c r="B86" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D86" t="s">
         <v>29</v>
       </c>
       <c r="E86" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F86" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G86" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H86" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="I86" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
       <c r="J86">
-        <v>171</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87">
-        <v>471</v>
+        <v>411</v>
       </c>
       <c r="B87" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D87" t="s">
         <v>29</v>
       </c>
       <c r="E87" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F87" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G87" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H87" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="I87" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
       <c r="J87">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88">
-        <v>162</v>
+        <v>412</v>
       </c>
       <c r="B88" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C88" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D88" t="s">
         <v>29</v>
       </c>
       <c r="E88" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F88" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G88" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H88" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="I88" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="J88">
-        <v>77</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="B89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C89" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D89" t="s">
         <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F89" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G89" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H89" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="I89" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="J89">
-        <v>73</v>
+        <v>369</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="B90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C90" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D90" t="s">
         <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F90" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="G90" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H90" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="I90" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="J90">
-        <v>66</v>
+        <v>504</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D91" t="s">
         <v>29</v>
       </c>
       <c r="E91" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F91" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G91" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H91" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
       <c r="I91" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="J91">
-        <v>58</v>
+        <v>443</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92">
-        <v>382</v>
+        <v>313</v>
       </c>
       <c r="B92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D92" t="s">
         <v>29</v>
       </c>
       <c r="E92" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F92" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G92" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H92" t="s">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="I92" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="J92">
-        <v>73</v>
+        <v>347</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93">
-        <v>419</v>
+        <v>314</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C93" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D93" t="s">
         <v>29</v>
       </c>
       <c r="E93" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F93" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G93" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H93" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="I93" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="J93">
-        <v>61</v>
+        <v>290</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94">
-        <v>244</v>
+        <v>315</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D94" t="s">
         <v>29</v>
       </c>
       <c r="E94" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F94" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G94" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H94" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="I94" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="J94">
-        <v>62</v>
+        <v>292</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95">
-        <v>245</v>
+        <v>316</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D95" t="s">
         <v>29</v>
       </c>
       <c r="E95" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F95" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G95" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H95" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="I95" t="s">
-        <v>345</v>
+        <v>397</v>
       </c>
       <c r="J95">
-        <v>63</v>
+        <v>136</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96">
-        <v>246</v>
+        <v>352</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D96" t="s">
         <v>29</v>
       </c>
       <c r="E96" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F96" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G96" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H96" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="I96" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J96">
-        <v>58</v>
+        <v>216</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97">
-        <v>247</v>
+        <v>353</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C97" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D97" t="s">
         <v>29</v>
       </c>
       <c r="E97" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F97" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G97" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H97" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="I97" t="s">
-        <v>345</v>
+        <v>399</v>
       </c>
       <c r="J97">
-        <v>67</v>
+        <v>306</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98">
-        <v>383</v>
+        <v>258</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D98" t="s">
         <v>29</v>
       </c>
       <c r="E98" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F98" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G98" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H98" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="I98" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J98">
-        <v>69</v>
+        <v>313</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99">
-        <v>158</v>
+        <v>259</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D99" t="s">
         <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F99" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G99" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H99" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="I99" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J99">
-        <v>84</v>
+        <v>298</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="A100">
-        <v>159</v>
+        <v>495</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D100" t="s">
         <v>29</v>
       </c>
       <c r="E100" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F100" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G100" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H100" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="I100" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J100">
-        <v>74</v>
+        <v>183</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101">
-        <v>160</v>
+        <v>498</v>
       </c>
       <c r="B101" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D101" t="s">
         <v>29</v>
       </c>
       <c r="E101" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F101" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G101" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H101" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="I101" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J101">
-        <v>75</v>
+        <v>167</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="A102">
-        <v>384</v>
+        <v>499</v>
       </c>
       <c r="B102" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C102" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D102" t="s">
         <v>29</v>
       </c>
       <c r="E102" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F102" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G102" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H102" t="s">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="I102" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J102">
-        <v>65</v>
+        <v>155</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="A103">
-        <v>385</v>
+        <v>500</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D103" t="s">
         <v>29</v>
       </c>
       <c r="E103" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F103" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G103" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H103" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="I103" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J103">
-        <v>65</v>
+        <v>142</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="A104">
-        <v>109</v>
+        <v>503</v>
       </c>
       <c r="B104" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D104" t="s">
         <v>29</v>
       </c>
       <c r="E104" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F104" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G104" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H104" t="s">
-        <v>247</v>
+        <v>325</v>
       </c>
       <c r="I104" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J104">
-        <v>81</v>
+        <v>126</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105">
-        <v>262</v>
+        <v>505</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D105" t="s">
         <v>29</v>
       </c>
       <c r="E105" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F105" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G105" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H105" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="I105" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J105">
-        <v>84</v>
+        <v>141</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106">
-        <v>263</v>
+        <v>437</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D106" t="s">
         <v>29</v>
       </c>
       <c r="E106" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F106" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G106" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H106" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="I106" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J106">
-        <v>65</v>
+        <v>171</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107">
-        <v>264</v>
+        <v>471</v>
       </c>
       <c r="B107" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D107" t="s">
         <v>29</v>
       </c>
       <c r="E107" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F107" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G107" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H107" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="I107" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J107">
-        <v>63</v>
+        <v>166</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108">
-        <v>265</v>
+        <v>476</v>
       </c>
       <c r="B108" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D108" t="s">
         <v>29</v>
       </c>
       <c r="E108" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F108" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G108" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H108" t="s">
-        <v>301</v>
+        <v>327</v>
       </c>
       <c r="I108" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J108">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109">
-        <v>416</v>
+        <v>479</v>
       </c>
       <c r="B109" t="s">
         <v>19</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D109" t="s">
         <v>29</v>
       </c>
       <c r="E109" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F109" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="G109" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H109" t="s">
-        <v>302</v>
+        <v>328</v>
       </c>
       <c r="I109" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J109">
-        <v>67</v>
+        <v>157</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110">
-        <v>417</v>
+        <v>481</v>
       </c>
       <c r="B110" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D110" t="s">
         <v>29</v>
       </c>
       <c r="E110" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F110" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G110" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H110" t="s">
-        <v>247</v>
+        <v>328</v>
       </c>
       <c r="I110" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J110">
-        <v>91</v>
+        <v>191</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="A111">
-        <v>418</v>
+        <v>483</v>
       </c>
       <c r="B111" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D111" t="s">
         <v>29</v>
       </c>
       <c r="E111" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F111" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G111" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H111" t="s">
-        <v>303</v>
+        <v>328</v>
       </c>
       <c r="I111" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J111">
-        <v>64</v>
+        <v>137</v>
       </c>
     </row>
     <row r="112" spans="1:10">
       <c r="A112">
-        <v>111</v>
+        <v>484</v>
       </c>
       <c r="B112" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D112" t="s">
         <v>29</v>
       </c>
       <c r="E112" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F112" t="s">
         <v>164</v>
       </c>
       <c r="G112" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H112" t="s">
-        <v>247</v>
+        <v>329</v>
       </c>
       <c r="I112" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J112">
-        <v>62</v>
+        <v>172</v>
       </c>
     </row>
     <row r="113" spans="1:10">
       <c r="A113">
-        <v>165</v>
+        <v>488</v>
       </c>
       <c r="B113" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D113" t="s">
         <v>29</v>
       </c>
       <c r="E113" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F113" t="s">
         <v>165</v>
       </c>
       <c r="G113" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H113" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="I113" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J113">
-        <v>68</v>
+        <v>167</v>
       </c>
     </row>
     <row r="114" spans="1:10">
       <c r="A114">
-        <v>166</v>
+        <v>489</v>
       </c>
       <c r="B114" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D114" t="s">
         <v>29</v>
       </c>
       <c r="E114" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F114" t="s">
         <v>166</v>
       </c>
       <c r="G114" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H114" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="I114" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="J114">
-        <v>81</v>
+        <v>107</v>
       </c>
     </row>
     <row r="115" spans="1:10">
       <c r="A115">
-        <v>241</v>
+        <v>162</v>
       </c>
       <c r="B115" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C115" t="s">
         <v>25</v>
@@ -5104,30 +5248,30 @@
         <v>29</v>
       </c>
       <c r="E115" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F115" t="s">
         <v>167</v>
       </c>
       <c r="G115" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H115" t="s">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="I115" t="s">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="J115">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="116" spans="1:10">
       <c r="A116">
-        <v>242</v>
+        <v>163</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C116" t="s">
         <v>25</v>
@@ -5136,30 +5280,30 @@
         <v>29</v>
       </c>
       <c r="E116" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F116" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G116" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H116" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="I116" t="s">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="J116">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="A117">
-        <v>243</v>
+        <v>164</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C117" t="s">
         <v>25</v>
@@ -5168,1203 +5312,1203 @@
         <v>29</v>
       </c>
       <c r="E117" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F117" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G117" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H117" t="s">
-        <v>307</v>
+        <v>332</v>
       </c>
       <c r="I117" t="s">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="J117">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="118" spans="1:10">
       <c r="A118">
-        <v>390</v>
+        <v>266</v>
       </c>
       <c r="B118" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D118" t="s">
         <v>29</v>
       </c>
       <c r="E118" t="s">
+        <v>54</v>
+      </c>
+      <c r="F118" t="s">
+        <v>170</v>
+      </c>
+      <c r="G118" t="s">
+        <v>271</v>
+      </c>
+      <c r="H118" t="s">
+        <v>333</v>
+      </c>
+      <c r="I118" t="s">
+        <v>392</v>
+      </c>
+      <c r="J118">
         <v>58</v>
-      </c>
-      <c r="F118" t="s">
-        <v>169</v>
-      </c>
-      <c r="G118" t="s">
-        <v>240</v>
-      </c>
-      <c r="H118" t="s">
-        <v>308</v>
-      </c>
-      <c r="I118" t="s">
-        <v>352</v>
-      </c>
-      <c r="J118">
-        <v>190</v>
       </c>
     </row>
     <row r="119" spans="1:10">
       <c r="A119">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B119" t="s">
         <v>14</v>
       </c>
       <c r="C119" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D119" t="s">
         <v>29</v>
       </c>
       <c r="E119" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F119" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G119" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H119" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="I119" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J119">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="120" spans="1:10">
       <c r="A120">
+        <v>419</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="s">
+        <v>25</v>
+      </c>
+      <c r="D120" t="s">
+        <v>29</v>
+      </c>
+      <c r="E120" t="s">
+        <v>54</v>
+      </c>
+      <c r="F120" t="s">
+        <v>170</v>
+      </c>
+      <c r="G120" t="s">
+        <v>271</v>
+      </c>
+      <c r="H120" t="s">
+        <v>330</v>
+      </c>
+      <c r="I120" t="s">
         <v>392</v>
       </c>
-      <c r="B120" t="s">
-        <v>14</v>
-      </c>
-      <c r="C120" t="s">
-        <v>26</v>
-      </c>
-      <c r="D120" t="s">
-        <v>29</v>
-      </c>
-      <c r="E120" t="s">
-        <v>58</v>
-      </c>
-      <c r="F120" t="s">
-        <v>171</v>
-      </c>
-      <c r="G120" t="s">
-        <v>240</v>
-      </c>
-      <c r="H120" t="s">
-        <v>310</v>
-      </c>
-      <c r="I120" t="s">
-        <v>352</v>
-      </c>
       <c r="J120">
-        <v>90</v>
+        <v>61</v>
       </c>
     </row>
     <row r="121" spans="1:10">
       <c r="A121">
-        <v>393</v>
+        <v>244</v>
       </c>
       <c r="B121" t="s">
         <v>15</v>
       </c>
       <c r="C121" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D121" t="s">
         <v>29</v>
       </c>
       <c r="E121" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F121" t="s">
         <v>172</v>
       </c>
       <c r="G121" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H121" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="I121" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J121">
-        <v>110</v>
+        <v>62</v>
       </c>
     </row>
     <row r="122" spans="1:10">
       <c r="A122">
-        <v>452</v>
+        <v>245</v>
       </c>
       <c r="B122" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C122" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D122" t="s">
         <v>29</v>
       </c>
       <c r="E122" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F122" t="s">
         <v>173</v>
       </c>
       <c r="G122" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H122" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="I122" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J122">
-        <v>169</v>
+        <v>63</v>
       </c>
     </row>
     <row r="123" spans="1:10">
       <c r="A123">
-        <v>453</v>
+        <v>246</v>
       </c>
       <c r="B123" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C123" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D123" t="s">
         <v>29</v>
       </c>
       <c r="E123" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F123" t="s">
         <v>174</v>
       </c>
       <c r="G123" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H123" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="I123" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J123">
-        <v>101</v>
+        <v>58</v>
       </c>
     </row>
     <row r="124" spans="1:10">
       <c r="A124">
-        <v>454</v>
+        <v>247</v>
       </c>
       <c r="B124" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C124" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D124" t="s">
         <v>29</v>
       </c>
       <c r="E124" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F124" t="s">
         <v>175</v>
       </c>
       <c r="G124" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H124" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="I124" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J124">
-        <v>110</v>
+        <v>67</v>
       </c>
     </row>
     <row r="125" spans="1:10">
       <c r="A125">
-        <v>213</v>
+        <v>383</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D125" t="s">
         <v>29</v>
       </c>
       <c r="E125" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F125" t="s">
         <v>176</v>
       </c>
       <c r="G125" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H125" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="I125" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J125">
-        <v>109</v>
+        <v>69</v>
       </c>
     </row>
     <row r="126" spans="1:10">
       <c r="A126">
-        <v>394</v>
+        <v>158</v>
       </c>
       <c r="B126" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C126" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D126" t="s">
         <v>29</v>
       </c>
       <c r="E126" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F126" t="s">
         <v>177</v>
       </c>
       <c r="G126" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H126" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="I126" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J126">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="127" spans="1:10">
       <c r="A127">
-        <v>396</v>
+        <v>159</v>
       </c>
       <c r="B127" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C127" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D127" t="s">
         <v>29</v>
       </c>
       <c r="E127" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F127" t="s">
         <v>178</v>
       </c>
       <c r="G127" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H127" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="I127" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J127">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="128" spans="1:10">
       <c r="A128">
-        <v>399</v>
+        <v>160</v>
       </c>
       <c r="B128" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C128" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D128" t="s">
         <v>29</v>
       </c>
       <c r="E128" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F128" t="s">
         <v>179</v>
       </c>
       <c r="G128" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H128" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="I128" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J128">
-        <v>108</v>
+        <v>75</v>
       </c>
     </row>
     <row r="129" spans="1:10">
       <c r="A129">
-        <v>189</v>
+        <v>384</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D129" t="s">
         <v>29</v>
       </c>
       <c r="E129" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F129" t="s">
         <v>180</v>
       </c>
       <c r="G129" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H129" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="I129" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J129">
-        <v>96</v>
+        <v>65</v>
       </c>
     </row>
     <row r="130" spans="1:10">
       <c r="A130">
-        <v>190</v>
+        <v>385</v>
       </c>
       <c r="B130" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C130" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D130" t="s">
         <v>29</v>
       </c>
       <c r="E130" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="F130" t="s">
         <v>181</v>
       </c>
       <c r="G130" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H130" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="I130" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J130">
-        <v>97</v>
+        <v>65</v>
       </c>
     </row>
     <row r="131" spans="1:10">
       <c r="A131">
-        <v>228</v>
+        <v>109</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C131" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D131" t="s">
         <v>29</v>
       </c>
       <c r="E131" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F131" t="s">
         <v>182</v>
       </c>
       <c r="G131" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H131" t="s">
-        <v>319</v>
+        <v>278</v>
       </c>
       <c r="I131" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J131">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132" spans="1:10">
       <c r="A132">
-        <v>469</v>
+        <v>262</v>
       </c>
       <c r="B132" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C132" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D132" t="s">
         <v>29</v>
       </c>
       <c r="E132" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F132" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G132" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H132" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="I132" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J132">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="133" spans="1:10">
       <c r="A133">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B133" t="s">
         <v>15</v>
       </c>
       <c r="C133" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D133" t="s">
         <v>29</v>
       </c>
       <c r="E133" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F133" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G133" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H133" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="I133" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J133">
-        <v>105</v>
+        <v>65</v>
       </c>
     </row>
     <row r="134" spans="1:10">
       <c r="A134">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="B134" t="s">
         <v>12</v>
       </c>
       <c r="C134" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D134" t="s">
         <v>29</v>
       </c>
       <c r="E134" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F134" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G134" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H134" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="I134" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="J134">
-        <v>105</v>
+        <v>63</v>
       </c>
     </row>
     <row r="135" spans="1:10">
       <c r="A135">
-        <v>151</v>
+        <v>265</v>
       </c>
       <c r="B135" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C135" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D135" t="s">
         <v>29</v>
       </c>
       <c r="E135" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F135" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G135" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H135" t="s">
-        <v>247</v>
+        <v>345</v>
       </c>
       <c r="I135" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="J135">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="136" spans="1:10">
       <c r="A136">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="B136" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C136" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D136" t="s">
         <v>29</v>
       </c>
       <c r="E136" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F136" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="G136" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H136" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="I136" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="J136">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="137" spans="1:10">
       <c r="A137">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="B137" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C137" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D137" t="s">
         <v>29</v>
       </c>
       <c r="E137" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F137" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G137" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H137" t="s">
-        <v>324</v>
+        <v>278</v>
       </c>
       <c r="I137" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="J137">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="138" spans="1:10">
       <c r="A138">
-        <v>441</v>
+        <v>418</v>
       </c>
       <c r="B138" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C138" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D138" t="s">
         <v>29</v>
       </c>
       <c r="E138" t="s">
+        <v>57</v>
+      </c>
+      <c r="F138" t="s">
+        <v>184</v>
+      </c>
+      <c r="G138" t="s">
+        <v>271</v>
+      </c>
+      <c r="H138" t="s">
+        <v>347</v>
+      </c>
+      <c r="I138" t="s">
+        <v>392</v>
+      </c>
+      <c r="J138">
         <v>64</v>
-      </c>
-      <c r="F138" t="s">
-        <v>187</v>
-      </c>
-      <c r="G138" t="s">
-        <v>240</v>
-      </c>
-      <c r="H138" t="s">
-        <v>325</v>
-      </c>
-      <c r="I138" t="s">
-        <v>353</v>
-      </c>
-      <c r="J138">
-        <v>129</v>
       </c>
     </row>
     <row r="139" spans="1:10">
       <c r="A139">
-        <v>443</v>
+        <v>111</v>
       </c>
       <c r="B139" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C139" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D139" t="s">
         <v>29</v>
       </c>
       <c r="E139" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F139" t="s">
         <v>188</v>
       </c>
       <c r="G139" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H139" t="s">
-        <v>324</v>
+        <v>278</v>
       </c>
       <c r="I139" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="J139">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140" spans="1:10">
       <c r="A140">
-        <v>444</v>
+        <v>165</v>
       </c>
       <c r="B140" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C140" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D140" t="s">
         <v>29</v>
       </c>
       <c r="E140" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F140" t="s">
         <v>189</v>
       </c>
       <c r="G140" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H140" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="I140" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="J140">
-        <v>107</v>
+        <v>68</v>
       </c>
     </row>
     <row r="141" spans="1:10">
       <c r="A141">
-        <v>236</v>
+        <v>166</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C141" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D141" t="s">
         <v>29</v>
       </c>
       <c r="E141" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F141" t="s">
         <v>190</v>
       </c>
       <c r="G141" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H141" t="s">
-        <v>247</v>
+        <v>349</v>
       </c>
       <c r="I141" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="J141">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="142" spans="1:10">
       <c r="A142">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B142" t="s">
         <v>15</v>
       </c>
       <c r="C142" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D142" t="s">
         <v>29</v>
       </c>
       <c r="E142" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F142" t="s">
         <v>191</v>
       </c>
       <c r="G142" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="H142" t="s">
-        <v>247</v>
+        <v>348</v>
       </c>
       <c r="I142" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="J142">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="143" spans="1:10">
       <c r="A143">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="B143" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C143" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D143" t="s">
         <v>29</v>
       </c>
       <c r="E143" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F143" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G143" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H143" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
       <c r="I143" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="J143">
-        <v>111</v>
+        <v>80</v>
       </c>
     </row>
     <row r="144" spans="1:10">
       <c r="A144">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="B144" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C144" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D144" t="s">
         <v>29</v>
       </c>
       <c r="E144" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F144" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G144" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H144" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="I144" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="J144">
-        <v>84</v>
+        <v>55</v>
       </c>
     </row>
     <row r="145" spans="1:10">
       <c r="A145">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="B145" t="s">
         <v>19</v>
       </c>
       <c r="C145" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D145" t="s">
         <v>29</v>
       </c>
       <c r="E145" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F145" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G145" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H145" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="I145" t="s">
-        <v>353</v>
+        <v>400</v>
       </c>
       <c r="J145">
-        <v>66</v>
+        <v>190</v>
       </c>
     </row>
     <row r="146" spans="1:10">
       <c r="A146">
-        <v>193</v>
+        <v>391</v>
       </c>
       <c r="B146" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C146" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D146" t="s">
         <v>29</v>
       </c>
       <c r="E146" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F146" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G146" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H146" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="I146" t="s">
-        <v>353</v>
+        <v>400</v>
       </c>
       <c r="J146">
-        <v>167</v>
+        <v>95</v>
       </c>
     </row>
     <row r="147" spans="1:10">
       <c r="A147">
-        <v>300</v>
+        <v>392</v>
       </c>
       <c r="B147" t="s">
         <v>14</v>
       </c>
       <c r="C147" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D147" t="s">
         <v>29</v>
       </c>
       <c r="E147" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F147" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G147" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H147" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="I147" t="s">
-        <v>353</v>
+        <v>400</v>
       </c>
       <c r="J147">
-        <v>149</v>
+        <v>90</v>
       </c>
     </row>
     <row r="148" spans="1:10">
       <c r="A148">
-        <v>304</v>
+        <v>393</v>
       </c>
       <c r="B148" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C148" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D148" t="s">
         <v>29</v>
       </c>
       <c r="E148" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F148" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G148" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H148" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="I148" t="s">
-        <v>353</v>
+        <v>400</v>
       </c>
       <c r="J148">
-        <v>200</v>
+        <v>110</v>
       </c>
     </row>
     <row r="149" spans="1:10">
       <c r="A149">
+        <v>452</v>
+      </c>
+      <c r="B149" t="s">
+        <v>10</v>
+      </c>
+      <c r="C149" t="s">
+        <v>26</v>
+      </c>
+      <c r="D149" t="s">
+        <v>29</v>
+      </c>
+      <c r="E149" t="s">
+        <v>60</v>
+      </c>
+      <c r="F149" t="s">
+        <v>197</v>
+      </c>
+      <c r="G149" t="s">
+        <v>271</v>
+      </c>
+      <c r="H149" t="s">
         <v>356</v>
       </c>
-      <c r="B149" t="s">
-        <v>13</v>
-      </c>
-      <c r="C149" t="s">
-        <v>27</v>
-      </c>
-      <c r="D149" t="s">
-        <v>29</v>
-      </c>
-      <c r="E149" t="s">
-        <v>66</v>
-      </c>
-      <c r="F149" t="s">
-        <v>198</v>
-      </c>
-      <c r="G149" t="s">
-        <v>240</v>
-      </c>
-      <c r="H149" t="s">
-        <v>331</v>
-      </c>
       <c r="I149" t="s">
-        <v>353</v>
+        <v>400</v>
       </c>
       <c r="J149">
-        <v>772</v>
+        <v>169</v>
       </c>
     </row>
     <row r="150" spans="1:10">
       <c r="A150">
-        <v>132</v>
+        <v>453</v>
       </c>
       <c r="B150" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C150" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D150" t="s">
         <v>29</v>
       </c>
       <c r="E150" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F150" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G150" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H150" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="I150" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J150">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="151" spans="1:10">
       <c r="A151">
-        <v>192</v>
+        <v>454</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C151" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D151" t="s">
         <v>29</v>
       </c>
       <c r="E151" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F151" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G151" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H151" t="s">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="I151" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J151">
-        <v>83</v>
+        <v>110</v>
       </c>
     </row>
     <row r="152" spans="1:10">
       <c r="A152">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="B152" t="s">
         <v>15</v>
       </c>
       <c r="C152" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D152" t="s">
         <v>29</v>
       </c>
       <c r="E152" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F152" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G152" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H152" t="s">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="I152" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J152">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="153" spans="1:10">
       <c r="A153">
-        <v>195</v>
+        <v>394</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C153" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D153" t="s">
         <v>29</v>
       </c>
       <c r="E153" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F153" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G153" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H153" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="I153" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J153">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="154" spans="1:10">
       <c r="A154">
-        <v>196</v>
+        <v>396</v>
       </c>
       <c r="B154" t="s">
         <v>15</v>
       </c>
       <c r="C154" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D154" t="s">
         <v>29</v>
       </c>
       <c r="E154" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F154" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G154" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H154" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="I154" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J154">
         <v>91</v>
@@ -6372,778 +6516,778 @@
     </row>
     <row r="155" spans="1:10">
       <c r="A155">
-        <v>462</v>
+        <v>399</v>
       </c>
       <c r="B155" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C155" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D155" t="s">
         <v>29</v>
       </c>
       <c r="E155" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F155" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G155" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H155" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="I155" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J155">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="156" spans="1:10">
       <c r="A156">
-        <v>463</v>
+        <v>189</v>
       </c>
       <c r="B156" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C156" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D156" t="s">
         <v>29</v>
       </c>
       <c r="E156" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F156" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G156" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H156" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="I156" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J156">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="157" spans="1:10">
       <c r="A157">
-        <v>464</v>
+        <v>190</v>
       </c>
       <c r="B157" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C157" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D157" t="s">
         <v>29</v>
       </c>
       <c r="E157" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F157" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G157" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H157" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="I157" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J157">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="158" spans="1:10">
       <c r="A158">
-        <v>465</v>
+        <v>228</v>
       </c>
       <c r="B158" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C158" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D158" t="s">
         <v>29</v>
       </c>
       <c r="E158" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F158" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G158" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H158" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="I158" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J158">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="159" spans="1:10">
       <c r="A159">
-        <v>105</v>
+        <v>469</v>
       </c>
       <c r="B159" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C159" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D159" t="s">
         <v>29</v>
       </c>
       <c r="E159" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F159" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G159" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H159" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="I159" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J159">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="160" spans="1:10">
       <c r="A160">
-        <v>145</v>
+        <v>478</v>
       </c>
       <c r="B160" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C160" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D160" t="s">
         <v>29</v>
       </c>
       <c r="E160" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F160" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G160" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H160" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="I160" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J160">
-        <v>94</v>
+        <v>192</v>
       </c>
     </row>
     <row r="161" spans="1:10">
       <c r="A161">
-        <v>146</v>
+        <v>276</v>
       </c>
       <c r="B161" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C161" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D161" t="s">
         <v>29</v>
       </c>
       <c r="E161" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F161" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G161" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H161" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="I161" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J161">
-        <v>97</v>
+        <v>105</v>
       </c>
     </row>
     <row r="162" spans="1:10">
       <c r="A162">
-        <v>425</v>
+        <v>279</v>
       </c>
       <c r="B162" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C162" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D162" t="s">
         <v>29</v>
       </c>
       <c r="E162" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F162" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G162" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H162" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="I162" t="s">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="J162">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="163" spans="1:10">
       <c r="A163">
-        <v>426</v>
+        <v>151</v>
       </c>
       <c r="B163" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C163" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D163" t="s">
         <v>29</v>
       </c>
       <c r="E163" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F163" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G163" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H163" t="s">
-        <v>336</v>
+        <v>278</v>
       </c>
       <c r="I163" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J163">
-        <v>97</v>
+        <v>63</v>
       </c>
     </row>
     <row r="164" spans="1:10">
       <c r="A164">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="B164" t="s">
         <v>17</v>
       </c>
       <c r="C164" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D164" t="s">
         <v>29</v>
       </c>
       <c r="E164" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F164" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G164" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H164" t="s">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="I164" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J164">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="165" spans="1:10">
       <c r="A165">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B165" t="s">
         <v>17</v>
       </c>
       <c r="C165" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D165" t="s">
         <v>29</v>
       </c>
       <c r="E165" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F165" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G165" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H165" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="I165" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J165">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="166" spans="1:10">
       <c r="A166">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="B166" t="s">
         <v>17</v>
       </c>
       <c r="C166" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D166" t="s">
         <v>29</v>
       </c>
       <c r="E166" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F166" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G166" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H166" t="s">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="I166" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J166">
-        <v>102</v>
+        <v>129</v>
       </c>
     </row>
     <row r="167" spans="1:10">
       <c r="A167">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B167" t="s">
         <v>17</v>
       </c>
       <c r="C167" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D167" t="s">
         <v>29</v>
       </c>
       <c r="E167" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F167" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="G167" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H167" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="I167" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J167">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="168" spans="1:10">
       <c r="A168">
-        <v>72</v>
+        <v>444</v>
       </c>
       <c r="B168" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C168" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D168" t="s">
         <v>29</v>
       </c>
       <c r="E168" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F168" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G168" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H168" t="s">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="I168" t="s">
-        <v>355</v>
+        <v>401</v>
       </c>
       <c r="J168">
-        <v>81</v>
+        <v>107</v>
       </c>
     </row>
     <row r="169" spans="1:10">
       <c r="A169">
-        <v>208</v>
+        <v>492</v>
       </c>
       <c r="B169" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C169" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D169" t="s">
         <v>29</v>
       </c>
       <c r="E169" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F169" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G169" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H169" t="s">
-        <v>338</v>
+        <v>371</v>
       </c>
       <c r="I169" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J169">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="170" spans="1:10">
       <c r="A170">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="B170" t="s">
         <v>15</v>
       </c>
       <c r="C170" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D170" t="s">
         <v>29</v>
       </c>
       <c r="E170" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F170" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G170" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H170" t="s">
-        <v>338</v>
+        <v>278</v>
       </c>
       <c r="I170" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J170">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="171" spans="1:10">
       <c r="A171">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B171" t="s">
         <v>15</v>
       </c>
       <c r="C171" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D171" t="s">
         <v>29</v>
       </c>
       <c r="E171" t="s">
+        <v>67</v>
+      </c>
+      <c r="F171" t="s">
+        <v>217</v>
+      </c>
+      <c r="G171" t="s">
+        <v>272</v>
+      </c>
+      <c r="H171" t="s">
+        <v>278</v>
+      </c>
+      <c r="I171" t="s">
+        <v>401</v>
+      </c>
+      <c r="J171">
         <v>69</v>
-      </c>
-      <c r="F171" t="s">
-        <v>220</v>
-      </c>
-      <c r="G171" t="s">
-        <v>240</v>
-      </c>
-      <c r="H171" t="s">
-        <v>338</v>
-      </c>
-      <c r="I171" t="s">
-        <v>354</v>
-      </c>
-      <c r="J171">
-        <v>98</v>
       </c>
     </row>
     <row r="172" spans="1:10">
       <c r="A172">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="B172" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C172" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D172" t="s">
         <v>29</v>
       </c>
       <c r="E172" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F172" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G172" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H172" t="s">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="I172" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J172">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="173" spans="1:10">
       <c r="A173">
-        <v>212</v>
+        <v>301</v>
       </c>
       <c r="B173" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C173" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D173" t="s">
         <v>29</v>
       </c>
       <c r="E173" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F173" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G173" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H173" t="s">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="I173" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J173">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="174" spans="1:10">
       <c r="A174">
-        <v>73</v>
+        <v>413</v>
       </c>
       <c r="B174" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C174" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D174" t="s">
         <v>29</v>
       </c>
       <c r="E174" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F174" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G174" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H174" t="s">
-        <v>339</v>
+        <v>372</v>
       </c>
       <c r="I174" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J174">
-        <v>123</v>
+        <v>66</v>
       </c>
     </row>
     <row r="175" spans="1:10">
       <c r="A175">
-        <v>273</v>
+        <v>193</v>
       </c>
       <c r="B175" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C175" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D175" t="s">
         <v>29</v>
       </c>
       <c r="E175" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F175" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G175" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H175" t="s">
-        <v>340</v>
+        <v>373</v>
       </c>
       <c r="I175" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J175">
-        <v>108</v>
+        <v>167</v>
       </c>
     </row>
     <row r="176" spans="1:10">
       <c r="A176">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="B176" t="s">
         <v>14</v>
       </c>
       <c r="C176" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D176" t="s">
         <v>29</v>
       </c>
       <c r="E176" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F176" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G176" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H176" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
       <c r="I176" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J176">
-        <v>116</v>
+        <v>149</v>
       </c>
     </row>
     <row r="177" spans="1:10">
       <c r="A177">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="B177" t="s">
         <v>14</v>
       </c>
       <c r="C177" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D177" t="s">
         <v>29</v>
       </c>
       <c r="E177" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F177" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G177" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H177" t="s">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="I177" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J177">
-        <v>112</v>
+        <v>200</v>
       </c>
     </row>
     <row r="178" spans="1:10">
       <c r="A178">
-        <v>277</v>
+        <v>356</v>
       </c>
       <c r="B178" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C178" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D178" t="s">
         <v>29</v>
       </c>
       <c r="E178" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F178" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="G178" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H178" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="I178" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="J178">
-        <v>102</v>
+        <v>772</v>
       </c>
     </row>
     <row r="179" spans="1:10">
       <c r="A179">
-        <v>278</v>
+        <v>132</v>
       </c>
       <c r="B179" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C179" t="s">
         <v>28</v>
@@ -7152,30 +7296,30 @@
         <v>29</v>
       </c>
       <c r="E179" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F179" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="G179" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H179" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="I179" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J179">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="180" spans="1:10">
       <c r="A180">
-        <v>280</v>
+        <v>192</v>
       </c>
       <c r="B180" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C180" t="s">
         <v>28</v>
@@ -7184,30 +7328,30 @@
         <v>29</v>
       </c>
       <c r="E180" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F180" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G180" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H180" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="I180" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J180">
-        <v>101</v>
+        <v>83</v>
       </c>
     </row>
     <row r="181" spans="1:10">
       <c r="A181">
-        <v>281</v>
+        <v>194</v>
       </c>
       <c r="B181" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C181" t="s">
         <v>28</v>
@@ -7216,30 +7360,30 @@
         <v>29</v>
       </c>
       <c r="E181" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F181" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G181" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H181" t="s">
-        <v>340</v>
+        <v>377</v>
       </c>
       <c r="I181" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J181">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="182" spans="1:10">
       <c r="A182">
-        <v>74</v>
+        <v>195</v>
       </c>
       <c r="B182" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C182" t="s">
         <v>28</v>
@@ -7248,30 +7392,30 @@
         <v>29</v>
       </c>
       <c r="E182" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F182" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G182" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H182" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="I182" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J182">
-        <v>54</v>
+        <v>110</v>
       </c>
     </row>
     <row r="183" spans="1:10">
       <c r="A183">
-        <v>107</v>
+        <v>196</v>
       </c>
       <c r="B183" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C183" t="s">
         <v>28</v>
@@ -7280,30 +7424,30 @@
         <v>29</v>
       </c>
       <c r="E183" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F183" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G183" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H183" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
       <c r="I183" t="s">
-        <v>355</v>
+        <v>402</v>
       </c>
       <c r="J183">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="184" spans="1:10">
       <c r="A184">
-        <v>138</v>
+        <v>462</v>
       </c>
       <c r="B184" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C184" t="s">
         <v>28</v>
@@ -7312,19 +7456,19 @@
         <v>29</v>
       </c>
       <c r="E184" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F184" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G184" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H184" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="I184" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J184">
         <v>104</v>
@@ -7332,10 +7476,10 @@
     </row>
     <row r="185" spans="1:10">
       <c r="A185">
-        <v>139</v>
+        <v>463</v>
       </c>
       <c r="B185" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C185" t="s">
         <v>28</v>
@@ -7344,30 +7488,30 @@
         <v>29</v>
       </c>
       <c r="E185" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F185" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G185" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H185" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="I185" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J185">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="186" spans="1:10">
       <c r="A186">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="B186" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C186" t="s">
         <v>28</v>
@@ -7376,30 +7520,30 @@
         <v>29</v>
       </c>
       <c r="E186" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F186" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G186" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H186" t="s">
-        <v>343</v>
+        <v>378</v>
       </c>
       <c r="I186" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J186">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="187" spans="1:10">
       <c r="A187">
-        <v>422</v>
+        <v>465</v>
       </c>
       <c r="B187" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C187" t="s">
         <v>28</v>
@@ -7408,30 +7552,30 @@
         <v>29</v>
       </c>
       <c r="E187" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F187" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G187" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H187" t="s">
-        <v>343</v>
+        <v>378</v>
       </c>
       <c r="I187" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J187">
-        <v>103</v>
+        <v>91</v>
       </c>
     </row>
     <row r="188" spans="1:10">
       <c r="A188">
-        <v>423</v>
+        <v>105</v>
       </c>
       <c r="B188" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C188" t="s">
         <v>28</v>
@@ -7440,30 +7584,30 @@
         <v>29</v>
       </c>
       <c r="E188" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F188" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G188" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H188" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
       <c r="I188" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J188">
-        <v>98</v>
+        <v>67</v>
       </c>
     </row>
     <row r="189" spans="1:10">
       <c r="A189">
-        <v>424</v>
+        <v>145</v>
       </c>
       <c r="B189" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C189" t="s">
         <v>28</v>
@@ -7472,30 +7616,30 @@
         <v>29</v>
       </c>
       <c r="E189" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F189" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G189" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H189" t="s">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="I189" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J189">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="190" spans="1:10">
       <c r="A190">
-        <v>460</v>
+        <v>146</v>
       </c>
       <c r="B190" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C190" t="s">
         <v>28</v>
@@ -7504,30 +7648,30 @@
         <v>29</v>
       </c>
       <c r="E190" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F190" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G190" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="H190" t="s">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="I190" t="s">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="J190">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="191" spans="1:10">
       <c r="A191">
-        <v>461</v>
+        <v>425</v>
       </c>
       <c r="B191" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C191" t="s">
         <v>28</v>
@@ -7536,21 +7680,1109 @@
         <v>29</v>
       </c>
       <c r="E191" t="s">
+        <v>70</v>
+      </c>
+      <c r="F191" t="s">
+        <v>237</v>
+      </c>
+      <c r="G191" t="s">
+        <v>271</v>
+      </c>
+      <c r="H191" t="s">
+        <v>381</v>
+      </c>
+      <c r="I191" t="s">
+        <v>402</v>
+      </c>
+      <c r="J191">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10">
+      <c r="A192">
+        <v>426</v>
+      </c>
+      <c r="B192" t="s">
+        <v>17</v>
+      </c>
+      <c r="C192" t="s">
+        <v>28</v>
+      </c>
+      <c r="D192" t="s">
+        <v>29</v>
+      </c>
+      <c r="E192" t="s">
+        <v>70</v>
+      </c>
+      <c r="F192" t="s">
+        <v>238</v>
+      </c>
+      <c r="G192" t="s">
+        <v>271</v>
+      </c>
+      <c r="H192" t="s">
+        <v>381</v>
+      </c>
+      <c r="I192" t="s">
+        <v>402</v>
+      </c>
+      <c r="J192">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10">
+      <c r="A193">
+        <v>427</v>
+      </c>
+      <c r="B193" t="s">
+        <v>17</v>
+      </c>
+      <c r="C193" t="s">
+        <v>28</v>
+      </c>
+      <c r="D193" t="s">
+        <v>29</v>
+      </c>
+      <c r="E193" t="s">
+        <v>70</v>
+      </c>
+      <c r="F193" t="s">
+        <v>239</v>
+      </c>
+      <c r="G193" t="s">
+        <v>271</v>
+      </c>
+      <c r="H193" t="s">
+        <v>381</v>
+      </c>
+      <c r="I193" t="s">
+        <v>402</v>
+      </c>
+      <c r="J193">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
+      <c r="A194">
+        <v>428</v>
+      </c>
+      <c r="B194" t="s">
+        <v>17</v>
+      </c>
+      <c r="C194" t="s">
+        <v>28</v>
+      </c>
+      <c r="D194" t="s">
+        <v>29</v>
+      </c>
+      <c r="E194" t="s">
+        <v>70</v>
+      </c>
+      <c r="F194" t="s">
+        <v>240</v>
+      </c>
+      <c r="G194" t="s">
+        <v>271</v>
+      </c>
+      <c r="H194" t="s">
+        <v>381</v>
+      </c>
+      <c r="I194" t="s">
+        <v>402</v>
+      </c>
+      <c r="J194">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10">
+      <c r="A195">
+        <v>431</v>
+      </c>
+      <c r="B195" t="s">
+        <v>17</v>
+      </c>
+      <c r="C195" t="s">
+        <v>28</v>
+      </c>
+      <c r="D195" t="s">
+        <v>29</v>
+      </c>
+      <c r="E195" t="s">
+        <v>70</v>
+      </c>
+      <c r="F195" t="s">
+        <v>241</v>
+      </c>
+      <c r="G195" t="s">
+        <v>271</v>
+      </c>
+      <c r="H195" t="s">
+        <v>381</v>
+      </c>
+      <c r="I195" t="s">
+        <v>402</v>
+      </c>
+      <c r="J195">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
+      <c r="A196">
+        <v>432</v>
+      </c>
+      <c r="B196" t="s">
+        <v>17</v>
+      </c>
+      <c r="C196" t="s">
+        <v>28</v>
+      </c>
+      <c r="D196" t="s">
+        <v>29</v>
+      </c>
+      <c r="E196" t="s">
+        <v>70</v>
+      </c>
+      <c r="F196" t="s">
+        <v>242</v>
+      </c>
+      <c r="G196" t="s">
+        <v>271</v>
+      </c>
+      <c r="H196" t="s">
+        <v>381</v>
+      </c>
+      <c r="I196" t="s">
+        <v>402</v>
+      </c>
+      <c r="J196">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
+      <c r="A197">
+        <v>506</v>
+      </c>
+      <c r="B197" t="s">
+        <v>18</v>
+      </c>
+      <c r="C197" t="s">
+        <v>28</v>
+      </c>
+      <c r="D197" t="s">
+        <v>29</v>
+      </c>
+      <c r="E197" t="s">
+        <v>70</v>
+      </c>
+      <c r="F197" t="s">
+        <v>243</v>
+      </c>
+      <c r="G197" t="s">
+        <v>271</v>
+      </c>
+      <c r="H197" t="s">
+        <v>382</v>
+      </c>
+      <c r="I197" t="s">
+        <v>402</v>
+      </c>
+      <c r="J197">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
+      <c r="A198">
+        <v>508</v>
+      </c>
+      <c r="B198" t="s">
+        <v>18</v>
+      </c>
+      <c r="C198" t="s">
+        <v>28</v>
+      </c>
+      <c r="D198" t="s">
+        <v>29</v>
+      </c>
+      <c r="E198" t="s">
+        <v>70</v>
+      </c>
+      <c r="F198" t="s">
+        <v>244</v>
+      </c>
+      <c r="G198" t="s">
+        <v>271</v>
+      </c>
+      <c r="H198" t="s">
+        <v>382</v>
+      </c>
+      <c r="I198" t="s">
+        <v>402</v>
+      </c>
+      <c r="J198">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10">
+      <c r="A199">
+        <v>72</v>
+      </c>
+      <c r="B199" t="s">
+        <v>10</v>
+      </c>
+      <c r="C199" t="s">
+        <v>28</v>
+      </c>
+      <c r="D199" t="s">
+        <v>29</v>
+      </c>
+      <c r="E199" t="s">
         <v>71</v>
       </c>
-      <c r="F191" t="s">
-        <v>219</v>
-      </c>
-      <c r="G191" t="s">
-        <v>240</v>
-      </c>
-      <c r="H191" t="s">
-        <v>342</v>
-      </c>
-      <c r="I191" t="s">
-        <v>354</v>
-      </c>
-      <c r="J191">
+      <c r="F199" t="s">
+        <v>245</v>
+      </c>
+      <c r="G199" t="s">
+        <v>271</v>
+      </c>
+      <c r="H199" t="s">
+        <v>383</v>
+      </c>
+      <c r="I199" t="s">
+        <v>403</v>
+      </c>
+      <c r="J199">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="200" spans="1:10">
+      <c r="A200">
+        <v>208</v>
+      </c>
+      <c r="B200" t="s">
+        <v>15</v>
+      </c>
+      <c r="C200" t="s">
+        <v>28</v>
+      </c>
+      <c r="D200" t="s">
+        <v>29</v>
+      </c>
+      <c r="E200" t="s">
+        <v>71</v>
+      </c>
+      <c r="F200" t="s">
+        <v>246</v>
+      </c>
+      <c r="G200" t="s">
+        <v>271</v>
+      </c>
+      <c r="H200" t="s">
+        <v>384</v>
+      </c>
+      <c r="I200" t="s">
+        <v>402</v>
+      </c>
+      <c r="J200">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10">
+      <c r="A201">
+        <v>209</v>
+      </c>
+      <c r="B201" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201" t="s">
+        <v>28</v>
+      </c>
+      <c r="D201" t="s">
+        <v>29</v>
+      </c>
+      <c r="E201" t="s">
+        <v>71</v>
+      </c>
+      <c r="F201" t="s">
+        <v>247</v>
+      </c>
+      <c r="G201" t="s">
+        <v>271</v>
+      </c>
+      <c r="H201" t="s">
+        <v>384</v>
+      </c>
+      <c r="I201" t="s">
+        <v>402</v>
+      </c>
+      <c r="J201">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10">
+      <c r="A202">
+        <v>210</v>
+      </c>
+      <c r="B202" t="s">
+        <v>15</v>
+      </c>
+      <c r="C202" t="s">
+        <v>28</v>
+      </c>
+      <c r="D202" t="s">
+        <v>29</v>
+      </c>
+      <c r="E202" t="s">
+        <v>71</v>
+      </c>
+      <c r="F202" t="s">
+        <v>248</v>
+      </c>
+      <c r="G202" t="s">
+        <v>271</v>
+      </c>
+      <c r="H202" t="s">
+        <v>384</v>
+      </c>
+      <c r="I202" t="s">
+        <v>402</v>
+      </c>
+      <c r="J202">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10">
+      <c r="A203">
+        <v>211</v>
+      </c>
+      <c r="B203" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203" t="s">
+        <v>28</v>
+      </c>
+      <c r="D203" t="s">
+        <v>29</v>
+      </c>
+      <c r="E203" t="s">
+        <v>71</v>
+      </c>
+      <c r="F203" t="s">
+        <v>249</v>
+      </c>
+      <c r="G203" t="s">
+        <v>271</v>
+      </c>
+      <c r="H203" t="s">
+        <v>384</v>
+      </c>
+      <c r="I203" t="s">
+        <v>402</v>
+      </c>
+      <c r="J203">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10">
+      <c r="A204">
+        <v>212</v>
+      </c>
+      <c r="B204" t="s">
+        <v>15</v>
+      </c>
+      <c r="C204" t="s">
+        <v>28</v>
+      </c>
+      <c r="D204" t="s">
+        <v>29</v>
+      </c>
+      <c r="E204" t="s">
+        <v>71</v>
+      </c>
+      <c r="F204" t="s">
+        <v>250</v>
+      </c>
+      <c r="G204" t="s">
+        <v>271</v>
+      </c>
+      <c r="H204" t="s">
+        <v>384</v>
+      </c>
+      <c r="I204" t="s">
+        <v>402</v>
+      </c>
+      <c r="J204">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10">
+      <c r="A205">
+        <v>509</v>
+      </c>
+      <c r="B205" t="s">
+        <v>18</v>
+      </c>
+      <c r="C205" t="s">
+        <v>28</v>
+      </c>
+      <c r="D205" t="s">
+        <v>29</v>
+      </c>
+      <c r="E205" t="s">
+        <v>71</v>
+      </c>
+      <c r="F205" t="s">
+        <v>251</v>
+      </c>
+      <c r="G205" t="s">
+        <v>271</v>
+      </c>
+      <c r="H205" t="s">
+        <v>385</v>
+      </c>
+      <c r="I205" t="s">
+        <v>402</v>
+      </c>
+      <c r="J205">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="206" spans="1:10">
+      <c r="A206">
+        <v>511</v>
+      </c>
+      <c r="B206" t="s">
+        <v>18</v>
+      </c>
+      <c r="C206" t="s">
+        <v>28</v>
+      </c>
+      <c r="D206" t="s">
+        <v>29</v>
+      </c>
+      <c r="E206" t="s">
+        <v>71</v>
+      </c>
+      <c r="F206" t="s">
+        <v>252</v>
+      </c>
+      <c r="G206" t="s">
+        <v>271</v>
+      </c>
+      <c r="H206" t="s">
+        <v>385</v>
+      </c>
+      <c r="I206" t="s">
+        <v>402</v>
+      </c>
+      <c r="J206">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10">
+      <c r="A207">
+        <v>512</v>
+      </c>
+      <c r="B207" t="s">
+        <v>18</v>
+      </c>
+      <c r="C207" t="s">
+        <v>28</v>
+      </c>
+      <c r="D207" t="s">
+        <v>29</v>
+      </c>
+      <c r="E207" t="s">
+        <v>71</v>
+      </c>
+      <c r="F207" t="s">
+        <v>253</v>
+      </c>
+      <c r="G207" t="s">
+        <v>271</v>
+      </c>
+      <c r="H207" t="s">
+        <v>385</v>
+      </c>
+      <c r="I207" t="s">
+        <v>402</v>
+      </c>
+      <c r="J207">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10">
+      <c r="A208">
+        <v>73</v>
+      </c>
+      <c r="B208" t="s">
+        <v>10</v>
+      </c>
+      <c r="C208" t="s">
+        <v>28</v>
+      </c>
+      <c r="D208" t="s">
+        <v>29</v>
+      </c>
+      <c r="E208" t="s">
+        <v>72</v>
+      </c>
+      <c r="F208" t="s">
+        <v>254</v>
+      </c>
+      <c r="G208" t="s">
+        <v>271</v>
+      </c>
+      <c r="H208" t="s">
+        <v>386</v>
+      </c>
+      <c r="I208" t="s">
+        <v>402</v>
+      </c>
+      <c r="J208">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10">
+      <c r="A209">
+        <v>273</v>
+      </c>
+      <c r="B209" t="s">
+        <v>14</v>
+      </c>
+      <c r="C209" t="s">
+        <v>28</v>
+      </c>
+      <c r="D209" t="s">
+        <v>29</v>
+      </c>
+      <c r="E209" t="s">
+        <v>72</v>
+      </c>
+      <c r="F209" t="s">
+        <v>255</v>
+      </c>
+      <c r="G209" t="s">
+        <v>271</v>
+      </c>
+      <c r="H209" t="s">
+        <v>387</v>
+      </c>
+      <c r="I209" t="s">
+        <v>402</v>
+      </c>
+      <c r="J209">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
+      <c r="A210">
+        <v>274</v>
+      </c>
+      <c r="B210" t="s">
+        <v>14</v>
+      </c>
+      <c r="C210" t="s">
+        <v>28</v>
+      </c>
+      <c r="D210" t="s">
+        <v>29</v>
+      </c>
+      <c r="E210" t="s">
+        <v>72</v>
+      </c>
+      <c r="F210" t="s">
+        <v>256</v>
+      </c>
+      <c r="G210" t="s">
+        <v>271</v>
+      </c>
+      <c r="H210" t="s">
+        <v>387</v>
+      </c>
+      <c r="I210" t="s">
+        <v>402</v>
+      </c>
+      <c r="J210">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10">
+      <c r="A211">
+        <v>275</v>
+      </c>
+      <c r="B211" t="s">
+        <v>14</v>
+      </c>
+      <c r="C211" t="s">
+        <v>28</v>
+      </c>
+      <c r="D211" t="s">
+        <v>29</v>
+      </c>
+      <c r="E211" t="s">
+        <v>72</v>
+      </c>
+      <c r="F211" t="s">
+        <v>257</v>
+      </c>
+      <c r="G211" t="s">
+        <v>271</v>
+      </c>
+      <c r="H211" t="s">
+        <v>387</v>
+      </c>
+      <c r="I211" t="s">
+        <v>402</v>
+      </c>
+      <c r="J211">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10">
+      <c r="A212">
+        <v>277</v>
+      </c>
+      <c r="B212" t="s">
+        <v>14</v>
+      </c>
+      <c r="C212" t="s">
+        <v>28</v>
+      </c>
+      <c r="D212" t="s">
+        <v>29</v>
+      </c>
+      <c r="E212" t="s">
+        <v>72</v>
+      </c>
+      <c r="F212" t="s">
+        <v>258</v>
+      </c>
+      <c r="G212" t="s">
+        <v>271</v>
+      </c>
+      <c r="H212" t="s">
+        <v>387</v>
+      </c>
+      <c r="I212" t="s">
+        <v>402</v>
+      </c>
+      <c r="J212">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10">
+      <c r="A213">
+        <v>278</v>
+      </c>
+      <c r="B213" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213" t="s">
+        <v>28</v>
+      </c>
+      <c r="D213" t="s">
+        <v>29</v>
+      </c>
+      <c r="E213" t="s">
+        <v>72</v>
+      </c>
+      <c r="F213" t="s">
+        <v>259</v>
+      </c>
+      <c r="G213" t="s">
+        <v>271</v>
+      </c>
+      <c r="H213" t="s">
+        <v>387</v>
+      </c>
+      <c r="I213" t="s">
+        <v>402</v>
+      </c>
+      <c r="J213">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="A214">
+        <v>280</v>
+      </c>
+      <c r="B214" t="s">
+        <v>14</v>
+      </c>
+      <c r="C214" t="s">
+        <v>28</v>
+      </c>
+      <c r="D214" t="s">
+        <v>29</v>
+      </c>
+      <c r="E214" t="s">
+        <v>72</v>
+      </c>
+      <c r="F214" t="s">
+        <v>260</v>
+      </c>
+      <c r="G214" t="s">
+        <v>271</v>
+      </c>
+      <c r="H214" t="s">
+        <v>387</v>
+      </c>
+      <c r="I214" t="s">
+        <v>402</v>
+      </c>
+      <c r="J214">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10">
+      <c r="A215">
+        <v>281</v>
+      </c>
+      <c r="B215" t="s">
+        <v>14</v>
+      </c>
+      <c r="C215" t="s">
+        <v>28</v>
+      </c>
+      <c r="D215" t="s">
+        <v>29</v>
+      </c>
+      <c r="E215" t="s">
+        <v>72</v>
+      </c>
+      <c r="F215" t="s">
+        <v>261</v>
+      </c>
+      <c r="G215" t="s">
+        <v>271</v>
+      </c>
+      <c r="H215" t="s">
+        <v>387</v>
+      </c>
+      <c r="I215" t="s">
+        <v>402</v>
+      </c>
+      <c r="J215">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
+      <c r="A216">
+        <v>74</v>
+      </c>
+      <c r="B216" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216" t="s">
+        <v>28</v>
+      </c>
+      <c r="D216" t="s">
+        <v>29</v>
+      </c>
+      <c r="E216" t="s">
+        <v>73</v>
+      </c>
+      <c r="F216" t="s">
+        <v>262</v>
+      </c>
+      <c r="G216" t="s">
+        <v>271</v>
+      </c>
+      <c r="H216" t="s">
+        <v>388</v>
+      </c>
+      <c r="I216" t="s">
+        <v>402</v>
+      </c>
+      <c r="J216">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="A217">
+        <v>107</v>
+      </c>
+      <c r="B217" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" t="s">
+        <v>28</v>
+      </c>
+      <c r="D217" t="s">
+        <v>29</v>
+      </c>
+      <c r="E217" t="s">
+        <v>73</v>
+      </c>
+      <c r="F217" t="s">
+        <v>263</v>
+      </c>
+      <c r="G217" t="s">
+        <v>271</v>
+      </c>
+      <c r="H217" t="s">
+        <v>388</v>
+      </c>
+      <c r="I217" t="s">
+        <v>403</v>
+      </c>
+      <c r="J217">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10">
+      <c r="A218">
+        <v>138</v>
+      </c>
+      <c r="B218" t="s">
+        <v>12</v>
+      </c>
+      <c r="C218" t="s">
+        <v>28</v>
+      </c>
+      <c r="D218" t="s">
+        <v>29</v>
+      </c>
+      <c r="E218" t="s">
+        <v>73</v>
+      </c>
+      <c r="F218" t="s">
+        <v>264</v>
+      </c>
+      <c r="G218" t="s">
+        <v>271</v>
+      </c>
+      <c r="H218" t="s">
+        <v>389</v>
+      </c>
+      <c r="I218" t="s">
+        <v>402</v>
+      </c>
+      <c r="J218">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10">
+      <c r="A219">
+        <v>139</v>
+      </c>
+      <c r="B219" t="s">
+        <v>12</v>
+      </c>
+      <c r="C219" t="s">
+        <v>28</v>
+      </c>
+      <c r="D219" t="s">
+        <v>29</v>
+      </c>
+      <c r="E219" t="s">
+        <v>73</v>
+      </c>
+      <c r="F219" t="s">
+        <v>265</v>
+      </c>
+      <c r="G219" t="s">
+        <v>271</v>
+      </c>
+      <c r="H219" t="s">
+        <v>389</v>
+      </c>
+      <c r="I219" t="s">
+        <v>402</v>
+      </c>
+      <c r="J219">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10">
+      <c r="A220">
+        <v>421</v>
+      </c>
+      <c r="B220" t="s">
+        <v>17</v>
+      </c>
+      <c r="C220" t="s">
+        <v>28</v>
+      </c>
+      <c r="D220" t="s">
+        <v>29</v>
+      </c>
+      <c r="E220" t="s">
+        <v>73</v>
+      </c>
+      <c r="F220" t="s">
+        <v>266</v>
+      </c>
+      <c r="G220" t="s">
+        <v>271</v>
+      </c>
+      <c r="H220" t="s">
+        <v>390</v>
+      </c>
+      <c r="I220" t="s">
+        <v>402</v>
+      </c>
+      <c r="J220">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10">
+      <c r="A221">
+        <v>422</v>
+      </c>
+      <c r="B221" t="s">
+        <v>17</v>
+      </c>
+      <c r="C221" t="s">
+        <v>28</v>
+      </c>
+      <c r="D221" t="s">
+        <v>29</v>
+      </c>
+      <c r="E221" t="s">
+        <v>73</v>
+      </c>
+      <c r="F221" t="s">
+        <v>267</v>
+      </c>
+      <c r="G221" t="s">
+        <v>271</v>
+      </c>
+      <c r="H221" t="s">
+        <v>390</v>
+      </c>
+      <c r="I221" t="s">
+        <v>402</v>
+      </c>
+      <c r="J221">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
+      <c r="A222">
+        <v>423</v>
+      </c>
+      <c r="B222" t="s">
+        <v>17</v>
+      </c>
+      <c r="C222" t="s">
+        <v>28</v>
+      </c>
+      <c r="D222" t="s">
+        <v>29</v>
+      </c>
+      <c r="E222" t="s">
+        <v>73</v>
+      </c>
+      <c r="F222" t="s">
+        <v>268</v>
+      </c>
+      <c r="G222" t="s">
+        <v>271</v>
+      </c>
+      <c r="H222" t="s">
+        <v>390</v>
+      </c>
+      <c r="I222" t="s">
+        <v>402</v>
+      </c>
+      <c r="J222">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
+      <c r="A223">
+        <v>424</v>
+      </c>
+      <c r="B223" t="s">
+        <v>17</v>
+      </c>
+      <c r="C223" t="s">
+        <v>28</v>
+      </c>
+      <c r="D223" t="s">
+        <v>29</v>
+      </c>
+      <c r="E223" t="s">
+        <v>73</v>
+      </c>
+      <c r="F223" t="s">
+        <v>269</v>
+      </c>
+      <c r="G223" t="s">
+        <v>271</v>
+      </c>
+      <c r="H223" t="s">
+        <v>390</v>
+      </c>
+      <c r="I223" t="s">
+        <v>402</v>
+      </c>
+      <c r="J223">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
+      <c r="A224">
+        <v>460</v>
+      </c>
+      <c r="B224" t="s">
+        <v>18</v>
+      </c>
+      <c r="C224" t="s">
+        <v>28</v>
+      </c>
+      <c r="D224" t="s">
+        <v>29</v>
+      </c>
+      <c r="E224" t="s">
+        <v>73</v>
+      </c>
+      <c r="F224" t="s">
+        <v>270</v>
+      </c>
+      <c r="G224" t="s">
+        <v>271</v>
+      </c>
+      <c r="H224" t="s">
+        <v>389</v>
+      </c>
+      <c r="I224" t="s">
+        <v>402</v>
+      </c>
+      <c r="J224">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10">
+      <c r="A225">
+        <v>461</v>
+      </c>
+      <c r="B225" t="s">
+        <v>18</v>
+      </c>
+      <c r="C225" t="s">
+        <v>28</v>
+      </c>
+      <c r="D225" t="s">
+        <v>29</v>
+      </c>
+      <c r="E225" t="s">
+        <v>73</v>
+      </c>
+      <c r="F225" t="s">
+        <v>247</v>
+      </c>
+      <c r="G225" t="s">
+        <v>271</v>
+      </c>
+      <c r="H225" t="s">
+        <v>389</v>
+      </c>
+      <c r="I225" t="s">
+        <v>402</v>
+      </c>
+      <c r="J225">
         <v>104</v>
       </c>
     </row>

--- a/VHTs_and_Community_Demos_Extract.xlsx
+++ b/VHTs_and_Community_Demos_Extract.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="433">
   <si>
     <t>Entry Index</t>
   </si>
@@ -172,6 +172,9 @@
     <t>KOTIDO GIRLS P/S</t>
   </si>
   <si>
+    <t>LOKIDING P/S</t>
+  </si>
+  <si>
     <t>LOOKOROK P/S</t>
   </si>
   <si>
@@ -343,6 +346,12 @@
     <t>Kathile west cell</t>
   </si>
   <si>
+    <t>Nasuguru cell</t>
+  </si>
+  <si>
+    <t>Lopelipel cell</t>
+  </si>
+  <si>
     <t>KAILOB</t>
   </si>
   <si>
@@ -466,6 +475,9 @@
     <t>Lokiding trading centre</t>
   </si>
   <si>
+    <t>Lokiding 2</t>
+  </si>
+  <si>
     <t>Kawich</t>
   </si>
   <si>
@@ -547,6 +559,9 @@
     <t>kambisi</t>
   </si>
   <si>
+    <t>Kambisi</t>
+  </si>
+  <si>
     <t>Lokwakwa village</t>
   </si>
   <si>
@@ -649,6 +664,18 @@
     <t>Lemusui subcounty offices</t>
   </si>
   <si>
+    <t>Gogoth village</t>
+  </si>
+  <si>
+    <t>Alapat village</t>
+  </si>
+  <si>
+    <t>Morwakimat village</t>
+  </si>
+  <si>
+    <t>Katabok village</t>
+  </si>
+  <si>
     <t>Lokaale village trees</t>
   </si>
   <si>
@@ -661,9 +688,24 @@
     <t>Loowoi village</t>
   </si>
   <si>
+    <t>Center where they sell local bear</t>
+  </si>
+  <si>
     <t>Loreng village community trees</t>
   </si>
   <si>
+    <t>Lokibuyo village</t>
+  </si>
+  <si>
+    <t>Market area of lokibuyo village</t>
+  </si>
+  <si>
+    <t>Lobooloin village</t>
+  </si>
+  <si>
+    <t>Awoyareng village trees</t>
+  </si>
+  <si>
     <t>Nakuri village. In the saving group</t>
   </si>
   <si>
@@ -679,6 +721,9 @@
     <t>Kakomokwe village</t>
   </si>
   <si>
+    <t>Nakuri natapar farmers saving group</t>
+  </si>
+  <si>
     <t>Health center iv</t>
   </si>
   <si>
@@ -691,6 +736,9 @@
     <t>Alakara church ministries namalu</t>
   </si>
   <si>
+    <t>Heath center iv antinental day</t>
+  </si>
+  <si>
     <t>Lopiida market</t>
   </si>
   <si>
@@ -778,6 +826,9 @@
     <t>Logolei</t>
   </si>
   <si>
+    <t>Kololo</t>
+  </si>
+  <si>
     <t>Lepeei</t>
   </si>
   <si>
@@ -829,6 +880,18 @@
     <t>Lolet</t>
   </si>
   <si>
+    <t>Kamwhili</t>
+  </si>
+  <si>
+    <t>Katanga</t>
+  </si>
+  <si>
+    <t>Lopiida</t>
+  </si>
+  <si>
+    <t>Kopokwa</t>
+  </si>
+  <si>
     <t>VHT</t>
   </si>
   <si>
@@ -985,6 +1048,9 @@
     <t>Oluka Emmanuel</t>
   </si>
   <si>
+    <t>Achuun Lucy Brenda and Aermun Lowas</t>
+  </si>
+  <si>
     <t>Adong lilly grace</t>
   </si>
   <si>
@@ -1018,6 +1084,9 @@
     <t>Mary Goretti</t>
   </si>
   <si>
+    <t>Lomonyang Moses</t>
+  </si>
+  <si>
     <t>Cecellia</t>
   </si>
   <si>
@@ -1120,6 +1189,12 @@
     <t>Cheptoo Evaline and cherotich Catherine</t>
   </si>
   <si>
+    <t>Cheptoo Evaline, cherotich catherine and loreng musa</t>
+  </si>
+  <si>
+    <t>Cheptoo evaline, cherotich catherine and loreng musa</t>
+  </si>
+  <si>
     <t>Angella Joseph and iriama simon peter</t>
   </si>
   <si>
@@ -1132,9 +1207,18 @@
     <t>Iriama Allan stephen and Keke Lucy</t>
   </si>
   <si>
+    <t>Iriama allan Stephen and keke lucy</t>
+  </si>
+  <si>
+    <t>Iriama allan stephen and keke lucy</t>
+  </si>
+  <si>
     <t>Aleper pius and Nakiru luja</t>
   </si>
   <si>
+    <t>Aleper pius, Nakiru luja</t>
+  </si>
+  <si>
     <t>Nakalei Hellen</t>
   </si>
   <si>
@@ -1145,6 +1229,9 @@
   </si>
   <si>
     <t>Nakalei Hellen, and Adyaka james</t>
+  </si>
+  <si>
+    <t>Nakalei Hellen, Adyaka James</t>
   </si>
   <si>
     <t>Joseph</t>
@@ -1583,7 +1670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J225"/>
+  <dimension ref="A1:J246"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1635,16 +1722,16 @@
         <v>30</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H2" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="I2" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="J2">
         <v>152</v>
@@ -1667,16 +1754,16 @@
         <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H3" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="I3" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="J3">
         <v>176</v>
@@ -1699,16 +1786,16 @@
         <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H4" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="I4" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="J4">
         <v>168</v>
@@ -1731,16 +1818,16 @@
         <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H5" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="I5" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="J5">
         <v>238</v>
@@ -1763,16 +1850,16 @@
         <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H6" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="I6" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="J6">
         <v>222</v>
@@ -1795,16 +1882,16 @@
         <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H7" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="I7" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="J7">
         <v>142</v>
@@ -1827,16 +1914,16 @@
         <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H8" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I8" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J8">
         <v>83</v>
@@ -1859,16 +1946,16 @@
         <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G9" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H9" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I9" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J9">
         <v>91</v>
@@ -1891,16 +1978,16 @@
         <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G10" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H10" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I10" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J10">
         <v>123</v>
@@ -1923,16 +2010,16 @@
         <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G11" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H11" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="I11" t="s">
-        <v>393</v>
+        <v>422</v>
       </c>
       <c r="J11">
         <v>88</v>
@@ -1955,16 +2042,16 @@
         <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H12" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I12" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J12">
         <v>235</v>
@@ -1987,16 +2074,16 @@
         <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H13" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="I13" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J13">
         <v>136</v>
@@ -2019,16 +2106,16 @@
         <v>36</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H14" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="I14" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J14">
         <v>154</v>
@@ -2051,16 +2138,16 @@
         <v>36</v>
       </c>
       <c r="F15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H15" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="I15" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J15">
         <v>161</v>
@@ -2083,16 +2170,16 @@
         <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H16" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="I16" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J16">
         <v>185</v>
@@ -2115,16 +2202,16 @@
         <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H17" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="I17" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J17">
         <v>146</v>
@@ -2147,16 +2234,16 @@
         <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H18" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="I18" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J18">
         <v>174</v>
@@ -2179,16 +2266,16 @@
         <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H19" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="I19" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J19">
         <v>133</v>
@@ -2211,16 +2298,16 @@
         <v>37</v>
       </c>
       <c r="F20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H20" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="I20" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J20">
         <v>126</v>
@@ -2243,16 +2330,16 @@
         <v>37</v>
       </c>
       <c r="F21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H21" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="I21" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J21">
         <v>131</v>
@@ -2275,16 +2362,16 @@
         <v>37</v>
       </c>
       <c r="F22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G22" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H22" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="I22" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J22">
         <v>151</v>
@@ -2307,16 +2394,16 @@
         <v>37</v>
       </c>
       <c r="F23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G23" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H23" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="I23" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J23">
         <v>144</v>
@@ -2339,16 +2426,16 @@
         <v>37</v>
       </c>
       <c r="F24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H24" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="I24" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J24">
         <v>158</v>
@@ -2371,16 +2458,16 @@
         <v>37</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G25" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H25" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="I25" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J25">
         <v>128</v>
@@ -2403,16 +2490,16 @@
         <v>37</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G26" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H26" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="I26" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J26">
         <v>176</v>
@@ -2435,16 +2522,16 @@
         <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H27" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="I27" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J27">
         <v>141</v>
@@ -2467,16 +2554,16 @@
         <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H28" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="I28" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J28">
         <v>124</v>
@@ -2499,16 +2586,16 @@
         <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G29" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H29" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="I29" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J29">
         <v>158</v>
@@ -2531,16 +2618,16 @@
         <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H30" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="I30" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J30">
         <v>142</v>
@@ -2563,16 +2650,16 @@
         <v>39</v>
       </c>
       <c r="F31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G31" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H31" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="I31" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J31">
         <v>146</v>
@@ -2595,16 +2682,16 @@
         <v>39</v>
       </c>
       <c r="F32" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G32" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H32" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I32" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J32">
         <v>173</v>
@@ -2627,16 +2714,16 @@
         <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G33" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H33" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="I33" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J33">
         <v>135</v>
@@ -2659,16 +2746,16 @@
         <v>39</v>
       </c>
       <c r="F34" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G34" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H34" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I34" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J34">
         <v>154</v>
@@ -2691,16 +2778,16 @@
         <v>39</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G35" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H35" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I35" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J35">
         <v>168</v>
@@ -2723,16 +2810,16 @@
         <v>39</v>
       </c>
       <c r="F36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G36" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H36" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I36" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J36">
         <v>161</v>
@@ -2755,16 +2842,16 @@
         <v>39</v>
       </c>
       <c r="F37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G37" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H37" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I37" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J37">
         <v>176</v>
@@ -2787,16 +2874,16 @@
         <v>39</v>
       </c>
       <c r="F38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G38" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H38" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I38" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J38">
         <v>132</v>
@@ -2819,16 +2906,16 @@
         <v>39</v>
       </c>
       <c r="F39" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G39" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H39" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I39" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="J39">
         <v>223</v>
@@ -2851,16 +2938,16 @@
         <v>40</v>
       </c>
       <c r="F40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G40" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H40" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="I40" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J40">
         <v>60</v>
@@ -2883,16 +2970,16 @@
         <v>40</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G41" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H41" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="I41" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J41">
         <v>82</v>
@@ -2915,16 +3002,16 @@
         <v>40</v>
       </c>
       <c r="F42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G42" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H42" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="I42" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J42">
         <v>71</v>
@@ -2947,16 +3034,16 @@
         <v>40</v>
       </c>
       <c r="F43" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G43" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H43" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="I43" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J43">
         <v>50</v>
@@ -2979,16 +3066,16 @@
         <v>40</v>
       </c>
       <c r="F44" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G44" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H44" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="I44" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J44">
         <v>86</v>
@@ -3011,16 +3098,16 @@
         <v>40</v>
       </c>
       <c r="F45" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G45" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H45" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="I45" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J45">
         <v>79</v>
@@ -3043,16 +3130,16 @@
         <v>40</v>
       </c>
       <c r="F46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G46" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H46" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="I46" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J46">
         <v>90</v>
@@ -3075,16 +3162,16 @@
         <v>40</v>
       </c>
       <c r="F47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G47" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H47" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="I47" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J47">
         <v>48</v>
@@ -3107,16 +3194,16 @@
         <v>40</v>
       </c>
       <c r="F48" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G48" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H48" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="I48" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J48">
         <v>83</v>
@@ -3139,16 +3226,16 @@
         <v>40</v>
       </c>
       <c r="F49" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G49" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H49" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="I49" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J49">
         <v>79</v>
@@ -3171,16 +3258,16 @@
         <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G50" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H50" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="I50" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J50">
         <v>89</v>
@@ -3203,16 +3290,16 @@
         <v>42</v>
       </c>
       <c r="F51" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G51" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H51" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="I51" t="s">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="J51">
         <v>80</v>
@@ -3235,16 +3322,16 @@
         <v>42</v>
       </c>
       <c r="F52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G52" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H52" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="I52" t="s">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="J52">
         <v>74</v>
@@ -3267,16 +3354,16 @@
         <v>42</v>
       </c>
       <c r="F53" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G53" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H53" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="I53" t="s">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="J53">
         <v>75</v>
@@ -3284,10 +3371,10 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54">
-        <v>433</v>
+        <v>521</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C54" t="s">
         <v>22</v>
@@ -3296,30 +3383,30 @@
         <v>29</v>
       </c>
       <c r="E54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F54" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G54" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H54" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="I54" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="J54">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55">
-        <v>434</v>
+        <v>530</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C55" t="s">
         <v>22</v>
@@ -3328,30 +3415,30 @@
         <v>29</v>
       </c>
       <c r="E55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F55" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G55" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H55" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="I55" t="s">
-        <v>395</v>
+        <v>425</v>
       </c>
       <c r="J55">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56">
-        <v>319</v>
+        <v>433</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C56" t="s">
         <v>22</v>
@@ -3360,30 +3447,30 @@
         <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F56" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G56" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H56" t="s">
-        <v>278</v>
+        <v>324</v>
       </c>
       <c r="I56" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J56">
-        <v>113</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57">
-        <v>321</v>
+        <v>434</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
         <v>22</v>
@@ -3392,27 +3479,27 @@
         <v>29</v>
       </c>
       <c r="E57" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F57" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G57" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H57" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="I57" t="s">
-        <v>395</v>
+        <v>424</v>
       </c>
       <c r="J57">
-        <v>107</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -3427,88 +3514,88 @@
         <v>44</v>
       </c>
       <c r="F58" t="s">
+        <v>114</v>
+      </c>
+      <c r="G58" t="s">
+        <v>293</v>
+      </c>
+      <c r="H58" t="s">
+        <v>299</v>
+      </c>
+      <c r="I58" t="s">
+        <v>424</v>
+      </c>
+      <c r="J58">
         <v>113</v>
-      </c>
-      <c r="G58" t="s">
-        <v>271</v>
-      </c>
-      <c r="H58" t="s">
-        <v>306</v>
-      </c>
-      <c r="I58" t="s">
-        <v>395</v>
-      </c>
-      <c r="J58">
-        <v>117</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59">
-        <v>82</v>
+        <v>321</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
         <v>29</v>
       </c>
       <c r="E59" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F59" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G59" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H59" t="s">
-        <v>278</v>
+        <v>326</v>
       </c>
       <c r="I59" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="J59">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D60" t="s">
         <v>29</v>
       </c>
       <c r="E60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F60" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G60" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H60" t="s">
-        <v>278</v>
+        <v>327</v>
       </c>
       <c r="I60" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="J60">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s">
         <v>11</v>
@@ -3523,27 +3610,27 @@
         <v>45</v>
       </c>
       <c r="F61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G61" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H61" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="I61" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J61">
-        <v>107</v>
+        <v>93</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62">
-        <v>334</v>
+        <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C62" t="s">
         <v>23</v>
@@ -3555,27 +3642,27 @@
         <v>45</v>
       </c>
       <c r="F62" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G62" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H62" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I62" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J62">
-        <v>118</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C63" t="s">
         <v>23</v>
@@ -3587,24 +3674,24 @@
         <v>45</v>
       </c>
       <c r="F63" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G63" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H63" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="I63" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J63">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -3619,24 +3706,24 @@
         <v>45</v>
       </c>
       <c r="F64" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G64" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H64" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="I64" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J64">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -3651,27 +3738,27 @@
         <v>45</v>
       </c>
       <c r="F65" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G65" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H65" t="s">
-        <v>278</v>
+        <v>329</v>
       </c>
       <c r="I65" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J65">
-        <v>226</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66">
-        <v>85</v>
+        <v>337</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C66" t="s">
         <v>23</v>
@@ -3680,30 +3767,30 @@
         <v>29</v>
       </c>
       <c r="E66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F66" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G66" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H66" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="I66" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J66">
-        <v>162</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67">
-        <v>86</v>
+        <v>339</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C67" t="s">
         <v>23</v>
@@ -3712,27 +3799,27 @@
         <v>29</v>
       </c>
       <c r="E67" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F67" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G67" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H67" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="I67" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J67">
-        <v>143</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
         <v>11</v>
@@ -3747,27 +3834,27 @@
         <v>46</v>
       </c>
       <c r="F68" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G68" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H68" t="s">
-        <v>278</v>
+        <v>329</v>
       </c>
       <c r="I68" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J68">
-        <v>132</v>
+        <v>162</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69">
-        <v>340</v>
+        <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C69" t="s">
         <v>23</v>
@@ -3779,27 +3866,27 @@
         <v>46</v>
       </c>
       <c r="F69" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G69" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H69" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="I69" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J69">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70">
-        <v>342</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
         <v>23</v>
@@ -3811,24 +3898,24 @@
         <v>46</v>
       </c>
       <c r="F70" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G70" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H70" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="I70" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J70">
-        <v>97</v>
+        <v>132</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -3843,24 +3930,24 @@
         <v>46</v>
       </c>
       <c r="F71" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G71" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H71" t="s">
-        <v>278</v>
+        <v>331</v>
       </c>
       <c r="I71" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J71">
-        <v>244</v>
+        <v>136</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -3875,27 +3962,27 @@
         <v>46</v>
       </c>
       <c r="F72" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G72" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H72" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="I72" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J72">
-        <v>132</v>
+        <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73">
-        <v>94</v>
+        <v>343</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
         <v>23</v>
@@ -3904,30 +3991,30 @@
         <v>29</v>
       </c>
       <c r="E73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F73" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G73" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H73" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="I73" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J73">
-        <v>429</v>
+        <v>244</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74">
-        <v>96</v>
+        <v>346</v>
       </c>
       <c r="B74" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
         <v>23</v>
@@ -3936,30 +4023,30 @@
         <v>29</v>
       </c>
       <c r="E74" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F74" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G74" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H74" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="I74" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J74">
-        <v>478</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C75" t="s">
         <v>23</v>
@@ -3971,27 +4058,27 @@
         <v>47</v>
       </c>
       <c r="F75" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G75" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H75" t="s">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="I75" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J75">
-        <v>517</v>
+        <v>429</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76">
-        <v>317</v>
+        <v>96</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C76" t="s">
         <v>23</v>
@@ -4003,27 +4090,27 @@
         <v>47</v>
       </c>
       <c r="F76" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G76" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H76" t="s">
-        <v>278</v>
+        <v>334</v>
       </c>
       <c r="I76" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J76">
-        <v>148</v>
+        <v>478</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77">
-        <v>318</v>
+        <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C77" t="s">
         <v>23</v>
@@ -4035,24 +4122,24 @@
         <v>47</v>
       </c>
       <c r="F77" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G77" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H77" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I77" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J77">
-        <v>109</v>
+        <v>517</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -4067,24 +4154,24 @@
         <v>47</v>
       </c>
       <c r="F78" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G78" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H78" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="I78" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J78">
-        <v>90</v>
+        <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -4099,24 +4186,24 @@
         <v>47</v>
       </c>
       <c r="F79" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G79" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H79" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="I79" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J79">
-        <v>136</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -4131,24 +4218,24 @@
         <v>47</v>
       </c>
       <c r="F80" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G80" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H80" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="I80" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J80">
-        <v>119</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -4163,27 +4250,27 @@
         <v>47</v>
       </c>
       <c r="F81" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G81" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H81" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="I81" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J81">
-        <v>59</v>
+        <v>136</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82">
-        <v>401</v>
+        <v>325</v>
       </c>
       <c r="B82" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C82" t="s">
         <v>23</v>
@@ -4192,30 +4279,30 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F82" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G82" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H82" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="I82" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J82">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83">
-        <v>406</v>
+        <v>326</v>
       </c>
       <c r="B83" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C83" t="s">
         <v>23</v>
@@ -4224,27 +4311,27 @@
         <v>29</v>
       </c>
       <c r="E83" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F83" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G83" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H83" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="I83" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J83">
-        <v>88</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B84" t="s">
         <v>19</v>
@@ -4259,24 +4346,24 @@
         <v>48</v>
       </c>
       <c r="F84" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G84" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H84" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="I84" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J84">
-        <v>99</v>
+        <v>134</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B85" t="s">
         <v>19</v>
@@ -4291,24 +4378,24 @@
         <v>48</v>
       </c>
       <c r="F85" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G85" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H85" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="I85" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J85">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B86" t="s">
         <v>19</v>
@@ -4323,24 +4410,24 @@
         <v>48</v>
       </c>
       <c r="F86" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G86" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H86" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="I86" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J86">
-        <v>77</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B87" t="s">
         <v>19</v>
@@ -4355,24 +4442,24 @@
         <v>48</v>
       </c>
       <c r="F87" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G87" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H87" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="I87" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J87">
-        <v>72</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B88" t="s">
         <v>19</v>
@@ -4387,27 +4474,27 @@
         <v>48</v>
       </c>
       <c r="F88" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G88" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H88" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="I88" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J88">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89">
-        <v>90</v>
+        <v>411</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C89" t="s">
         <v>23</v>
@@ -4416,30 +4503,30 @@
         <v>29</v>
       </c>
       <c r="E89" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F89" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G89" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H89" t="s">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="I89" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J89">
-        <v>369</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90">
-        <v>91</v>
+        <v>412</v>
       </c>
       <c r="B90" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C90" t="s">
         <v>23</v>
@@ -4448,27 +4535,27 @@
         <v>29</v>
       </c>
       <c r="E90" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F90" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G90" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H90" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="I90" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J90">
-        <v>504</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B91" t="s">
         <v>11</v>
@@ -4483,27 +4570,27 @@
         <v>49</v>
       </c>
       <c r="F91" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G91" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H91" t="s">
-        <v>320</v>
+        <v>339</v>
       </c>
       <c r="I91" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J91">
-        <v>443</v>
+        <v>369</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92">
-        <v>313</v>
+        <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C92" t="s">
         <v>23</v>
@@ -4515,27 +4602,27 @@
         <v>49</v>
       </c>
       <c r="F92" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G92" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H92" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="I92" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J92">
-        <v>347</v>
+        <v>504</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93">
-        <v>314</v>
+        <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C93" t="s">
         <v>23</v>
@@ -4547,24 +4634,24 @@
         <v>49</v>
       </c>
       <c r="F93" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G93" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H93" t="s">
-        <v>278</v>
+        <v>341</v>
       </c>
       <c r="I93" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J93">
-        <v>290</v>
+        <v>443</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -4579,24 +4666,24 @@
         <v>49</v>
       </c>
       <c r="F94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G94" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H94" t="s">
-        <v>278</v>
+        <v>340</v>
       </c>
       <c r="I94" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J94">
-        <v>292</v>
+        <v>347</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -4611,91 +4698,91 @@
         <v>49</v>
       </c>
       <c r="F95" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G95" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="H95" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="I95" t="s">
-        <v>397</v>
+        <v>426</v>
       </c>
       <c r="J95">
-        <v>136</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96">
-        <v>352</v>
+        <v>315</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
       </c>
       <c r="C96" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D96" t="s">
         <v>29</v>
       </c>
       <c r="E96" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F96" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G96" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H96" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="I96" t="s">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="J96">
-        <v>216</v>
+        <v>292</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="A97">
-        <v>353</v>
+        <v>316</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C97" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D97" t="s">
         <v>29</v>
       </c>
       <c r="E97" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F97" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G97" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H97" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="I97" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="J97">
-        <v>306</v>
+        <v>136</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="A98">
-        <v>258</v>
+        <v>352</v>
       </c>
       <c r="B98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
         <v>24</v>
@@ -4704,27 +4791,27 @@
         <v>29</v>
       </c>
       <c r="E98" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F98" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G98" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H98" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="I98" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J98">
-        <v>313</v>
+        <v>216</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="A99">
-        <v>259</v>
+        <v>353</v>
       </c>
       <c r="B99" t="s">
         <v>14</v>
@@ -4736,30 +4823,30 @@
         <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G99" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H99" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="I99" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="J99">
-        <v>298</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="A100">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="B100" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C100" t="s">
         <v>24</v>
@@ -4771,27 +4858,27 @@
         <v>52</v>
       </c>
       <c r="F100" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G100" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H100" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="I100" t="s">
-        <v>398</v>
+        <v>428</v>
       </c>
       <c r="J100">
-        <v>183</v>
+        <v>221</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="A101">
-        <v>498</v>
+        <v>258</v>
       </c>
       <c r="B101" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C101" t="s">
         <v>24</v>
@@ -4800,30 +4887,30 @@
         <v>29</v>
       </c>
       <c r="E101" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F101" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G101" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H101" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="I101" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J101">
-        <v>167</v>
+        <v>313</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="A102">
-        <v>499</v>
+        <v>259</v>
       </c>
       <c r="B102" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C102" t="s">
         <v>24</v>
@@ -4832,27 +4919,27 @@
         <v>29</v>
       </c>
       <c r="E102" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F102" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G102" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H102" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="I102" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J102">
-        <v>155</v>
+        <v>298</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="A103">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B103" t="s">
         <v>14</v>
@@ -4864,30 +4951,30 @@
         <v>29</v>
       </c>
       <c r="E103" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F103" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G103" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H103" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="I103" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J103">
-        <v>142</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="A104">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B104" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C104" t="s">
         <v>24</v>
@@ -4896,30 +4983,30 @@
         <v>29</v>
       </c>
       <c r="E104" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F104" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G104" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H104" t="s">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="I104" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J104">
-        <v>126</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="A105">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -4928,30 +5015,30 @@
         <v>29</v>
       </c>
       <c r="E105" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F105" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G105" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H105" t="s">
-        <v>326</v>
+        <v>346</v>
       </c>
       <c r="I105" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J105">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="A106">
-        <v>437</v>
+        <v>500</v>
       </c>
       <c r="B106" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C106" t="s">
         <v>24</v>
@@ -4963,27 +5050,27 @@
         <v>53</v>
       </c>
       <c r="F106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G106" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H106" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="I106" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J106">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="A107">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="B107" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C107" t="s">
         <v>24</v>
@@ -4995,27 +5082,27 @@
         <v>53</v>
       </c>
       <c r="F107" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G107" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H107" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
       <c r="I107" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J107">
-        <v>166</v>
+        <v>126</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="A108">
-        <v>476</v>
+        <v>505</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C108" t="s">
         <v>24</v>
@@ -5027,27 +5114,27 @@
         <v>53</v>
       </c>
       <c r="F108" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G108" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H108" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="I108" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J108">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="A109">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="B109" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C109" t="s">
         <v>24</v>
@@ -5056,27 +5143,27 @@
         <v>29</v>
       </c>
       <c r="E109" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F109" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G109" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H109" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="I109" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J109">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="A110">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
@@ -5088,27 +5175,27 @@
         <v>29</v>
       </c>
       <c r="E110" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F110" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G110" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H110" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="I110" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J110">
-        <v>191</v>
+        <v>166</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="A111">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="B111" t="s">
         <v>18</v>
@@ -5120,27 +5207,27 @@
         <v>29</v>
       </c>
       <c r="E111" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F111" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G111" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H111" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="I111" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J111">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="112" spans="1:10">
       <c r="A112">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B112" t="s">
         <v>19</v>
@@ -5152,27 +5239,27 @@
         <v>29</v>
       </c>
       <c r="E112" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F112" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G112" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H112" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="I112" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J112">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="113" spans="1:10">
       <c r="A113">
-        <v>488</v>
+        <v>481</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
@@ -5184,27 +5271,27 @@
         <v>29</v>
       </c>
       <c r="E113" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F113" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G113" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H113" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="I113" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J113">
-        <v>167</v>
+        <v>191</v>
       </c>
     </row>
     <row r="114" spans="1:10">
       <c r="A114">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B114" t="s">
         <v>18</v>
@@ -5216,33 +5303,33 @@
         <v>29</v>
       </c>
       <c r="E114" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F114" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G114" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H114" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="I114" t="s">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="J114">
-        <v>107</v>
+        <v>137</v>
       </c>
     </row>
     <row r="115" spans="1:10">
       <c r="A115">
-        <v>162</v>
+        <v>484</v>
       </c>
       <c r="B115" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C115" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D115" t="s">
         <v>29</v>
@@ -5251,30 +5338,30 @@
         <v>54</v>
       </c>
       <c r="F115" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G115" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H115" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="I115" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="J115">
-        <v>77</v>
+        <v>172</v>
       </c>
     </row>
     <row r="116" spans="1:10">
       <c r="A116">
-        <v>163</v>
+        <v>488</v>
       </c>
       <c r="B116" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D116" t="s">
         <v>29</v>
@@ -5283,30 +5370,30 @@
         <v>54</v>
       </c>
       <c r="F116" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G116" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H116" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="I116" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="J116">
-        <v>73</v>
+        <v>167</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="A117">
-        <v>164</v>
+        <v>489</v>
       </c>
       <c r="B117" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C117" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D117" t="s">
         <v>29</v>
@@ -5315,27 +5402,27 @@
         <v>54</v>
       </c>
       <c r="F117" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G117" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H117" t="s">
-        <v>332</v>
+        <v>351</v>
       </c>
       <c r="I117" t="s">
-        <v>392</v>
+        <v>427</v>
       </c>
       <c r="J117">
-        <v>66</v>
+        <v>107</v>
       </c>
     </row>
     <row r="118" spans="1:10">
       <c r="A118">
-        <v>266</v>
+        <v>162</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C118" t="s">
         <v>25</v>
@@ -5344,30 +5431,30 @@
         <v>29</v>
       </c>
       <c r="E118" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F118" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G118" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H118" t="s">
-        <v>333</v>
+        <v>352</v>
       </c>
       <c r="I118" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J118">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="119" spans="1:10">
       <c r="A119">
-        <v>382</v>
+        <v>163</v>
       </c>
       <c r="B119" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C119" t="s">
         <v>25</v>
@@ -5376,19 +5463,19 @@
         <v>29</v>
       </c>
       <c r="E119" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F119" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G119" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H119" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="I119" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J119">
         <v>73</v>
@@ -5396,10 +5483,10 @@
     </row>
     <row r="120" spans="1:10">
       <c r="A120">
-        <v>419</v>
+        <v>164</v>
       </c>
       <c r="B120" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C120" t="s">
         <v>25</v>
@@ -5408,27 +5495,27 @@
         <v>29</v>
       </c>
       <c r="E120" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F120" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G120" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H120" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="I120" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J120">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="121" spans="1:10">
       <c r="A121">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="B121" t="s">
         <v>15</v>
@@ -5443,27 +5530,27 @@
         <v>55</v>
       </c>
       <c r="F121" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G121" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H121" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="I121" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J121">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="122" spans="1:10">
       <c r="A122">
-        <v>245</v>
+        <v>382</v>
       </c>
       <c r="B122" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C122" t="s">
         <v>25</v>
@@ -5475,27 +5562,27 @@
         <v>55</v>
       </c>
       <c r="F122" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G122" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H122" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="I122" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J122">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="123" spans="1:10">
       <c r="A123">
-        <v>246</v>
+        <v>419</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C123" t="s">
         <v>25</v>
@@ -5510,24 +5597,24 @@
         <v>174</v>
       </c>
       <c r="G123" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H123" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="I123" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J123">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="124" spans="1:10">
       <c r="A124">
-        <v>247</v>
+        <v>520</v>
       </c>
       <c r="B124" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C124" t="s">
         <v>25</v>
@@ -5539,27 +5626,27 @@
         <v>55</v>
       </c>
       <c r="F124" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G124" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H124" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="I124" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J124">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="125" spans="1:10">
       <c r="A125">
-        <v>383</v>
+        <v>244</v>
       </c>
       <c r="B125" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C125" t="s">
         <v>25</v>
@@ -5568,30 +5655,30 @@
         <v>29</v>
       </c>
       <c r="E125" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F125" t="s">
         <v>176</v>
       </c>
       <c r="G125" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H125" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="I125" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J125">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="126" spans="1:10">
       <c r="A126">
-        <v>158</v>
+        <v>245</v>
       </c>
       <c r="B126" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C126" t="s">
         <v>25</v>
@@ -5606,24 +5693,24 @@
         <v>177</v>
       </c>
       <c r="G126" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H126" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="I126" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J126">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="127" spans="1:10">
       <c r="A127">
-        <v>159</v>
+        <v>246</v>
       </c>
       <c r="B127" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C127" t="s">
         <v>25</v>
@@ -5638,24 +5725,24 @@
         <v>178</v>
       </c>
       <c r="G127" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H127" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="I127" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J127">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:10">
       <c r="A128">
-        <v>160</v>
+        <v>247</v>
       </c>
       <c r="B128" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C128" t="s">
         <v>25</v>
@@ -5670,24 +5757,24 @@
         <v>179</v>
       </c>
       <c r="G128" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H128" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="I128" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J128">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="129" spans="1:10">
       <c r="A129">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B129" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C129" t="s">
         <v>25</v>
@@ -5702,24 +5789,24 @@
         <v>180</v>
       </c>
       <c r="G129" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H129" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="I129" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J129">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="130" spans="1:10">
       <c r="A130">
-        <v>385</v>
+        <v>519</v>
       </c>
       <c r="B130" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C130" t="s">
         <v>25</v>
@@ -5734,24 +5821,24 @@
         <v>181</v>
       </c>
       <c r="G130" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H130" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="I130" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J130">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="131" spans="1:10">
       <c r="A131">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="B131" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C131" t="s">
         <v>25</v>
@@ -5766,21 +5853,21 @@
         <v>182</v>
       </c>
       <c r="G131" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H131" t="s">
-        <v>278</v>
+        <v>361</v>
       </c>
       <c r="I131" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J131">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="132" spans="1:10">
       <c r="A132">
-        <v>262</v>
+        <v>159</v>
       </c>
       <c r="B132" t="s">
         <v>12</v>
@@ -5798,24 +5885,24 @@
         <v>183</v>
       </c>
       <c r="G132" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H132" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="I132" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J132">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="133" spans="1:10">
       <c r="A133">
-        <v>263</v>
+        <v>160</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C133" t="s">
         <v>25</v>
@@ -5830,24 +5917,24 @@
         <v>184</v>
       </c>
       <c r="G133" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H133" t="s">
-        <v>343</v>
+        <v>363</v>
       </c>
       <c r="I133" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J133">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="134" spans="1:10">
       <c r="A134">
-        <v>264</v>
+        <v>384</v>
       </c>
       <c r="B134" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C134" t="s">
         <v>25</v>
@@ -5862,24 +5949,24 @@
         <v>185</v>
       </c>
       <c r="G134" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H134" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="I134" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J134">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="135" spans="1:10">
       <c r="A135">
-        <v>265</v>
+        <v>385</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C135" t="s">
         <v>25</v>
@@ -5894,24 +5981,24 @@
         <v>186</v>
       </c>
       <c r="G135" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H135" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="I135" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J135">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="136" spans="1:10">
       <c r="A136">
-        <v>416</v>
+        <v>109</v>
       </c>
       <c r="B136" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C136" t="s">
         <v>25</v>
@@ -5920,30 +6007,30 @@
         <v>29</v>
       </c>
       <c r="E136" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F136" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="G136" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H136" t="s">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="I136" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J136">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="137" spans="1:10">
       <c r="A137">
-        <v>417</v>
+        <v>262</v>
       </c>
       <c r="B137" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C137" t="s">
         <v>25</v>
@@ -5952,30 +6039,30 @@
         <v>29</v>
       </c>
       <c r="E137" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F137" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G137" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H137" t="s">
-        <v>278</v>
+        <v>365</v>
       </c>
       <c r="I137" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J137">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="138" spans="1:10">
       <c r="A138">
-        <v>418</v>
+        <v>263</v>
       </c>
       <c r="B138" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C138" t="s">
         <v>25</v>
@@ -5984,30 +6071,30 @@
         <v>29</v>
       </c>
       <c r="E138" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F138" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G138" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H138" t="s">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="I138" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J138">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="139" spans="1:10">
       <c r="A139">
-        <v>111</v>
+        <v>264</v>
       </c>
       <c r="B139" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C139" t="s">
         <v>25</v>
@@ -6019,27 +6106,27 @@
         <v>58</v>
       </c>
       <c r="F139" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G139" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H139" t="s">
-        <v>278</v>
+        <v>367</v>
       </c>
       <c r="I139" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J139">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="140" spans="1:10">
       <c r="A140">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="B140" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C140" t="s">
         <v>25</v>
@@ -6051,27 +6138,27 @@
         <v>58</v>
       </c>
       <c r="F140" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="G140" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H140" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="I140" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J140">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="141" spans="1:10">
       <c r="A141">
-        <v>166</v>
+        <v>416</v>
       </c>
       <c r="B141" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C141" t="s">
         <v>25</v>
@@ -6083,27 +6170,27 @@
         <v>58</v>
       </c>
       <c r="F141" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="G141" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H141" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="I141" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J141">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="142" spans="1:10">
       <c r="A142">
-        <v>241</v>
+        <v>417</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C142" t="s">
         <v>25</v>
@@ -6115,27 +6202,27 @@
         <v>58</v>
       </c>
       <c r="F142" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G142" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H142" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="I142" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J142">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
     <row r="143" spans="1:10">
       <c r="A143">
-        <v>242</v>
+        <v>418</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C143" t="s">
         <v>25</v>
@@ -6150,24 +6237,24 @@
         <v>189</v>
       </c>
       <c r="G143" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H143" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="I143" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J143">
-        <v>80</v>
+        <v>64</v>
       </c>
     </row>
     <row r="144" spans="1:10">
       <c r="A144">
-        <v>243</v>
+        <v>111</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C144" t="s">
         <v>25</v>
@@ -6176,33 +6263,33 @@
         <v>29</v>
       </c>
       <c r="E144" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F144" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G144" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H144" t="s">
-        <v>351</v>
+        <v>299</v>
       </c>
       <c r="I144" t="s">
-        <v>392</v>
+        <v>421</v>
       </c>
       <c r="J144">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="145" spans="1:10">
       <c r="A145">
-        <v>390</v>
+        <v>165</v>
       </c>
       <c r="B145" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C145" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D145" t="s">
         <v>29</v>
@@ -6211,30 +6298,30 @@
         <v>59</v>
       </c>
       <c r="F145" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G145" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H145" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="I145" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="J145">
-        <v>190</v>
+        <v>68</v>
       </c>
     </row>
     <row r="146" spans="1:10">
       <c r="A146">
-        <v>391</v>
+        <v>166</v>
       </c>
       <c r="B146" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C146" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D146" t="s">
         <v>29</v>
@@ -6243,30 +6330,30 @@
         <v>59</v>
       </c>
       <c r="F146" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G146" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H146" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="I146" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="J146">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="147" spans="1:10">
       <c r="A147">
-        <v>392</v>
+        <v>241</v>
       </c>
       <c r="B147" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C147" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D147" t="s">
         <v>29</v>
@@ -6275,30 +6362,30 @@
         <v>59</v>
       </c>
       <c r="F147" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G147" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H147" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="I147" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="J147">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="148" spans="1:10">
       <c r="A148">
-        <v>393</v>
+        <v>242</v>
       </c>
       <c r="B148" t="s">
         <v>15</v>
       </c>
       <c r="C148" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D148" t="s">
         <v>29</v>
@@ -6307,59 +6394,59 @@
         <v>59</v>
       </c>
       <c r="F148" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G148" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H148" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="I148" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="J148">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="149" spans="1:10">
       <c r="A149">
-        <v>452</v>
+        <v>243</v>
       </c>
       <c r="B149" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C149" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D149" t="s">
         <v>29</v>
       </c>
       <c r="E149" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F149" t="s">
         <v>197</v>
       </c>
       <c r="G149" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H149" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="I149" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="J149">
-        <v>169</v>
+        <v>55</v>
       </c>
     </row>
     <row r="150" spans="1:10">
       <c r="A150">
-        <v>453</v>
+        <v>390</v>
       </c>
       <c r="B150" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C150" t="s">
         <v>26</v>
@@ -6374,24 +6461,24 @@
         <v>198</v>
       </c>
       <c r="G150" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H150" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="I150" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J150">
-        <v>101</v>
+        <v>190</v>
       </c>
     </row>
     <row r="151" spans="1:10">
       <c r="A151">
-        <v>454</v>
+        <v>391</v>
       </c>
       <c r="B151" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C151" t="s">
         <v>26</v>
@@ -6406,24 +6493,24 @@
         <v>199</v>
       </c>
       <c r="G151" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H151" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="I151" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J151">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="152" spans="1:10">
       <c r="A152">
-        <v>213</v>
+        <v>392</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C152" t="s">
         <v>26</v>
@@ -6432,30 +6519,30 @@
         <v>29</v>
       </c>
       <c r="E152" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F152" t="s">
         <v>200</v>
       </c>
       <c r="G152" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H152" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="I152" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J152">
-        <v>109</v>
+        <v>90</v>
       </c>
     </row>
     <row r="153" spans="1:10">
       <c r="A153">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B153" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C153" t="s">
         <v>26</v>
@@ -6464,30 +6551,30 @@
         <v>29</v>
       </c>
       <c r="E153" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F153" t="s">
         <v>201</v>
       </c>
       <c r="G153" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H153" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="I153" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J153">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="154" spans="1:10">
       <c r="A154">
-        <v>396</v>
+        <v>452</v>
       </c>
       <c r="B154" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C154" t="s">
         <v>26</v>
@@ -6502,21 +6589,21 @@
         <v>202</v>
       </c>
       <c r="G154" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H154" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="I154" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J154">
-        <v>91</v>
+        <v>169</v>
       </c>
     </row>
     <row r="155" spans="1:10">
       <c r="A155">
-        <v>399</v>
+        <v>453</v>
       </c>
       <c r="B155" t="s">
         <v>11</v>
@@ -6534,24 +6621,24 @@
         <v>203</v>
       </c>
       <c r="G155" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H155" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="I155" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J155">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="156" spans="1:10">
       <c r="A156">
-        <v>189</v>
+        <v>454</v>
       </c>
       <c r="B156" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C156" t="s">
         <v>26</v>
@@ -6560,30 +6647,30 @@
         <v>29</v>
       </c>
       <c r="E156" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F156" t="s">
         <v>204</v>
       </c>
       <c r="G156" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H156" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="I156" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J156">
-        <v>96</v>
+        <v>110</v>
       </c>
     </row>
     <row r="157" spans="1:10">
       <c r="A157">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="B157" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C157" t="s">
         <v>26</v>
@@ -6598,24 +6685,24 @@
         <v>205</v>
       </c>
       <c r="G157" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H157" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="I157" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J157">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158" spans="1:10">
       <c r="A158">
-        <v>228</v>
+        <v>394</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C158" t="s">
         <v>26</v>
@@ -6630,24 +6717,24 @@
         <v>206</v>
       </c>
       <c r="G158" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H158" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="I158" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J158">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="159" spans="1:10">
       <c r="A159">
-        <v>469</v>
+        <v>396</v>
       </c>
       <c r="B159" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C159" t="s">
         <v>26</v>
@@ -6659,27 +6746,27 @@
         <v>62</v>
       </c>
       <c r="F159" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G159" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H159" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="I159" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J159">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="160" spans="1:10">
       <c r="A160">
-        <v>478</v>
+        <v>399</v>
       </c>
       <c r="B160" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C160" t="s">
         <v>26</v>
@@ -6691,27 +6778,27 @@
         <v>62</v>
       </c>
       <c r="F160" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G160" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H160" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="I160" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J160">
-        <v>192</v>
+        <v>108</v>
       </c>
     </row>
     <row r="161" spans="1:10">
       <c r="A161">
-        <v>276</v>
+        <v>189</v>
       </c>
       <c r="B161" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C161" t="s">
         <v>26</v>
@@ -6723,27 +6810,27 @@
         <v>63</v>
       </c>
       <c r="F161" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G161" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H161" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="I161" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J161">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="162" spans="1:10">
       <c r="A162">
-        <v>279</v>
+        <v>190</v>
       </c>
       <c r="B162" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C162" t="s">
         <v>26</v>
@@ -6755,80 +6842,80 @@
         <v>63</v>
       </c>
       <c r="F162" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G162" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H162" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="I162" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J162">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="163" spans="1:10">
       <c r="A163">
-        <v>151</v>
+        <v>228</v>
       </c>
       <c r="B163" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C163" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D163" t="s">
         <v>29</v>
       </c>
       <c r="E163" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F163" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G163" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H163" t="s">
-        <v>278</v>
+        <v>386</v>
       </c>
       <c r="I163" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="J163">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="164" spans="1:10">
       <c r="A164">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="B164" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C164" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D164" t="s">
         <v>29</v>
       </c>
       <c r="E164" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F164" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G164" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H164" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="I164" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="J164">
         <v>81</v>
@@ -6836,106 +6923,106 @@
     </row>
     <row r="165" spans="1:10">
       <c r="A165">
-        <v>438</v>
+        <v>478</v>
       </c>
       <c r="B165" t="s">
         <v>17</v>
       </c>
       <c r="C165" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D165" t="s">
         <v>29</v>
       </c>
       <c r="E165" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F165" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G165" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H165" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="I165" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="J165">
-        <v>95</v>
+        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:10">
       <c r="A166">
-        <v>441</v>
+        <v>276</v>
       </c>
       <c r="B166" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C166" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D166" t="s">
         <v>29</v>
       </c>
       <c r="E166" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F166" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G166" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H166" t="s">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="I166" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="J166">
-        <v>129</v>
+        <v>105</v>
       </c>
     </row>
     <row r="167" spans="1:10">
       <c r="A167">
-        <v>443</v>
+        <v>279</v>
       </c>
       <c r="B167" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C167" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D167" t="s">
         <v>29</v>
       </c>
       <c r="E167" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F167" t="s">
         <v>213</v>
       </c>
       <c r="G167" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H167" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="I167" t="s">
-        <v>401</v>
+        <v>429</v>
       </c>
       <c r="J167">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="168" spans="1:10">
       <c r="A168">
-        <v>444</v>
+        <v>151</v>
       </c>
       <c r="B168" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C168" t="s">
         <v>27</v>
@@ -6950,24 +7037,24 @@
         <v>214</v>
       </c>
       <c r="G168" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H168" t="s">
-        <v>370</v>
+        <v>299</v>
       </c>
       <c r="I168" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J168">
-        <v>107</v>
+        <v>63</v>
       </c>
     </row>
     <row r="169" spans="1:10">
       <c r="A169">
-        <v>492</v>
+        <v>445</v>
       </c>
       <c r="B169" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C169" t="s">
         <v>27</v>
@@ -6976,30 +7063,30 @@
         <v>29</v>
       </c>
       <c r="E169" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F169" t="s">
         <v>215</v>
       </c>
       <c r="G169" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H169" t="s">
-        <v>371</v>
+        <v>390</v>
       </c>
       <c r="I169" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J169">
-        <v>120</v>
+        <v>81</v>
       </c>
     </row>
     <row r="170" spans="1:10">
       <c r="A170">
-        <v>236</v>
+        <v>527</v>
       </c>
       <c r="B170" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C170" t="s">
         <v>27</v>
@@ -7008,30 +7095,30 @@
         <v>29</v>
       </c>
       <c r="E170" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F170" t="s">
         <v>216</v>
       </c>
       <c r="G170" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H170" t="s">
-        <v>278</v>
+        <v>391</v>
       </c>
       <c r="I170" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J170">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="171" spans="1:10">
       <c r="A171">
-        <v>237</v>
+        <v>528</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C171" t="s">
         <v>27</v>
@@ -7040,30 +7127,30 @@
         <v>29</v>
       </c>
       <c r="E171" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F171" t="s">
         <v>217</v>
       </c>
       <c r="G171" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H171" t="s">
-        <v>278</v>
+        <v>392</v>
       </c>
       <c r="I171" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J171">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="172" spans="1:10">
       <c r="A172">
-        <v>260</v>
+        <v>529</v>
       </c>
       <c r="B172" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C172" t="s">
         <v>27</v>
@@ -7072,30 +7159,30 @@
         <v>29</v>
       </c>
       <c r="E172" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F172" t="s">
         <v>218</v>
       </c>
       <c r="G172" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H172" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="I172" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J172">
-        <v>111</v>
+        <v>74</v>
       </c>
     </row>
     <row r="173" spans="1:10">
       <c r="A173">
-        <v>301</v>
+        <v>531</v>
       </c>
       <c r="B173" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C173" t="s">
         <v>27</v>
@@ -7104,30 +7191,30 @@
         <v>29</v>
       </c>
       <c r="E173" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F173" t="s">
         <v>219</v>
       </c>
       <c r="G173" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H173" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="I173" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J173">
-        <v>84</v>
+        <v>75</v>
       </c>
     </row>
     <row r="174" spans="1:10">
       <c r="A174">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="B174" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C174" t="s">
         <v>27</v>
@@ -7136,30 +7223,30 @@
         <v>29</v>
       </c>
       <c r="E174" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F174" t="s">
         <v>220</v>
       </c>
       <c r="G174" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H174" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="I174" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J174">
-        <v>66</v>
+        <v>95</v>
       </c>
     </row>
     <row r="175" spans="1:10">
       <c r="A175">
-        <v>193</v>
+        <v>441</v>
       </c>
       <c r="B175" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C175" t="s">
         <v>27</v>
@@ -7168,30 +7255,30 @@
         <v>29</v>
       </c>
       <c r="E175" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F175" t="s">
         <v>221</v>
       </c>
       <c r="G175" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H175" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="I175" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J175">
-        <v>167</v>
+        <v>129</v>
       </c>
     </row>
     <row r="176" spans="1:10">
       <c r="A176">
-        <v>300</v>
+        <v>443</v>
       </c>
       <c r="B176" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C176" t="s">
         <v>27</v>
@@ -7200,30 +7287,30 @@
         <v>29</v>
       </c>
       <c r="E176" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F176" t="s">
         <v>222</v>
       </c>
       <c r="G176" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H176" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="I176" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J176">
-        <v>149</v>
+        <v>89</v>
       </c>
     </row>
     <row r="177" spans="1:10">
       <c r="A177">
-        <v>304</v>
+        <v>444</v>
       </c>
       <c r="B177" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C177" t="s">
         <v>27</v>
@@ -7232,30 +7319,30 @@
         <v>29</v>
       </c>
       <c r="E177" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F177" t="s">
         <v>223</v>
       </c>
       <c r="G177" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H177" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="I177" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J177">
-        <v>200</v>
+        <v>107</v>
       </c>
     </row>
     <row r="178" spans="1:10">
       <c r="A178">
-        <v>356</v>
+        <v>533</v>
       </c>
       <c r="B178" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C178" t="s">
         <v>27</v>
@@ -7264,531 +7351,531 @@
         <v>29</v>
       </c>
       <c r="E178" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F178" t="s">
         <v>224</v>
       </c>
       <c r="G178" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H178" t="s">
-        <v>376</v>
+        <v>395</v>
       </c>
       <c r="I178" t="s">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="J178">
-        <v>772</v>
+        <v>72</v>
       </c>
     </row>
     <row r="179" spans="1:10">
       <c r="A179">
-        <v>132</v>
+        <v>492</v>
       </c>
       <c r="B179" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C179" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D179" t="s">
         <v>29</v>
       </c>
       <c r="E179" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F179" t="s">
         <v>225</v>
       </c>
       <c r="G179" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H179" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
       <c r="I179" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J179">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="180" spans="1:10">
       <c r="A180">
-        <v>192</v>
+        <v>518</v>
       </c>
       <c r="B180" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C180" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D180" t="s">
         <v>29</v>
       </c>
       <c r="E180" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F180" t="s">
         <v>226</v>
       </c>
       <c r="G180" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H180" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="I180" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J180">
-        <v>83</v>
+        <v>102</v>
       </c>
     </row>
     <row r="181" spans="1:10">
       <c r="A181">
-        <v>194</v>
+        <v>523</v>
       </c>
       <c r="B181" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C181" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D181" t="s">
         <v>29</v>
       </c>
       <c r="E181" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F181" t="s">
         <v>227</v>
       </c>
       <c r="G181" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H181" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="I181" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J181">
-        <v>103</v>
+        <v>122</v>
       </c>
     </row>
     <row r="182" spans="1:10">
       <c r="A182">
-        <v>195</v>
+        <v>525</v>
       </c>
       <c r="B182" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C182" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D182" t="s">
         <v>29</v>
       </c>
       <c r="E182" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F182" t="s">
         <v>228</v>
       </c>
       <c r="G182" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H182" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="I182" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J182">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="183" spans="1:10">
       <c r="A183">
-        <v>196</v>
+        <v>526</v>
       </c>
       <c r="B183" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C183" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D183" t="s">
         <v>29</v>
       </c>
       <c r="E183" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F183" t="s">
         <v>229</v>
       </c>
       <c r="G183" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H183" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="I183" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J183">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="184" spans="1:10">
       <c r="A184">
-        <v>462</v>
+        <v>236</v>
       </c>
       <c r="B184" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C184" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D184" t="s">
         <v>29</v>
       </c>
       <c r="E184" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F184" t="s">
         <v>230</v>
       </c>
       <c r="G184" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H184" t="s">
-        <v>378</v>
+        <v>299</v>
       </c>
       <c r="I184" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J184">
-        <v>104</v>
+        <v>67</v>
       </c>
     </row>
     <row r="185" spans="1:10">
       <c r="A185">
-        <v>463</v>
+        <v>237</v>
       </c>
       <c r="B185" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C185" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D185" t="s">
         <v>29</v>
       </c>
       <c r="E185" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F185" t="s">
         <v>231</v>
       </c>
       <c r="G185" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="H185" t="s">
-        <v>378</v>
+        <v>299</v>
       </c>
       <c r="I185" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J185">
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="186" spans="1:10">
       <c r="A186">
-        <v>464</v>
+        <v>260</v>
       </c>
       <c r="B186" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C186" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D186" t="s">
         <v>29</v>
       </c>
       <c r="E186" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F186" t="s">
         <v>232</v>
       </c>
       <c r="G186" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H186" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="I186" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J186">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="187" spans="1:10">
       <c r="A187">
-        <v>465</v>
+        <v>301</v>
       </c>
       <c r="B187" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C187" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D187" t="s">
         <v>29</v>
       </c>
       <c r="E187" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F187" t="s">
         <v>233</v>
       </c>
       <c r="G187" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H187" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="I187" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J187">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="188" spans="1:10">
       <c r="A188">
-        <v>105</v>
+        <v>413</v>
       </c>
       <c r="B188" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C188" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D188" t="s">
         <v>29</v>
       </c>
       <c r="E188" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F188" t="s">
         <v>234</v>
       </c>
       <c r="G188" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H188" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="I188" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J188">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="189" spans="1:10">
       <c r="A189">
-        <v>145</v>
+        <v>532</v>
       </c>
       <c r="B189" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C189" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D189" t="s">
         <v>29</v>
       </c>
       <c r="E189" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F189" t="s">
         <v>235</v>
       </c>
       <c r="G189" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H189" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="I189" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J189">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="190" spans="1:10">
       <c r="A190">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="B190" t="s">
         <v>12</v>
       </c>
       <c r="C190" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D190" t="s">
         <v>29</v>
       </c>
       <c r="E190" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F190" t="s">
         <v>236</v>
       </c>
       <c r="G190" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H190" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="I190" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J190">
-        <v>97</v>
+        <v>167</v>
       </c>
     </row>
     <row r="191" spans="1:10">
       <c r="A191">
-        <v>425</v>
+        <v>300</v>
       </c>
       <c r="B191" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C191" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D191" t="s">
         <v>29</v>
       </c>
       <c r="E191" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F191" t="s">
         <v>237</v>
       </c>
       <c r="G191" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H191" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="I191" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J191">
-        <v>96</v>
+        <v>149</v>
       </c>
     </row>
     <row r="192" spans="1:10">
       <c r="A192">
-        <v>426</v>
+        <v>304</v>
       </c>
       <c r="B192" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C192" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D192" t="s">
         <v>29</v>
       </c>
       <c r="E192" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F192" t="s">
         <v>238</v>
       </c>
       <c r="G192" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H192" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="I192" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J192">
-        <v>97</v>
+        <v>200</v>
       </c>
     </row>
     <row r="193" spans="1:10">
       <c r="A193">
-        <v>427</v>
+        <v>356</v>
       </c>
       <c r="B193" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C193" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D193" t="s">
         <v>29</v>
       </c>
       <c r="E193" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F193" t="s">
         <v>239</v>
       </c>
       <c r="G193" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H193" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="I193" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J193">
-        <v>97</v>
+        <v>772</v>
       </c>
     </row>
     <row r="194" spans="1:10">
       <c r="A194">
-        <v>428</v>
+        <v>534</v>
       </c>
       <c r="B194" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C194" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D194" t="s">
         <v>29</v>
       </c>
       <c r="E194" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F194" t="s">
         <v>240</v>
       </c>
       <c r="G194" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H194" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="I194" t="s">
-        <v>402</v>
+        <v>430</v>
       </c>
       <c r="J194">
         <v>98</v>
@@ -7796,10 +7883,10 @@
     </row>
     <row r="195" spans="1:10">
       <c r="A195">
-        <v>431</v>
+        <v>132</v>
       </c>
       <c r="B195" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C195" t="s">
         <v>28</v>
@@ -7814,24 +7901,24 @@
         <v>241</v>
       </c>
       <c r="G195" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H195" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="I195" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J195">
-        <v>102</v>
+        <v>90</v>
       </c>
     </row>
     <row r="196" spans="1:10">
       <c r="A196">
-        <v>432</v>
+        <v>192</v>
       </c>
       <c r="B196" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C196" t="s">
         <v>28</v>
@@ -7846,24 +7933,24 @@
         <v>242</v>
       </c>
       <c r="G196" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H196" t="s">
-        <v>381</v>
+        <v>406</v>
       </c>
       <c r="I196" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J196">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="197" spans="1:10">
       <c r="A197">
-        <v>506</v>
+        <v>194</v>
       </c>
       <c r="B197" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C197" t="s">
         <v>28</v>
@@ -7878,24 +7965,24 @@
         <v>243</v>
       </c>
       <c r="G197" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H197" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="I197" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J197">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="198" spans="1:10">
       <c r="A198">
-        <v>508</v>
+        <v>195</v>
       </c>
       <c r="B198" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C198" t="s">
         <v>28</v>
@@ -7910,24 +7997,24 @@
         <v>244</v>
       </c>
       <c r="G198" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H198" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="I198" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J198">
-        <v>87</v>
+        <v>110</v>
       </c>
     </row>
     <row r="199" spans="1:10">
       <c r="A199">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="B199" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C199" t="s">
         <v>28</v>
@@ -7936,30 +8023,30 @@
         <v>29</v>
       </c>
       <c r="E199" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F199" t="s">
         <v>245</v>
       </c>
       <c r="G199" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H199" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="I199" t="s">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="J199">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="200" spans="1:10">
       <c r="A200">
-        <v>208</v>
+        <v>462</v>
       </c>
       <c r="B200" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C200" t="s">
         <v>28</v>
@@ -7968,30 +8055,30 @@
         <v>29</v>
       </c>
       <c r="E200" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F200" t="s">
         <v>246</v>
       </c>
       <c r="G200" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H200" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="I200" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J200">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="201" spans="1:10">
       <c r="A201">
-        <v>209</v>
+        <v>463</v>
       </c>
       <c r="B201" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C201" t="s">
         <v>28</v>
@@ -8000,30 +8087,30 @@
         <v>29</v>
       </c>
       <c r="E201" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F201" t="s">
         <v>247</v>
       </c>
       <c r="G201" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H201" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="I201" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J201">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="202" spans="1:10">
       <c r="A202">
-        <v>210</v>
+        <v>464</v>
       </c>
       <c r="B202" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C202" t="s">
         <v>28</v>
@@ -8032,30 +8119,30 @@
         <v>29</v>
       </c>
       <c r="E202" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F202" t="s">
         <v>248</v>
       </c>
       <c r="G202" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H202" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="I202" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J202">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="203" spans="1:10">
       <c r="A203">
-        <v>211</v>
+        <v>465</v>
       </c>
       <c r="B203" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C203" t="s">
         <v>28</v>
@@ -8064,30 +8151,30 @@
         <v>29</v>
       </c>
       <c r="E203" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F203" t="s">
         <v>249</v>
       </c>
       <c r="G203" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H203" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="I203" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J203">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="204" spans="1:10">
       <c r="A204">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C204" t="s">
         <v>28</v>
@@ -8102,24 +8189,24 @@
         <v>250</v>
       </c>
       <c r="G204" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H204" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="I204" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J204">
-        <v>104</v>
+        <v>67</v>
       </c>
     </row>
     <row r="205" spans="1:10">
       <c r="A205">
-        <v>509</v>
+        <v>145</v>
       </c>
       <c r="B205" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C205" t="s">
         <v>28</v>
@@ -8134,24 +8221,24 @@
         <v>251</v>
       </c>
       <c r="G205" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H205" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="I205" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J205">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="206" spans="1:10">
       <c r="A206">
-        <v>511</v>
+        <v>146</v>
       </c>
       <c r="B206" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C206" t="s">
         <v>28</v>
@@ -8166,24 +8253,24 @@
         <v>252</v>
       </c>
       <c r="G206" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H206" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="I206" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J206">
-        <v>80</v>
+        <v>97</v>
       </c>
     </row>
     <row r="207" spans="1:10">
       <c r="A207">
-        <v>512</v>
+        <v>425</v>
       </c>
       <c r="B207" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C207" t="s">
         <v>28</v>
@@ -8198,24 +8285,24 @@
         <v>253</v>
       </c>
       <c r="G207" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H207" t="s">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="I207" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J207">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="208" spans="1:10">
       <c r="A208">
-        <v>73</v>
+        <v>426</v>
       </c>
       <c r="B208" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C208" t="s">
         <v>28</v>
@@ -8224,30 +8311,30 @@
         <v>29</v>
       </c>
       <c r="E208" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F208" t="s">
         <v>254</v>
       </c>
       <c r="G208" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H208" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="I208" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J208">
-        <v>123</v>
+        <v>97</v>
       </c>
     </row>
     <row r="209" spans="1:10">
       <c r="A209">
-        <v>273</v>
+        <v>427</v>
       </c>
       <c r="B209" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C209" t="s">
         <v>28</v>
@@ -8256,30 +8343,30 @@
         <v>29</v>
       </c>
       <c r="E209" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F209" t="s">
         <v>255</v>
       </c>
       <c r="G209" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H209" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="I209" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J209">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="210" spans="1:10">
       <c r="A210">
-        <v>274</v>
+        <v>428</v>
       </c>
       <c r="B210" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C210" t="s">
         <v>28</v>
@@ -8288,30 +8375,30 @@
         <v>29</v>
       </c>
       <c r="E210" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F210" t="s">
         <v>256</v>
       </c>
       <c r="G210" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H210" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="I210" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J210">
-        <v>116</v>
+        <v>98</v>
       </c>
     </row>
     <row r="211" spans="1:10">
       <c r="A211">
-        <v>275</v>
+        <v>431</v>
       </c>
       <c r="B211" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C211" t="s">
         <v>28</v>
@@ -8320,30 +8407,30 @@
         <v>29</v>
       </c>
       <c r="E211" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F211" t="s">
         <v>257</v>
       </c>
       <c r="G211" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H211" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="I211" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J211">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="212" spans="1:10">
       <c r="A212">
-        <v>277</v>
+        <v>432</v>
       </c>
       <c r="B212" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C212" t="s">
         <v>28</v>
@@ -8352,30 +8439,30 @@
         <v>29</v>
       </c>
       <c r="E212" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F212" t="s">
         <v>258</v>
       </c>
       <c r="G212" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H212" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="I212" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J212">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="213" spans="1:10">
       <c r="A213">
-        <v>278</v>
+        <v>506</v>
       </c>
       <c r="B213" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C213" t="s">
         <v>28</v>
@@ -8384,30 +8471,30 @@
         <v>29</v>
       </c>
       <c r="E213" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F213" t="s">
         <v>259</v>
       </c>
       <c r="G213" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H213" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="I213" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J213">
-        <v>110</v>
+        <v>96</v>
       </c>
     </row>
     <row r="214" spans="1:10">
       <c r="A214">
-        <v>280</v>
+        <v>508</v>
       </c>
       <c r="B214" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C214" t="s">
         <v>28</v>
@@ -8416,30 +8503,30 @@
         <v>29</v>
       </c>
       <c r="E214" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F214" t="s">
         <v>260</v>
       </c>
       <c r="G214" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H214" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="I214" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J214">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="215" spans="1:10">
       <c r="A215">
-        <v>281</v>
+        <v>72</v>
       </c>
       <c r="B215" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C215" t="s">
         <v>28</v>
@@ -8454,24 +8541,24 @@
         <v>261</v>
       </c>
       <c r="G215" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H215" t="s">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="I215" t="s">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="J215">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="216" spans="1:10">
       <c r="A216">
-        <v>74</v>
+        <v>208</v>
       </c>
       <c r="B216" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C216" t="s">
         <v>28</v>
@@ -8480,30 +8567,30 @@
         <v>29</v>
       </c>
       <c r="E216" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F216" t="s">
         <v>262</v>
       </c>
       <c r="G216" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H216" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="I216" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J216">
-        <v>54</v>
+        <v>101</v>
       </c>
     </row>
     <row r="217" spans="1:10">
       <c r="A217">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="B217" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C217" t="s">
         <v>28</v>
@@ -8512,30 +8599,30 @@
         <v>29</v>
       </c>
       <c r="E217" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F217" t="s">
         <v>263</v>
       </c>
       <c r="G217" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H217" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="I217" t="s">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="J217">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
     <row r="218" spans="1:10">
       <c r="A218">
-        <v>138</v>
+        <v>210</v>
       </c>
       <c r="B218" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C218" t="s">
         <v>28</v>
@@ -8544,30 +8631,30 @@
         <v>29</v>
       </c>
       <c r="E218" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F218" t="s">
         <v>264</v>
       </c>
       <c r="G218" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H218" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="I218" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J218">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="219" spans="1:10">
       <c r="A219">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="B219" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C219" t="s">
         <v>28</v>
@@ -8576,30 +8663,30 @@
         <v>29</v>
       </c>
       <c r="E219" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F219" t="s">
         <v>265</v>
       </c>
       <c r="G219" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H219" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="I219" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J219">
-        <v>65</v>
+        <v>100</v>
       </c>
     </row>
     <row r="220" spans="1:10">
       <c r="A220">
-        <v>421</v>
+        <v>212</v>
       </c>
       <c r="B220" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C220" t="s">
         <v>28</v>
@@ -8608,30 +8695,30 @@
         <v>29</v>
       </c>
       <c r="E220" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F220" t="s">
         <v>266</v>
       </c>
       <c r="G220" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H220" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="I220" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J220">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="221" spans="1:10">
       <c r="A221">
-        <v>422</v>
+        <v>509</v>
       </c>
       <c r="B221" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C221" t="s">
         <v>28</v>
@@ -8640,30 +8727,30 @@
         <v>29</v>
       </c>
       <c r="E221" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F221" t="s">
         <v>267</v>
       </c>
       <c r="G221" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H221" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="I221" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J221">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="222" spans="1:10">
       <c r="A222">
-        <v>423</v>
+        <v>511</v>
       </c>
       <c r="B222" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C222" t="s">
         <v>28</v>
@@ -8672,30 +8759,30 @@
         <v>29</v>
       </c>
       <c r="E222" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F222" t="s">
         <v>268</v>
       </c>
       <c r="G222" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H222" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="I222" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J222">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="223" spans="1:10">
       <c r="A223">
-        <v>424</v>
+        <v>512</v>
       </c>
       <c r="B223" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C223" t="s">
         <v>28</v>
@@ -8704,27 +8791,27 @@
         <v>29</v>
       </c>
       <c r="E223" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F223" t="s">
         <v>269</v>
       </c>
       <c r="G223" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H223" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="I223" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J223">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="224" spans="1:10">
       <c r="A224">
-        <v>460</v>
+        <v>514</v>
       </c>
       <c r="B224" t="s">
         <v>18</v>
@@ -8736,30 +8823,30 @@
         <v>29</v>
       </c>
       <c r="E224" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F224" t="s">
         <v>270</v>
       </c>
       <c r="G224" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H224" t="s">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="I224" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J224">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="225" spans="1:10">
       <c r="A225">
-        <v>461</v>
+        <v>73</v>
       </c>
       <c r="B225" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C225" t="s">
         <v>28</v>
@@ -8771,19 +8858,691 @@
         <v>73</v>
       </c>
       <c r="F225" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="G225" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="H225" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="I225" t="s">
-        <v>402</v>
+        <v>431</v>
       </c>
       <c r="J225">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10">
+      <c r="A226">
+        <v>273</v>
+      </c>
+      <c r="B226" t="s">
+        <v>14</v>
+      </c>
+      <c r="C226" t="s">
+        <v>28</v>
+      </c>
+      <c r="D226" t="s">
+        <v>29</v>
+      </c>
+      <c r="E226" t="s">
+        <v>73</v>
+      </c>
+      <c r="F226" t="s">
+        <v>272</v>
+      </c>
+      <c r="G226" t="s">
+        <v>292</v>
+      </c>
+      <c r="H226" t="s">
+        <v>416</v>
+      </c>
+      <c r="I226" t="s">
+        <v>431</v>
+      </c>
+      <c r="J226">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10">
+      <c r="A227">
+        <v>274</v>
+      </c>
+      <c r="B227" t="s">
+        <v>14</v>
+      </c>
+      <c r="C227" t="s">
+        <v>28</v>
+      </c>
+      <c r="D227" t="s">
+        <v>29</v>
+      </c>
+      <c r="E227" t="s">
+        <v>73</v>
+      </c>
+      <c r="F227" t="s">
+        <v>273</v>
+      </c>
+      <c r="G227" t="s">
+        <v>292</v>
+      </c>
+      <c r="H227" t="s">
+        <v>416</v>
+      </c>
+      <c r="I227" t="s">
+        <v>431</v>
+      </c>
+      <c r="J227">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10">
+      <c r="A228">
+        <v>275</v>
+      </c>
+      <c r="B228" t="s">
+        <v>14</v>
+      </c>
+      <c r="C228" t="s">
+        <v>28</v>
+      </c>
+      <c r="D228" t="s">
+        <v>29</v>
+      </c>
+      <c r="E228" t="s">
+        <v>73</v>
+      </c>
+      <c r="F228" t="s">
+        <v>274</v>
+      </c>
+      <c r="G228" t="s">
+        <v>292</v>
+      </c>
+      <c r="H228" t="s">
+        <v>416</v>
+      </c>
+      <c r="I228" t="s">
+        <v>431</v>
+      </c>
+      <c r="J228">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10">
+      <c r="A229">
+        <v>277</v>
+      </c>
+      <c r="B229" t="s">
+        <v>14</v>
+      </c>
+      <c r="C229" t="s">
+        <v>28</v>
+      </c>
+      <c r="D229" t="s">
+        <v>29</v>
+      </c>
+      <c r="E229" t="s">
+        <v>73</v>
+      </c>
+      <c r="F229" t="s">
+        <v>275</v>
+      </c>
+      <c r="G229" t="s">
+        <v>292</v>
+      </c>
+      <c r="H229" t="s">
+        <v>416</v>
+      </c>
+      <c r="I229" t="s">
+        <v>431</v>
+      </c>
+      <c r="J229">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10">
+      <c r="A230">
+        <v>278</v>
+      </c>
+      <c r="B230" t="s">
+        <v>14</v>
+      </c>
+      <c r="C230" t="s">
+        <v>28</v>
+      </c>
+      <c r="D230" t="s">
+        <v>29</v>
+      </c>
+      <c r="E230" t="s">
+        <v>73</v>
+      </c>
+      <c r="F230" t="s">
+        <v>276</v>
+      </c>
+      <c r="G230" t="s">
+        <v>292</v>
+      </c>
+      <c r="H230" t="s">
+        <v>416</v>
+      </c>
+      <c r="I230" t="s">
+        <v>431</v>
+      </c>
+      <c r="J230">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10">
+      <c r="A231">
+        <v>280</v>
+      </c>
+      <c r="B231" t="s">
+        <v>14</v>
+      </c>
+      <c r="C231" t="s">
+        <v>28</v>
+      </c>
+      <c r="D231" t="s">
+        <v>29</v>
+      </c>
+      <c r="E231" t="s">
+        <v>73</v>
+      </c>
+      <c r="F231" t="s">
+        <v>277</v>
+      </c>
+      <c r="G231" t="s">
+        <v>292</v>
+      </c>
+      <c r="H231" t="s">
+        <v>416</v>
+      </c>
+      <c r="I231" t="s">
+        <v>431</v>
+      </c>
+      <c r="J231">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10">
+      <c r="A232">
+        <v>281</v>
+      </c>
+      <c r="B232" t="s">
+        <v>14</v>
+      </c>
+      <c r="C232" t="s">
+        <v>28</v>
+      </c>
+      <c r="D232" t="s">
+        <v>29</v>
+      </c>
+      <c r="E232" t="s">
+        <v>73</v>
+      </c>
+      <c r="F232" t="s">
+        <v>278</v>
+      </c>
+      <c r="G232" t="s">
+        <v>292</v>
+      </c>
+      <c r="H232" t="s">
+        <v>416</v>
+      </c>
+      <c r="I232" t="s">
+        <v>431</v>
+      </c>
+      <c r="J232">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10">
+      <c r="A233">
+        <v>74</v>
+      </c>
+      <c r="B233" t="s">
+        <v>10</v>
+      </c>
+      <c r="C233" t="s">
+        <v>28</v>
+      </c>
+      <c r="D233" t="s">
+        <v>29</v>
+      </c>
+      <c r="E233" t="s">
+        <v>74</v>
+      </c>
+      <c r="F233" t="s">
+        <v>279</v>
+      </c>
+      <c r="G233" t="s">
+        <v>292</v>
+      </c>
+      <c r="H233" t="s">
+        <v>417</v>
+      </c>
+      <c r="I233" t="s">
+        <v>431</v>
+      </c>
+      <c r="J233">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10">
+      <c r="A234">
+        <v>107</v>
+      </c>
+      <c r="B234" t="s">
+        <v>11</v>
+      </c>
+      <c r="C234" t="s">
+        <v>28</v>
+      </c>
+      <c r="D234" t="s">
+        <v>29</v>
+      </c>
+      <c r="E234" t="s">
+        <v>74</v>
+      </c>
+      <c r="F234" t="s">
+        <v>280</v>
+      </c>
+      <c r="G234" t="s">
+        <v>292</v>
+      </c>
+      <c r="H234" t="s">
+        <v>417</v>
+      </c>
+      <c r="I234" t="s">
+        <v>432</v>
+      </c>
+      <c r="J234">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10">
+      <c r="A235">
+        <v>138</v>
+      </c>
+      <c r="B235" t="s">
+        <v>12</v>
+      </c>
+      <c r="C235" t="s">
+        <v>28</v>
+      </c>
+      <c r="D235" t="s">
+        <v>29</v>
+      </c>
+      <c r="E235" t="s">
+        <v>74</v>
+      </c>
+      <c r="F235" t="s">
+        <v>281</v>
+      </c>
+      <c r="G235" t="s">
+        <v>292</v>
+      </c>
+      <c r="H235" t="s">
+        <v>418</v>
+      </c>
+      <c r="I235" t="s">
+        <v>431</v>
+      </c>
+      <c r="J235">
         <v>104</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10">
+      <c r="A236">
+        <v>139</v>
+      </c>
+      <c r="B236" t="s">
+        <v>12</v>
+      </c>
+      <c r="C236" t="s">
+        <v>28</v>
+      </c>
+      <c r="D236" t="s">
+        <v>29</v>
+      </c>
+      <c r="E236" t="s">
+        <v>74</v>
+      </c>
+      <c r="F236" t="s">
+        <v>282</v>
+      </c>
+      <c r="G236" t="s">
+        <v>292</v>
+      </c>
+      <c r="H236" t="s">
+        <v>418</v>
+      </c>
+      <c r="I236" t="s">
+        <v>431</v>
+      </c>
+      <c r="J236">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10">
+      <c r="A237">
+        <v>421</v>
+      </c>
+      <c r="B237" t="s">
+        <v>17</v>
+      </c>
+      <c r="C237" t="s">
+        <v>28</v>
+      </c>
+      <c r="D237" t="s">
+        <v>29</v>
+      </c>
+      <c r="E237" t="s">
+        <v>74</v>
+      </c>
+      <c r="F237" t="s">
+        <v>283</v>
+      </c>
+      <c r="G237" t="s">
+        <v>292</v>
+      </c>
+      <c r="H237" t="s">
+        <v>419</v>
+      </c>
+      <c r="I237" t="s">
+        <v>431</v>
+      </c>
+      <c r="J237">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10">
+      <c r="A238">
+        <v>422</v>
+      </c>
+      <c r="B238" t="s">
+        <v>17</v>
+      </c>
+      <c r="C238" t="s">
+        <v>28</v>
+      </c>
+      <c r="D238" t="s">
+        <v>29</v>
+      </c>
+      <c r="E238" t="s">
+        <v>74</v>
+      </c>
+      <c r="F238" t="s">
+        <v>284</v>
+      </c>
+      <c r="G238" t="s">
+        <v>292</v>
+      </c>
+      <c r="H238" t="s">
+        <v>419</v>
+      </c>
+      <c r="I238" t="s">
+        <v>431</v>
+      </c>
+      <c r="J238">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10">
+      <c r="A239">
+        <v>423</v>
+      </c>
+      <c r="B239" t="s">
+        <v>17</v>
+      </c>
+      <c r="C239" t="s">
+        <v>28</v>
+      </c>
+      <c r="D239" t="s">
+        <v>29</v>
+      </c>
+      <c r="E239" t="s">
+        <v>74</v>
+      </c>
+      <c r="F239" t="s">
+        <v>285</v>
+      </c>
+      <c r="G239" t="s">
+        <v>292</v>
+      </c>
+      <c r="H239" t="s">
+        <v>419</v>
+      </c>
+      <c r="I239" t="s">
+        <v>431</v>
+      </c>
+      <c r="J239">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10">
+      <c r="A240">
+        <v>424</v>
+      </c>
+      <c r="B240" t="s">
+        <v>17</v>
+      </c>
+      <c r="C240" t="s">
+        <v>28</v>
+      </c>
+      <c r="D240" t="s">
+        <v>29</v>
+      </c>
+      <c r="E240" t="s">
+        <v>74</v>
+      </c>
+      <c r="F240" t="s">
+        <v>286</v>
+      </c>
+      <c r="G240" t="s">
+        <v>292</v>
+      </c>
+      <c r="H240" t="s">
+        <v>419</v>
+      </c>
+      <c r="I240" t="s">
+        <v>431</v>
+      </c>
+      <c r="J240">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10">
+      <c r="A241">
+        <v>460</v>
+      </c>
+      <c r="B241" t="s">
+        <v>18</v>
+      </c>
+      <c r="C241" t="s">
+        <v>28</v>
+      </c>
+      <c r="D241" t="s">
+        <v>29</v>
+      </c>
+      <c r="E241" t="s">
+        <v>74</v>
+      </c>
+      <c r="F241" t="s">
+        <v>287</v>
+      </c>
+      <c r="G241" t="s">
+        <v>292</v>
+      </c>
+      <c r="H241" t="s">
+        <v>418</v>
+      </c>
+      <c r="I241" t="s">
+        <v>431</v>
+      </c>
+      <c r="J241">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10">
+      <c r="A242">
+        <v>461</v>
+      </c>
+      <c r="B242" t="s">
+        <v>18</v>
+      </c>
+      <c r="C242" t="s">
+        <v>28</v>
+      </c>
+      <c r="D242" t="s">
+        <v>29</v>
+      </c>
+      <c r="E242" t="s">
+        <v>74</v>
+      </c>
+      <c r="F242" t="s">
+        <v>263</v>
+      </c>
+      <c r="G242" t="s">
+        <v>292</v>
+      </c>
+      <c r="H242" t="s">
+        <v>418</v>
+      </c>
+      <c r="I242" t="s">
+        <v>431</v>
+      </c>
+      <c r="J242">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10">
+      <c r="A243">
+        <v>515</v>
+      </c>
+      <c r="B243" t="s">
+        <v>18</v>
+      </c>
+      <c r="C243" t="s">
+        <v>28</v>
+      </c>
+      <c r="D243" t="s">
+        <v>29</v>
+      </c>
+      <c r="E243" t="s">
+        <v>74</v>
+      </c>
+      <c r="F243" t="s">
+        <v>288</v>
+      </c>
+      <c r="G243" t="s">
+        <v>292</v>
+      </c>
+      <c r="H243" t="s">
+        <v>418</v>
+      </c>
+      <c r="I243" t="s">
+        <v>431</v>
+      </c>
+      <c r="J243">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10">
+      <c r="A244">
+        <v>516</v>
+      </c>
+      <c r="B244" t="s">
+        <v>18</v>
+      </c>
+      <c r="C244" t="s">
+        <v>28</v>
+      </c>
+      <c r="D244" t="s">
+        <v>29</v>
+      </c>
+      <c r="E244" t="s">
+        <v>74</v>
+      </c>
+      <c r="F244" t="s">
+        <v>289</v>
+      </c>
+      <c r="G244" t="s">
+        <v>292</v>
+      </c>
+      <c r="H244" t="s">
+        <v>418</v>
+      </c>
+      <c r="I244" t="s">
+        <v>431</v>
+      </c>
+      <c r="J244">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10">
+      <c r="A245">
+        <v>517</v>
+      </c>
+      <c r="B245" t="s">
+        <v>18</v>
+      </c>
+      <c r="C245" t="s">
+        <v>28</v>
+      </c>
+      <c r="D245" t="s">
+        <v>29</v>
+      </c>
+      <c r="E245" t="s">
+        <v>74</v>
+      </c>
+      <c r="F245" t="s">
+        <v>290</v>
+      </c>
+      <c r="G245" t="s">
+        <v>292</v>
+      </c>
+      <c r="H245" t="s">
+        <v>418</v>
+      </c>
+      <c r="I245" t="s">
+        <v>431</v>
+      </c>
+      <c r="J245">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10">
+      <c r="A246">
+        <v>522</v>
+      </c>
+      <c r="B246" t="s">
+        <v>18</v>
+      </c>
+      <c r="C246" t="s">
+        <v>28</v>
+      </c>
+      <c r="D246" t="s">
+        <v>29</v>
+      </c>
+      <c r="E246" t="s">
+        <v>74</v>
+      </c>
+      <c r="F246" t="s">
+        <v>291</v>
+      </c>
+      <c r="G246" t="s">
+        <v>292</v>
+      </c>
+      <c r="H246" t="s">
+        <v>418</v>
+      </c>
+      <c r="I246" t="s">
+        <v>431</v>
+      </c>
+      <c r="J246">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/VHTs_and_Community_Demos_Extract.xlsx
+++ b/VHTs_and_Community_Demos_Extract.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2274" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2290" uniqueCount="502">
   <si>
     <t>Entry Index</t>
   </si>
@@ -781,6 +781,12 @@
     <t>Natirae primary school catchment area</t>
   </si>
   <si>
+    <t>Natirae H/C III</t>
+  </si>
+  <si>
+    <t>Alone village/Natirae primary school catchment area</t>
+  </si>
+  <si>
     <t>Lemusui trading centre</t>
   </si>
   <si>
@@ -1376,6 +1382,12 @@
   </si>
   <si>
     <t>Peter achia, Michael Lochuge and Raphael Longole</t>
+  </si>
+  <si>
+    <t>Lochuge Michael, Longole Rapheal and Achia Peter</t>
+  </si>
+  <si>
+    <t>Lochuge Michael,Longole Rapheal and Achia Peter</t>
   </si>
   <si>
     <t>Cheptoo Evaline and cherotich Catherine</t>
@@ -1865,7 +1877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J284"/>
+  <dimension ref="A1:J286"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1920,13 +1932,13 @@
         <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="I2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J2">
         <v>152</v>
@@ -1952,13 +1964,13 @@
         <v>83</v>
       </c>
       <c r="G3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I3" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J3">
         <v>176</v>
@@ -1984,13 +1996,13 @@
         <v>84</v>
       </c>
       <c r="G4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I4" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J4">
         <v>168</v>
@@ -2016,13 +2028,13 @@
         <v>85</v>
       </c>
       <c r="G5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H5" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="I5" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J5">
         <v>238</v>
@@ -2048,13 +2060,13 @@
         <v>86</v>
       </c>
       <c r="G6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I6" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J6">
         <v>230</v>
@@ -2080,13 +2092,13 @@
         <v>87</v>
       </c>
       <c r="G7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="I7" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J7">
         <v>164</v>
@@ -2112,13 +2124,13 @@
         <v>88</v>
       </c>
       <c r="G8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I8" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J8">
         <v>222</v>
@@ -2144,13 +2156,13 @@
         <v>89</v>
       </c>
       <c r="G9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="I9" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J9">
         <v>142</v>
@@ -2176,13 +2188,13 @@
         <v>90</v>
       </c>
       <c r="G10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I10" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J10">
         <v>172</v>
@@ -2208,13 +2220,13 @@
         <v>91</v>
       </c>
       <c r="G11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I11" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J11">
         <v>83</v>
@@ -2240,13 +2252,13 @@
         <v>92</v>
       </c>
       <c r="G12" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I12" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J12">
         <v>91</v>
@@ -2272,13 +2284,13 @@
         <v>93</v>
       </c>
       <c r="G13" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I13" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J13">
         <v>123</v>
@@ -2304,13 +2316,13 @@
         <v>94</v>
       </c>
       <c r="G14" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H14" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="I14" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="J14">
         <v>88</v>
@@ -2336,13 +2348,13 @@
         <v>95</v>
       </c>
       <c r="G15" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="I15" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="J15">
         <v>144</v>
@@ -2368,13 +2380,13 @@
         <v>96</v>
       </c>
       <c r="G16" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H16" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I16" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J16">
         <v>235</v>
@@ -2400,13 +2412,13 @@
         <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H17" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="I17" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J17">
         <v>136</v>
@@ -2432,13 +2444,13 @@
         <v>97</v>
       </c>
       <c r="G18" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H18" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="I18" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J18">
         <v>154</v>
@@ -2464,13 +2476,13 @@
         <v>97</v>
       </c>
       <c r="G19" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="I19" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J19">
         <v>161</v>
@@ -2496,13 +2508,13 @@
         <v>98</v>
       </c>
       <c r="G20" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H20" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I20" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J20">
         <v>185</v>
@@ -2528,13 +2540,13 @@
         <v>99</v>
       </c>
       <c r="G21" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H21" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I21" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J21">
         <v>146</v>
@@ -2560,13 +2572,13 @@
         <v>99</v>
       </c>
       <c r="G22" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H22" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="I22" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J22">
         <v>174</v>
@@ -2592,13 +2604,13 @@
         <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H23" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="I23" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J23">
         <v>133</v>
@@ -2624,13 +2636,13 @@
         <v>101</v>
       </c>
       <c r="G24" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H24" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I24" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J24">
         <v>126</v>
@@ -2656,13 +2668,13 @@
         <v>102</v>
       </c>
       <c r="G25" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H25" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I25" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J25">
         <v>131</v>
@@ -2688,13 +2700,13 @@
         <v>103</v>
       </c>
       <c r="G26" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H26" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I26" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J26">
         <v>151</v>
@@ -2720,13 +2732,13 @@
         <v>103</v>
       </c>
       <c r="G27" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H27" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I27" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J27">
         <v>144</v>
@@ -2752,13 +2764,13 @@
         <v>103</v>
       </c>
       <c r="G28" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H28" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I28" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J28">
         <v>158</v>
@@ -2784,13 +2796,13 @@
         <v>103</v>
       </c>
       <c r="G29" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H29" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I29" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J29">
         <v>128</v>
@@ -2816,13 +2828,13 @@
         <v>103</v>
       </c>
       <c r="G30" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H30" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I30" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J30">
         <v>176</v>
@@ -2848,13 +2860,13 @@
         <v>104</v>
       </c>
       <c r="G31" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I31" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J31">
         <v>141</v>
@@ -2880,13 +2892,13 @@
         <v>105</v>
       </c>
       <c r="G32" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H32" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I32" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J32">
         <v>124</v>
@@ -2912,13 +2924,13 @@
         <v>105</v>
       </c>
       <c r="G33" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H33" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I33" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J33">
         <v>158</v>
@@ -2944,13 +2956,13 @@
         <v>105</v>
       </c>
       <c r="G34" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H34" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I34" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J34">
         <v>142</v>
@@ -2976,13 +2988,13 @@
         <v>106</v>
       </c>
       <c r="G35" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H35" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I35" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J35">
         <v>120</v>
@@ -3008,13 +3020,13 @@
         <v>107</v>
       </c>
       <c r="G36" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H36" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I36" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J36">
         <v>146</v>
@@ -3040,13 +3052,13 @@
         <v>108</v>
       </c>
       <c r="G37" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H37" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I37" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J37">
         <v>173</v>
@@ -3072,13 +3084,13 @@
         <v>109</v>
       </c>
       <c r="G38" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H38" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I38" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J38">
         <v>135</v>
@@ -3104,13 +3116,13 @@
         <v>108</v>
       </c>
       <c r="G39" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H39" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I39" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J39">
         <v>154</v>
@@ -3136,13 +3148,13 @@
         <v>110</v>
       </c>
       <c r="G40" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H40" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I40" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J40">
         <v>168</v>
@@ -3168,13 +3180,13 @@
         <v>110</v>
       </c>
       <c r="G41" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H41" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I41" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J41">
         <v>161</v>
@@ -3200,13 +3212,13 @@
         <v>110</v>
       </c>
       <c r="G42" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H42" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I42" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J42">
         <v>176</v>
@@ -3232,13 +3244,13 @@
         <v>110</v>
       </c>
       <c r="G43" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H43" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I43" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J43">
         <v>132</v>
@@ -3264,13 +3276,13 @@
         <v>111</v>
       </c>
       <c r="G44" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H44" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I44" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J44">
         <v>223</v>
@@ -3296,13 +3308,13 @@
         <v>112</v>
       </c>
       <c r="G45" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H45" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I45" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J45">
         <v>60</v>
@@ -3328,13 +3340,13 @@
         <v>112</v>
       </c>
       <c r="G46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H46" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I46" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J46">
         <v>82</v>
@@ -3360,13 +3372,13 @@
         <v>113</v>
       </c>
       <c r="G47" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H47" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I47" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J47">
         <v>71</v>
@@ -3392,13 +3404,13 @@
         <v>112</v>
       </c>
       <c r="G48" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H48" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I48" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J48">
         <v>50</v>
@@ -3424,13 +3436,13 @@
         <v>112</v>
       </c>
       <c r="G49" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H49" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I49" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J49">
         <v>86</v>
@@ -3456,13 +3468,13 @@
         <v>114</v>
       </c>
       <c r="G50" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H50" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I50" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J50">
         <v>79</v>
@@ -3488,13 +3500,13 @@
         <v>115</v>
       </c>
       <c r="G51" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H51" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I51" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J51">
         <v>90</v>
@@ -3520,13 +3532,13 @@
         <v>116</v>
       </c>
       <c r="G52" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H52" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I52" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J52">
         <v>48</v>
@@ -3552,13 +3564,13 @@
         <v>113</v>
       </c>
       <c r="G53" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H53" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="I53" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J53">
         <v>83</v>
@@ -3584,13 +3596,13 @@
         <v>117</v>
       </c>
       <c r="G54" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H54" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I54" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J54">
         <v>79</v>
@@ -3616,13 +3628,13 @@
         <v>118</v>
       </c>
       <c r="G55" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H55" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I55" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J55">
         <v>89</v>
@@ -3648,13 +3660,13 @@
         <v>119</v>
       </c>
       <c r="G56" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H56" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I56" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J56">
         <v>74</v>
@@ -3680,13 +3692,13 @@
         <v>120</v>
       </c>
       <c r="G57" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H57" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="I57" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J57">
         <v>97</v>
@@ -3712,13 +3724,13 @@
         <v>121</v>
       </c>
       <c r="G58" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H58" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I58" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J58">
         <v>146</v>
@@ -3744,13 +3756,13 @@
         <v>122</v>
       </c>
       <c r="G59" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H59" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I59" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J59">
         <v>105</v>
@@ -3776,13 +3788,13 @@
         <v>123</v>
       </c>
       <c r="G60" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H60" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I60" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J60">
         <v>95</v>
@@ -3808,13 +3820,13 @@
         <v>124</v>
       </c>
       <c r="G61" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H61" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="I61" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J61">
         <v>93</v>
@@ -3840,13 +3852,13 @@
         <v>125</v>
       </c>
       <c r="G62" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H62" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I62" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J62">
         <v>118</v>
@@ -3872,13 +3884,13 @@
         <v>126</v>
       </c>
       <c r="G63" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H63" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I63" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J63">
         <v>182</v>
@@ -3904,13 +3916,13 @@
         <v>127</v>
       </c>
       <c r="G64" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H64" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I64" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J64">
         <v>123</v>
@@ -3936,13 +3948,13 @@
         <v>128</v>
       </c>
       <c r="G65" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H65" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="I65" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J65">
         <v>80</v>
@@ -3968,13 +3980,13 @@
         <v>129</v>
       </c>
       <c r="G66" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H66" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="I66" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J66">
         <v>74</v>
@@ -4000,13 +4012,13 @@
         <v>130</v>
       </c>
       <c r="G67" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H67" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I67" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J67">
         <v>75</v>
@@ -4032,13 +4044,13 @@
         <v>131</v>
       </c>
       <c r="G68" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H68" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I68" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J68">
         <v>78</v>
@@ -4064,13 +4076,13 @@
         <v>132</v>
       </c>
       <c r="G69" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H69" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="I69" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J69">
         <v>77</v>
@@ -4096,13 +4108,13 @@
         <v>131</v>
       </c>
       <c r="G70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H70" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I70" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J70">
         <v>78</v>
@@ -4128,13 +4140,13 @@
         <v>130</v>
       </c>
       <c r="G71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H71" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I71" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J71">
         <v>72</v>
@@ -4160,13 +4172,13 @@
         <v>133</v>
       </c>
       <c r="G72" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H72" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I72" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J72">
         <v>80</v>
@@ -4192,13 +4204,13 @@
         <v>134</v>
       </c>
       <c r="G73" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H73" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I73" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J73">
         <v>68</v>
@@ -4224,13 +4236,13 @@
         <v>135</v>
       </c>
       <c r="G74" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H74" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I74" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J74">
         <v>69</v>
@@ -4256,13 +4268,13 @@
         <v>136</v>
       </c>
       <c r="G75" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H75" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="I75" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J75">
         <v>80</v>
@@ -4288,13 +4300,13 @@
         <v>137</v>
       </c>
       <c r="G76" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H76" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="I76" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J76">
         <v>69</v>
@@ -4320,13 +4332,13 @@
         <v>138</v>
       </c>
       <c r="G77" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H77" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I77" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J77">
         <v>113</v>
@@ -4352,13 +4364,13 @@
         <v>139</v>
       </c>
       <c r="G78" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H78" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="I78" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J78">
         <v>107</v>
@@ -4384,13 +4396,13 @@
         <v>140</v>
       </c>
       <c r="G79" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H79" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I79" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J79">
         <v>117</v>
@@ -4416,13 +4428,13 @@
         <v>141</v>
       </c>
       <c r="G80" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I80" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J80">
         <v>93</v>
@@ -4448,13 +4460,13 @@
         <v>142</v>
       </c>
       <c r="G81" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H81" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I81" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J81">
         <v>127</v>
@@ -4480,13 +4492,13 @@
         <v>143</v>
       </c>
       <c r="G82" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H82" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I82" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J82">
         <v>107</v>
@@ -4512,13 +4524,13 @@
         <v>144</v>
       </c>
       <c r="G83" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H83" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I83" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J83">
         <v>118</v>
@@ -4544,13 +4556,13 @@
         <v>145</v>
       </c>
       <c r="G84" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H84" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I84" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J84">
         <v>103</v>
@@ -4576,13 +4588,13 @@
         <v>146</v>
       </c>
       <c r="G85" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H85" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="I85" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J85">
         <v>117</v>
@@ -4608,13 +4620,13 @@
         <v>147</v>
       </c>
       <c r="G86" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H86" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I86" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J86">
         <v>226</v>
@@ -4640,13 +4652,13 @@
         <v>148</v>
       </c>
       <c r="G87" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H87" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I87" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J87">
         <v>114</v>
@@ -4672,13 +4684,13 @@
         <v>149</v>
       </c>
       <c r="G88" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H88" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="I88" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J88">
         <v>162</v>
@@ -4704,13 +4716,13 @@
         <v>150</v>
       </c>
       <c r="G89" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H89" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I89" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J89">
         <v>143</v>
@@ -4736,13 +4748,13 @@
         <v>151</v>
       </c>
       <c r="G90" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H90" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I90" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J90">
         <v>132</v>
@@ -4768,13 +4780,13 @@
         <v>152</v>
       </c>
       <c r="G91" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H91" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I91" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J91">
         <v>136</v>
@@ -4800,13 +4812,13 @@
         <v>153</v>
       </c>
       <c r="G92" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H92" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I92" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J92">
         <v>97</v>
@@ -4832,13 +4844,13 @@
         <v>154</v>
       </c>
       <c r="G93" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H93" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I93" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J93">
         <v>244</v>
@@ -4864,13 +4876,13 @@
         <v>151</v>
       </c>
       <c r="G94" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H94" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I94" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J94">
         <v>132</v>
@@ -4896,13 +4908,13 @@
         <v>155</v>
       </c>
       <c r="G95" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H95" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I95" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J95">
         <v>429</v>
@@ -4928,13 +4940,13 @@
         <v>156</v>
       </c>
       <c r="G96" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H96" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="I96" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J96">
         <v>478</v>
@@ -4960,13 +4972,13 @@
         <v>157</v>
       </c>
       <c r="G97" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H97" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I97" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J97">
         <v>517</v>
@@ -4992,13 +5004,13 @@
         <v>158</v>
       </c>
       <c r="G98" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H98" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I98" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J98">
         <v>148</v>
@@ -5024,13 +5036,13 @@
         <v>159</v>
       </c>
       <c r="G99" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H99" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I99" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J99">
         <v>109</v>
@@ -5056,13 +5068,13 @@
         <v>160</v>
       </c>
       <c r="G100" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H100" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I100" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J100">
         <v>90</v>
@@ -5088,13 +5100,13 @@
         <v>161</v>
       </c>
       <c r="G101" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H101" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I101" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J101">
         <v>136</v>
@@ -5120,13 +5132,13 @@
         <v>162</v>
       </c>
       <c r="G102" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H102" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I102" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J102">
         <v>119</v>
@@ -5152,13 +5164,13 @@
         <v>163</v>
       </c>
       <c r="G103" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H103" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I103" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J103">
         <v>59</v>
@@ -5184,13 +5196,13 @@
         <v>164</v>
       </c>
       <c r="G104" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H104" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I104" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J104">
         <v>134</v>
@@ -5216,13 +5228,13 @@
         <v>165</v>
       </c>
       <c r="G105" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H105" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="I105" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J105">
         <v>88</v>
@@ -5248,13 +5260,13 @@
         <v>166</v>
       </c>
       <c r="G106" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H106" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="I106" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J106">
         <v>99</v>
@@ -5280,13 +5292,13 @@
         <v>167</v>
       </c>
       <c r="G107" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H107" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="I107" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J107">
         <v>102</v>
@@ -5312,13 +5324,13 @@
         <v>164</v>
       </c>
       <c r="G108" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H108" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I108" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J108">
         <v>77</v>
@@ -5344,13 +5356,13 @@
         <v>167</v>
       </c>
       <c r="G109" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H109" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I109" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J109">
         <v>72</v>
@@ -5376,13 +5388,13 @@
         <v>168</v>
       </c>
       <c r="G110" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H110" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I110" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J110">
         <v>88</v>
@@ -5408,13 +5420,13 @@
         <v>169</v>
       </c>
       <c r="G111" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H111" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="I111" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J111">
         <v>369</v>
@@ -5440,13 +5452,13 @@
         <v>170</v>
       </c>
       <c r="G112" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H112" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I112" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J112">
         <v>504</v>
@@ -5472,13 +5484,13 @@
         <v>171</v>
       </c>
       <c r="G113" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H113" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I113" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J113">
         <v>443</v>
@@ -5504,13 +5516,13 @@
         <v>172</v>
       </c>
       <c r="G114" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H114" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I114" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J114">
         <v>347</v>
@@ -5536,13 +5548,13 @@
         <v>173</v>
       </c>
       <c r="G115" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H115" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I115" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J115">
         <v>290</v>
@@ -5568,13 +5580,13 @@
         <v>174</v>
       </c>
       <c r="G116" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H116" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I116" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J116">
         <v>292</v>
@@ -5600,13 +5612,13 @@
         <v>175</v>
       </c>
       <c r="G117" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H117" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I117" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J117">
         <v>136</v>
@@ -5632,13 +5644,13 @@
         <v>176</v>
       </c>
       <c r="G118" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H118" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="I118" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J118">
         <v>216</v>
@@ -5664,13 +5676,13 @@
         <v>177</v>
       </c>
       <c r="G119" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H119" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I119" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J119">
         <v>130</v>
@@ -5696,13 +5708,13 @@
         <v>178</v>
       </c>
       <c r="G120" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H120" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I120" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J120">
         <v>145</v>
@@ -5728,13 +5740,13 @@
         <v>179</v>
       </c>
       <c r="G121" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H121" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="I121" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J121">
         <v>139</v>
@@ -5760,13 +5772,13 @@
         <v>179</v>
       </c>
       <c r="G122" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H122" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I122" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J122">
         <v>198</v>
@@ -5792,13 +5804,13 @@
         <v>179</v>
       </c>
       <c r="G123" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H123" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I123" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J123">
         <v>183</v>
@@ -5824,13 +5836,13 @@
         <v>180</v>
       </c>
       <c r="G124" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H124" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I124" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J124">
         <v>155</v>
@@ -5856,13 +5868,13 @@
         <v>181</v>
       </c>
       <c r="G125" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H125" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="I125" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J125">
         <v>172</v>
@@ -5888,13 +5900,13 @@
         <v>182</v>
       </c>
       <c r="G126" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H126" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I126" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J126">
         <v>306</v>
@@ -5920,13 +5932,13 @@
         <v>183</v>
       </c>
       <c r="G127" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H127" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="I127" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J127">
         <v>221</v>
@@ -5952,13 +5964,13 @@
         <v>184</v>
       </c>
       <c r="G128" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H128" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I128" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J128">
         <v>221</v>
@@ -5984,13 +5996,13 @@
         <v>185</v>
       </c>
       <c r="G129" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H129" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I129" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J129">
         <v>464</v>
@@ -6016,13 +6028,13 @@
         <v>186</v>
       </c>
       <c r="G130" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H130" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I130" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J130">
         <v>409</v>
@@ -6048,13 +6060,13 @@
         <v>187</v>
       </c>
       <c r="G131" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H131" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I131" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J131">
         <v>219</v>
@@ -6080,13 +6092,13 @@
         <v>188</v>
       </c>
       <c r="G132" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H132" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I132" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J132">
         <v>194</v>
@@ -6112,13 +6124,13 @@
         <v>189</v>
       </c>
       <c r="G133" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H133" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I133" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J133">
         <v>263</v>
@@ -6144,13 +6156,13 @@
         <v>190</v>
       </c>
       <c r="G134" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H134" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I134" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J134">
         <v>260</v>
@@ -6176,13 +6188,13 @@
         <v>191</v>
       </c>
       <c r="G135" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H135" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I135" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J135">
         <v>313</v>
@@ -6208,13 +6220,13 @@
         <v>192</v>
       </c>
       <c r="G136" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H136" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I136" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J136">
         <v>298</v>
@@ -6240,13 +6252,13 @@
         <v>193</v>
       </c>
       <c r="G137" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H137" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I137" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J137">
         <v>183</v>
@@ -6272,13 +6284,13 @@
         <v>194</v>
       </c>
       <c r="G138" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H138" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="I138" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J138">
         <v>167</v>
@@ -6304,13 +6316,13 @@
         <v>195</v>
       </c>
       <c r="G139" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H139" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I139" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J139">
         <v>155</v>
@@ -6336,13 +6348,13 @@
         <v>196</v>
       </c>
       <c r="G140" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H140" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I140" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J140">
         <v>142</v>
@@ -6368,13 +6380,13 @@
         <v>197</v>
       </c>
       <c r="G141" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H141" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="I141" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J141">
         <v>126</v>
@@ -6400,13 +6412,13 @@
         <v>198</v>
       </c>
       <c r="G142" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H142" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I142" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J142">
         <v>141</v>
@@ -6432,13 +6444,13 @@
         <v>199</v>
       </c>
       <c r="G143" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H143" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I143" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J143">
         <v>171</v>
@@ -6464,13 +6476,13 @@
         <v>200</v>
       </c>
       <c r="G144" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H144" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I144" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J144">
         <v>166</v>
@@ -6496,13 +6508,13 @@
         <v>201</v>
       </c>
       <c r="G145" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H145" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I145" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J145">
         <v>153</v>
@@ -6528,13 +6540,13 @@
         <v>202</v>
       </c>
       <c r="G146" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H146" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I146" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J146">
         <v>157</v>
@@ -6560,13 +6572,13 @@
         <v>203</v>
       </c>
       <c r="G147" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I147" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J147">
         <v>191</v>
@@ -6592,13 +6604,13 @@
         <v>204</v>
       </c>
       <c r="G148" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I148" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J148">
         <v>137</v>
@@ -6624,13 +6636,13 @@
         <v>205</v>
       </c>
       <c r="G149" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I149" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J149">
         <v>172</v>
@@ -6656,13 +6668,13 @@
         <v>206</v>
       </c>
       <c r="G150" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H150" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I150" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J150">
         <v>167</v>
@@ -6688,13 +6700,13 @@
         <v>207</v>
       </c>
       <c r="G151" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H151" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I151" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J151">
         <v>107</v>
@@ -6720,13 +6732,13 @@
         <v>208</v>
       </c>
       <c r="G152" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H152" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I152" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J152">
         <v>190</v>
@@ -6752,13 +6764,13 @@
         <v>209</v>
       </c>
       <c r="G153" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H153" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="I153" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J153">
         <v>240</v>
@@ -6784,13 +6796,13 @@
         <v>210</v>
       </c>
       <c r="G154" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H154" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="I154" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J154">
         <v>206</v>
@@ -6816,13 +6828,13 @@
         <v>211</v>
       </c>
       <c r="G155" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H155" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I155" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J155">
         <v>216</v>
@@ -6848,13 +6860,13 @@
         <v>212</v>
       </c>
       <c r="G156" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H156" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I156" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J156">
         <v>77</v>
@@ -6880,13 +6892,13 @@
         <v>213</v>
       </c>
       <c r="G157" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H157" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="I157" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J157">
         <v>73</v>
@@ -6912,13 +6924,13 @@
         <v>214</v>
       </c>
       <c r="G158" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H158" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I158" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J158">
         <v>66</v>
@@ -6944,13 +6956,13 @@
         <v>215</v>
       </c>
       <c r="G159" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H159" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I159" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J159">
         <v>58</v>
@@ -6976,13 +6988,13 @@
         <v>216</v>
       </c>
       <c r="G160" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H160" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I160" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J160">
         <v>73</v>
@@ -7008,13 +7020,13 @@
         <v>215</v>
       </c>
       <c r="G161" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H161" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="I161" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J161">
         <v>61</v>
@@ -7040,13 +7052,13 @@
         <v>215</v>
       </c>
       <c r="G162" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H162" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="I162" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J162">
         <v>65</v>
@@ -7072,13 +7084,13 @@
         <v>217</v>
       </c>
       <c r="G163" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H163" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="I163" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J163">
         <v>62</v>
@@ -7104,13 +7116,13 @@
         <v>218</v>
       </c>
       <c r="G164" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H164" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I164" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J164">
         <v>63</v>
@@ -7136,13 +7148,13 @@
         <v>219</v>
       </c>
       <c r="G165" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H165" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="I165" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J165">
         <v>58</v>
@@ -7168,13 +7180,13 @@
         <v>220</v>
       </c>
       <c r="G166" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H166" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="I166" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J166">
         <v>67</v>
@@ -7200,13 +7212,13 @@
         <v>221</v>
       </c>
       <c r="G167" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H167" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="I167" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J167">
         <v>69</v>
@@ -7232,13 +7244,13 @@
         <v>222</v>
       </c>
       <c r="G168" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H168" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="I168" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J168">
         <v>71</v>
@@ -7264,13 +7276,13 @@
         <v>223</v>
       </c>
       <c r="G169" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H169" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I169" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J169">
         <v>84</v>
@@ -7296,13 +7308,13 @@
         <v>224</v>
       </c>
       <c r="G170" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H170" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="I170" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J170">
         <v>74</v>
@@ -7328,13 +7340,13 @@
         <v>225</v>
       </c>
       <c r="G171" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H171" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="I171" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J171">
         <v>75</v>
@@ -7360,13 +7372,13 @@
         <v>226</v>
       </c>
       <c r="G172" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H172" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I172" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J172">
         <v>65</v>
@@ -7392,13 +7404,13 @@
         <v>227</v>
       </c>
       <c r="G173" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H173" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="I173" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J173">
         <v>65</v>
@@ -7424,13 +7436,13 @@
         <v>228</v>
       </c>
       <c r="G174" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H174" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I174" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J174">
         <v>81</v>
@@ -7456,13 +7468,13 @@
         <v>229</v>
       </c>
       <c r="G175" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H175" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="I175" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J175">
         <v>84</v>
@@ -7488,13 +7500,13 @@
         <v>230</v>
       </c>
       <c r="G176" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H176" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="I176" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J176">
         <v>65</v>
@@ -7520,13 +7532,13 @@
         <v>231</v>
       </c>
       <c r="G177" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H177" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="I177" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J177">
         <v>63</v>
@@ -7552,13 +7564,13 @@
         <v>232</v>
       </c>
       <c r="G178" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H178" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="I178" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J178">
         <v>75</v>
@@ -7584,13 +7596,13 @@
         <v>212</v>
       </c>
       <c r="G179" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H179" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="I179" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J179">
         <v>67</v>
@@ -7616,13 +7628,13 @@
         <v>233</v>
       </c>
       <c r="G180" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H180" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I180" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J180">
         <v>91</v>
@@ -7648,13 +7660,13 @@
         <v>230</v>
       </c>
       <c r="G181" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H181" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I181" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J181">
         <v>64</v>
@@ -7680,13 +7692,13 @@
         <v>234</v>
       </c>
       <c r="G182" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H182" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I182" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J182">
         <v>62</v>
@@ -7712,13 +7724,13 @@
         <v>235</v>
       </c>
       <c r="G183" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H183" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="I183" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J183">
         <v>68</v>
@@ -7744,13 +7756,13 @@
         <v>236</v>
       </c>
       <c r="G184" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H184" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="I184" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J184">
         <v>81</v>
@@ -7776,13 +7788,13 @@
         <v>237</v>
       </c>
       <c r="G185" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H185" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="I185" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J185">
         <v>60</v>
@@ -7808,13 +7820,13 @@
         <v>235</v>
       </c>
       <c r="G186" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H186" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="I186" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J186">
         <v>80</v>
@@ -7840,13 +7852,13 @@
         <v>238</v>
       </c>
       <c r="G187" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H187" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="I187" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="J187">
         <v>55</v>
@@ -7872,13 +7884,13 @@
         <v>239</v>
       </c>
       <c r="G188" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H188" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="I188" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J188">
         <v>190</v>
@@ -7904,13 +7916,13 @@
         <v>240</v>
       </c>
       <c r="G189" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H189" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I189" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J189">
         <v>95</v>
@@ -7936,13 +7948,13 @@
         <v>241</v>
       </c>
       <c r="G190" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H190" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="I190" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J190">
         <v>90</v>
@@ -7968,13 +7980,13 @@
         <v>242</v>
       </c>
       <c r="G191" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H191" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="I191" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J191">
         <v>110</v>
@@ -8000,13 +8012,13 @@
         <v>243</v>
       </c>
       <c r="G192" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H192" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="I192" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J192">
         <v>169</v>
@@ -8032,13 +8044,13 @@
         <v>244</v>
       </c>
       <c r="G193" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H193" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="I193" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J193">
         <v>101</v>
@@ -8064,13 +8076,13 @@
         <v>245</v>
       </c>
       <c r="G194" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H194" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="I194" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J194">
         <v>110</v>
@@ -8096,13 +8108,13 @@
         <v>246</v>
       </c>
       <c r="G195" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H195" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I195" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J195">
         <v>109</v>
@@ -8128,13 +8140,13 @@
         <v>247</v>
       </c>
       <c r="G196" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H196" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I196" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J196">
         <v>102</v>
@@ -8160,13 +8172,13 @@
         <v>248</v>
       </c>
       <c r="G197" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H197" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I197" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J197">
         <v>91</v>
@@ -8192,13 +8204,13 @@
         <v>249</v>
       </c>
       <c r="G198" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H198" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="I198" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J198">
         <v>108</v>
@@ -8224,13 +8236,13 @@
         <v>250</v>
       </c>
       <c r="G199" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H199" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="I199" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J199">
         <v>96</v>
@@ -8256,13 +8268,13 @@
         <v>251</v>
       </c>
       <c r="G200" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H200" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I200" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J200">
         <v>97</v>
@@ -8288,13 +8300,13 @@
         <v>252</v>
       </c>
       <c r="G201" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H201" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I201" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J201">
         <v>94</v>
@@ -8320,13 +8332,13 @@
         <v>252</v>
       </c>
       <c r="G202" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H202" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I202" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J202">
         <v>81</v>
@@ -8352,13 +8364,13 @@
         <v>253</v>
       </c>
       <c r="G203" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H203" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="I203" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J203">
         <v>192</v>
@@ -8384,13 +8396,13 @@
         <v>254</v>
       </c>
       <c r="G204" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H204" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="I204" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J204">
         <v>105</v>
@@ -8416,13 +8428,13 @@
         <v>254</v>
       </c>
       <c r="G205" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H205" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I205" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="J205">
         <v>105</v>
@@ -8430,74 +8442,74 @@
     </row>
     <row r="206" spans="1:10">
       <c r="A206">
-        <v>151</v>
+        <v>583</v>
       </c>
       <c r="B206" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C206" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D206" t="s">
         <v>32</v>
       </c>
       <c r="E206" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F206" t="s">
         <v>255</v>
       </c>
       <c r="G206" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H206" t="s">
-        <v>342</v>
+        <v>456</v>
       </c>
       <c r="I206" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J206">
-        <v>63</v>
+        <v>110</v>
       </c>
     </row>
     <row r="207" spans="1:10">
       <c r="A207">
-        <v>445</v>
+        <v>584</v>
       </c>
       <c r="B207" t="s">
         <v>14</v>
       </c>
       <c r="C207" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D207" t="s">
         <v>32</v>
       </c>
       <c r="E207" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F207" t="s">
         <v>256</v>
       </c>
       <c r="G207" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H207" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="I207" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="J207">
-        <v>81</v>
+        <v>111</v>
       </c>
     </row>
     <row r="208" spans="1:10">
       <c r="A208">
-        <v>527</v>
+        <v>151</v>
       </c>
       <c r="B208" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C208" t="s">
         <v>30</v>
@@ -8512,24 +8524,24 @@
         <v>257</v>
       </c>
       <c r="G208" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H208" t="s">
-        <v>455</v>
+        <v>344</v>
       </c>
       <c r="I208" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J208">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="209" spans="1:10">
       <c r="A209">
-        <v>528</v>
+        <v>445</v>
       </c>
       <c r="B209" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C209" t="s">
         <v>30</v>
@@ -8544,21 +8556,21 @@
         <v>258</v>
       </c>
       <c r="G209" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H209" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="I209" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J209">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="210" spans="1:10">
       <c r="A210">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B210" t="s">
         <v>16</v>
@@ -8576,21 +8588,21 @@
         <v>259</v>
       </c>
       <c r="G210" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H210" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="I210" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J210">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="211" spans="1:10">
       <c r="A211">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B211" t="s">
         <v>16</v>
@@ -8608,24 +8620,24 @@
         <v>260</v>
       </c>
       <c r="G211" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H211" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="I211" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J211">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="212" spans="1:10">
       <c r="A212">
-        <v>438</v>
+        <v>529</v>
       </c>
       <c r="B212" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C212" t="s">
         <v>30</v>
@@ -8634,30 +8646,30 @@
         <v>32</v>
       </c>
       <c r="E212" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F212" t="s">
         <v>261</v>
       </c>
       <c r="G212" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H212" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="I212" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J212">
-        <v>95</v>
+        <v>74</v>
       </c>
     </row>
     <row r="213" spans="1:10">
       <c r="A213">
-        <v>441</v>
+        <v>531</v>
       </c>
       <c r="B213" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C213" t="s">
         <v>30</v>
@@ -8666,27 +8678,27 @@
         <v>32</v>
       </c>
       <c r="E213" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F213" t="s">
         <v>262</v>
       </c>
       <c r="G213" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H213" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I213" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J213">
-        <v>129</v>
+        <v>75</v>
       </c>
     </row>
     <row r="214" spans="1:10">
       <c r="A214">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B214" t="s">
         <v>14</v>
@@ -8704,21 +8716,21 @@
         <v>263</v>
       </c>
       <c r="G214" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H214" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="I214" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J214">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="215" spans="1:10">
       <c r="A215">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B215" t="s">
         <v>14</v>
@@ -8736,24 +8748,24 @@
         <v>264</v>
       </c>
       <c r="G215" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H215" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="I215" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J215">
-        <v>107</v>
+        <v>129</v>
       </c>
     </row>
     <row r="216" spans="1:10">
       <c r="A216">
-        <v>533</v>
+        <v>443</v>
       </c>
       <c r="B216" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C216" t="s">
         <v>30</v>
@@ -8768,24 +8780,24 @@
         <v>265</v>
       </c>
       <c r="G216" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H216" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="I216" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J216">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="217" spans="1:10">
       <c r="A217">
-        <v>492</v>
+        <v>444</v>
       </c>
       <c r="B217" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C217" t="s">
         <v>30</v>
@@ -8794,27 +8806,27 @@
         <v>32</v>
       </c>
       <c r="E217" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F217" t="s">
         <v>266</v>
       </c>
       <c r="G217" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H217" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="I217" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J217">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="218" spans="1:10">
       <c r="A218">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="B218" t="s">
         <v>16</v>
@@ -8826,27 +8838,27 @@
         <v>32</v>
       </c>
       <c r="E218" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F218" t="s">
         <v>267</v>
       </c>
       <c r="G218" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H218" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I218" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J218">
-        <v>102</v>
+        <v>72</v>
       </c>
     </row>
     <row r="219" spans="1:10">
       <c r="A219">
-        <v>523</v>
+        <v>492</v>
       </c>
       <c r="B219" t="s">
         <v>16</v>
@@ -8864,21 +8876,21 @@
         <v>268</v>
       </c>
       <c r="G219" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H219" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I219" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J219">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="220" spans="1:10">
       <c r="A220">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="B220" t="s">
         <v>16</v>
@@ -8896,21 +8908,21 @@
         <v>269</v>
       </c>
       <c r="G220" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H220" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="I220" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J220">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="221" spans="1:10">
       <c r="A221">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B221" t="s">
         <v>16</v>
@@ -8928,24 +8940,24 @@
         <v>270</v>
       </c>
       <c r="G221" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H221" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="I221" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J221">
-        <v>94</v>
+        <v>122</v>
       </c>
     </row>
     <row r="222" spans="1:10">
       <c r="A222">
-        <v>236</v>
+        <v>525</v>
       </c>
       <c r="B222" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C222" t="s">
         <v>30</v>
@@ -8954,30 +8966,30 @@
         <v>32</v>
       </c>
       <c r="E222" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F222" t="s">
         <v>271</v>
       </c>
       <c r="G222" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H222" t="s">
-        <v>342</v>
+        <v>466</v>
       </c>
       <c r="I222" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J222">
-        <v>67</v>
+        <v>104</v>
       </c>
     </row>
     <row r="223" spans="1:10">
       <c r="A223">
-        <v>237</v>
+        <v>526</v>
       </c>
       <c r="B223" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C223" t="s">
         <v>30</v>
@@ -8986,30 +8998,30 @@
         <v>32</v>
       </c>
       <c r="E223" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F223" t="s">
         <v>272</v>
       </c>
       <c r="G223" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H223" t="s">
-        <v>342</v>
+        <v>466</v>
       </c>
       <c r="I223" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J223">
-        <v>69</v>
+        <v>94</v>
       </c>
     </row>
     <row r="224" spans="1:10">
       <c r="A224">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="B224" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C224" t="s">
         <v>30</v>
@@ -9024,24 +9036,24 @@
         <v>273</v>
       </c>
       <c r="G224" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H224" t="s">
-        <v>463</v>
+        <v>344</v>
       </c>
       <c r="I224" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J224">
-        <v>111</v>
+        <v>67</v>
       </c>
     </row>
     <row r="225" spans="1:10">
       <c r="A225">
-        <v>301</v>
+        <v>237</v>
       </c>
       <c r="B225" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C225" t="s">
         <v>30</v>
@@ -9056,24 +9068,24 @@
         <v>274</v>
       </c>
       <c r="G225" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="H225" t="s">
-        <v>463</v>
+        <v>344</v>
       </c>
       <c r="I225" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J225">
-        <v>84</v>
+        <v>69</v>
       </c>
     </row>
     <row r="226" spans="1:10">
       <c r="A226">
-        <v>413</v>
+        <v>260</v>
       </c>
       <c r="B226" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C226" t="s">
         <v>30</v>
@@ -9088,24 +9100,24 @@
         <v>275</v>
       </c>
       <c r="G226" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H226" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="I226" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J226">
-        <v>66</v>
+        <v>111</v>
       </c>
     </row>
     <row r="227" spans="1:10">
       <c r="A227">
-        <v>532</v>
+        <v>301</v>
       </c>
       <c r="B227" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C227" t="s">
         <v>30</v>
@@ -9120,24 +9132,24 @@
         <v>276</v>
       </c>
       <c r="G227" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H227" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="I227" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J227">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="228" spans="1:10">
       <c r="A228">
-        <v>193</v>
+        <v>413</v>
       </c>
       <c r="B228" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C228" t="s">
         <v>30</v>
@@ -9146,30 +9158,30 @@
         <v>32</v>
       </c>
       <c r="E228" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F228" t="s">
         <v>277</v>
       </c>
       <c r="G228" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H228" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I228" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J228">
-        <v>167</v>
+        <v>66</v>
       </c>
     </row>
     <row r="229" spans="1:10">
       <c r="A229">
-        <v>300</v>
+        <v>532</v>
       </c>
       <c r="B229" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C229" t="s">
         <v>30</v>
@@ -9178,30 +9190,30 @@
         <v>32</v>
       </c>
       <c r="E229" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F229" t="s">
         <v>278</v>
       </c>
       <c r="G229" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H229" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I229" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J229">
-        <v>149</v>
+        <v>82</v>
       </c>
     </row>
     <row r="230" spans="1:10">
       <c r="A230">
-        <v>304</v>
+        <v>193</v>
       </c>
       <c r="B230" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C230" t="s">
         <v>30</v>
@@ -9216,24 +9228,24 @@
         <v>279</v>
       </c>
       <c r="G230" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H230" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I230" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J230">
-        <v>200</v>
+        <v>167</v>
       </c>
     </row>
     <row r="231" spans="1:10">
       <c r="A231">
-        <v>356</v>
+        <v>300</v>
       </c>
       <c r="B231" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C231" t="s">
         <v>30</v>
@@ -9248,24 +9260,24 @@
         <v>280</v>
       </c>
       <c r="G231" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H231" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="I231" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J231">
-        <v>772</v>
+        <v>149</v>
       </c>
     </row>
     <row r="232" spans="1:10">
       <c r="A232">
-        <v>534</v>
+        <v>304</v>
       </c>
       <c r="B232" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C232" t="s">
         <v>30</v>
@@ -9280,88 +9292,88 @@
         <v>281</v>
       </c>
       <c r="G232" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H232" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="I232" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J232">
-        <v>98</v>
+        <v>200</v>
       </c>
     </row>
     <row r="233" spans="1:10">
       <c r="A233">
-        <v>132</v>
+        <v>356</v>
       </c>
       <c r="B233" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C233" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D233" t="s">
         <v>32</v>
       </c>
       <c r="E233" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F233" t="s">
         <v>282</v>
       </c>
       <c r="G233" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H233" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="I233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="J233">
-        <v>90</v>
+        <v>772</v>
       </c>
     </row>
     <row r="234" spans="1:10">
       <c r="A234">
-        <v>192</v>
+        <v>534</v>
       </c>
       <c r="B234" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C234" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D234" t="s">
         <v>32</v>
       </c>
       <c r="E234" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F234" t="s">
         <v>283</v>
       </c>
       <c r="G234" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H234" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="J234">
-        <v>83</v>
+        <v>98</v>
       </c>
     </row>
     <row r="235" spans="1:10">
       <c r="A235">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="B235" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C235" t="s">
         <v>31</v>
@@ -9376,21 +9388,21 @@
         <v>284</v>
       </c>
       <c r="G235" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H235" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="I235" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J235">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="236" spans="1:10">
       <c r="A236">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B236" t="s">
         <v>17</v>
@@ -9408,21 +9420,21 @@
         <v>285</v>
       </c>
       <c r="G236" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H236" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="I236" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J236">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="237" spans="1:10">
       <c r="A237">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B237" t="s">
         <v>17</v>
@@ -9440,24 +9452,24 @@
         <v>286</v>
       </c>
       <c r="G237" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H237" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="I237" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J237">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="238" spans="1:10">
       <c r="A238">
-        <v>462</v>
+        <v>195</v>
       </c>
       <c r="B238" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C238" t="s">
         <v>31</v>
@@ -9472,24 +9484,24 @@
         <v>287</v>
       </c>
       <c r="G238" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H238" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="I238" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J238">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="239" spans="1:10">
       <c r="A239">
-        <v>463</v>
+        <v>196</v>
       </c>
       <c r="B239" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C239" t="s">
         <v>31</v>
@@ -9504,21 +9516,21 @@
         <v>288</v>
       </c>
       <c r="G239" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H239" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="I239" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J239">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="240" spans="1:10">
       <c r="A240">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B240" t="s">
         <v>16</v>
@@ -9536,21 +9548,21 @@
         <v>289</v>
       </c>
       <c r="G240" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H240" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="I240" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J240">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="241" spans="1:10">
       <c r="A241">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B241" t="s">
         <v>16</v>
@@ -9568,24 +9580,24 @@
         <v>290</v>
       </c>
       <c r="G241" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H241" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="I241" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J241">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="242" spans="1:10">
       <c r="A242">
-        <v>105</v>
+        <v>464</v>
       </c>
       <c r="B242" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C242" t="s">
         <v>31</v>
@@ -9594,30 +9606,30 @@
         <v>32</v>
       </c>
       <c r="E242" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F242" t="s">
         <v>291</v>
       </c>
       <c r="G242" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H242" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="I242" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J242">
-        <v>67</v>
+        <v>99</v>
       </c>
     </row>
     <row r="243" spans="1:10">
       <c r="A243">
-        <v>145</v>
+        <v>465</v>
       </c>
       <c r="B243" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C243" t="s">
         <v>31</v>
@@ -9626,30 +9638,30 @@
         <v>32</v>
       </c>
       <c r="E243" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F243" t="s">
         <v>292</v>
       </c>
       <c r="G243" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H243" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I243" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J243">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="244" spans="1:10">
       <c r="A244">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="B244" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C244" t="s">
         <v>31</v>
@@ -9664,24 +9676,24 @@
         <v>293</v>
       </c>
       <c r="G244" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H244" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="I244" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J244">
-        <v>97</v>
+        <v>67</v>
       </c>
     </row>
     <row r="245" spans="1:10">
       <c r="A245">
-        <v>425</v>
+        <v>145</v>
       </c>
       <c r="B245" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C245" t="s">
         <v>31</v>
@@ -9696,24 +9708,24 @@
         <v>294</v>
       </c>
       <c r="G245" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H245" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I245" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J245">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="246" spans="1:10">
       <c r="A246">
-        <v>426</v>
+        <v>146</v>
       </c>
       <c r="B246" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C246" t="s">
         <v>31</v>
@@ -9728,13 +9740,13 @@
         <v>295</v>
       </c>
       <c r="G246" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H246" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="I246" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J246">
         <v>97</v>
@@ -9742,7 +9754,7 @@
     </row>
     <row r="247" spans="1:10">
       <c r="A247">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B247" t="s">
         <v>14</v>
@@ -9760,21 +9772,21 @@
         <v>296</v>
       </c>
       <c r="G247" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H247" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="I247" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J247">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="248" spans="1:10">
       <c r="A248">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B248" t="s">
         <v>14</v>
@@ -9792,21 +9804,21 @@
         <v>297</v>
       </c>
       <c r="G248" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H248" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="I248" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J248">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="249" spans="1:10">
       <c r="A249">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B249" t="s">
         <v>14</v>
@@ -9824,21 +9836,21 @@
         <v>298</v>
       </c>
       <c r="G249" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H249" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="I249" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J249">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="250" spans="1:10">
       <c r="A250">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B250" t="s">
         <v>14</v>
@@ -9856,24 +9868,24 @@
         <v>299</v>
       </c>
       <c r="G250" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H250" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="I250" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J250">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="251" spans="1:10">
       <c r="A251">
-        <v>506</v>
+        <v>431</v>
       </c>
       <c r="B251" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C251" t="s">
         <v>31</v>
@@ -9888,24 +9900,24 @@
         <v>300</v>
       </c>
       <c r="G251" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H251" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="I251" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J251">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="252" spans="1:10">
       <c r="A252">
-        <v>508</v>
+        <v>432</v>
       </c>
       <c r="B252" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C252" t="s">
         <v>31</v>
@@ -9920,24 +9932,24 @@
         <v>301</v>
       </c>
       <c r="G252" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H252" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="I252" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J252">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
     <row r="253" spans="1:10">
       <c r="A253">
-        <v>72</v>
+        <v>506</v>
       </c>
       <c r="B253" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C253" t="s">
         <v>31</v>
@@ -9946,30 +9958,30 @@
         <v>32</v>
       </c>
       <c r="E253" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F253" t="s">
         <v>302</v>
       </c>
       <c r="G253" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H253" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="I253" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J253">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="254" spans="1:10">
       <c r="A254">
-        <v>208</v>
+        <v>508</v>
       </c>
       <c r="B254" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C254" t="s">
         <v>31</v>
@@ -9978,30 +9990,30 @@
         <v>32</v>
       </c>
       <c r="E254" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F254" t="s">
         <v>303</v>
       </c>
       <c r="G254" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H254" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="I254" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J254">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="255" spans="1:10">
       <c r="A255">
-        <v>209</v>
+        <v>72</v>
       </c>
       <c r="B255" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C255" t="s">
         <v>31</v>
@@ -10016,21 +10028,21 @@
         <v>304</v>
       </c>
       <c r="G255" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H255" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="I255" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="J255">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="256" spans="1:10">
       <c r="A256">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B256" t="s">
         <v>17</v>
@@ -10048,21 +10060,21 @@
         <v>305</v>
       </c>
       <c r="G256" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H256" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="I256" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J256">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="257" spans="1:10">
       <c r="A257">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B257" t="s">
         <v>17</v>
@@ -10080,21 +10092,21 @@
         <v>306</v>
       </c>
       <c r="G257" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H257" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="I257" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J257">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="258" spans="1:10">
       <c r="A258">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B258" t="s">
         <v>17</v>
@@ -10112,24 +10124,24 @@
         <v>307</v>
       </c>
       <c r="G258" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H258" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="I258" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J258">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="259" spans="1:10">
       <c r="A259">
-        <v>509</v>
+        <v>211</v>
       </c>
       <c r="B259" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C259" t="s">
         <v>31</v>
@@ -10144,24 +10156,24 @@
         <v>308</v>
       </c>
       <c r="G259" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H259" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="I259" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J259">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="260" spans="1:10">
       <c r="A260">
-        <v>511</v>
+        <v>212</v>
       </c>
       <c r="B260" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C260" t="s">
         <v>31</v>
@@ -10176,21 +10188,21 @@
         <v>309</v>
       </c>
       <c r="G260" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H260" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="I260" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J260">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="261" spans="1:10">
       <c r="A261">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B261" t="s">
         <v>16</v>
@@ -10208,21 +10220,21 @@
         <v>310</v>
       </c>
       <c r="G261" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H261" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="I261" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J261">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="262" spans="1:10">
       <c r="A262">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B262" t="s">
         <v>16</v>
@@ -10240,24 +10252,24 @@
         <v>311</v>
       </c>
       <c r="G262" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H262" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="I262" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J262">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="263" spans="1:10">
       <c r="A263">
-        <v>73</v>
+        <v>512</v>
       </c>
       <c r="B263" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C263" t="s">
         <v>31</v>
@@ -10266,30 +10278,30 @@
         <v>32</v>
       </c>
       <c r="E263" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F263" t="s">
         <v>312</v>
       </c>
       <c r="G263" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H263" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="I263" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J263">
-        <v>123</v>
+        <v>93</v>
       </c>
     </row>
     <row r="264" spans="1:10">
       <c r="A264">
-        <v>273</v>
+        <v>514</v>
       </c>
       <c r="B264" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C264" t="s">
         <v>31</v>
@@ -10298,30 +10310,30 @@
         <v>32</v>
       </c>
       <c r="E264" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F264" t="s">
         <v>313</v>
       </c>
       <c r="G264" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H264" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="I264" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J264">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="265" spans="1:10">
       <c r="A265">
-        <v>274</v>
+        <v>73</v>
       </c>
       <c r="B265" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C265" t="s">
         <v>31</v>
@@ -10336,21 +10348,21 @@
         <v>314</v>
       </c>
       <c r="G265" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H265" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="I265" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J265">
-        <v>116</v>
+        <v>123</v>
       </c>
     </row>
     <row r="266" spans="1:10">
       <c r="A266">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B266" t="s">
         <v>15</v>
@@ -10368,21 +10380,21 @@
         <v>315</v>
       </c>
       <c r="G266" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H266" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="I266" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J266">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="267" spans="1:10">
       <c r="A267">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B267" t="s">
         <v>15</v>
@@ -10400,21 +10412,21 @@
         <v>316</v>
       </c>
       <c r="G267" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H267" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="I267" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J267">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="268" spans="1:10">
       <c r="A268">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B268" t="s">
         <v>15</v>
@@ -10432,21 +10444,21 @@
         <v>317</v>
       </c>
       <c r="G268" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H268" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="I268" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J268">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="269" spans="1:10">
       <c r="A269">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B269" t="s">
         <v>15</v>
@@ -10464,21 +10476,21 @@
         <v>318</v>
       </c>
       <c r="G269" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H269" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="I269" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J269">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="270" spans="1:10">
       <c r="A270">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B270" t="s">
         <v>15</v>
@@ -10496,24 +10508,24 @@
         <v>319</v>
       </c>
       <c r="G270" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H270" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="I270" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J270">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="271" spans="1:10">
       <c r="A271">
-        <v>74</v>
+        <v>280</v>
       </c>
       <c r="B271" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C271" t="s">
         <v>31</v>
@@ -10522,30 +10534,30 @@
         <v>32</v>
       </c>
       <c r="E271" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F271" t="s">
         <v>320</v>
       </c>
       <c r="G271" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H271" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="I271" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J271">
-        <v>54</v>
+        <v>101</v>
       </c>
     </row>
     <row r="272" spans="1:10">
       <c r="A272">
-        <v>107</v>
+        <v>281</v>
       </c>
       <c r="B272" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C272" t="s">
         <v>31</v>
@@ -10554,30 +10566,30 @@
         <v>32</v>
       </c>
       <c r="E272" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F272" t="s">
         <v>321</v>
       </c>
       <c r="G272" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H272" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="I272" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="J272">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="273" spans="1:10">
       <c r="A273">
-        <v>138</v>
+        <v>74</v>
       </c>
       <c r="B273" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C273" t="s">
         <v>31</v>
@@ -10592,24 +10604,24 @@
         <v>322</v>
       </c>
       <c r="G273" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H273" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="I273" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J273">
-        <v>104</v>
+        <v>54</v>
       </c>
     </row>
     <row r="274" spans="1:10">
       <c r="A274">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="B274" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C274" t="s">
         <v>31</v>
@@ -10624,24 +10636,24 @@
         <v>323</v>
       </c>
       <c r="G274" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H274" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="I274" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="J274">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="275" spans="1:10">
       <c r="A275">
-        <v>421</v>
+        <v>138</v>
       </c>
       <c r="B275" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C275" t="s">
         <v>31</v>
@@ -10656,24 +10668,24 @@
         <v>324</v>
       </c>
       <c r="G275" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H275" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="I275" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J275">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="276" spans="1:10">
       <c r="A276">
-        <v>422</v>
+        <v>139</v>
       </c>
       <c r="B276" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C276" t="s">
         <v>31</v>
@@ -10688,21 +10700,21 @@
         <v>325</v>
       </c>
       <c r="G276" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H276" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="I276" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J276">
-        <v>103</v>
+        <v>65</v>
       </c>
     </row>
     <row r="277" spans="1:10">
       <c r="A277">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B277" t="s">
         <v>14</v>
@@ -10720,21 +10732,21 @@
         <v>326</v>
       </c>
       <c r="G277" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H277" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="I277" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J277">
-        <v>98</v>
+        <v>107</v>
       </c>
     </row>
     <row r="278" spans="1:10">
       <c r="A278">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B278" t="s">
         <v>14</v>
@@ -10752,13 +10764,13 @@
         <v>327</v>
       </c>
       <c r="G278" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H278" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="I278" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J278">
         <v>103</v>
@@ -10766,10 +10778,10 @@
     </row>
     <row r="279" spans="1:10">
       <c r="A279">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="B279" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C279" t="s">
         <v>31</v>
@@ -10784,24 +10796,24 @@
         <v>328</v>
       </c>
       <c r="G279" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H279" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="I279" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J279">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="280" spans="1:10">
       <c r="A280">
-        <v>461</v>
+        <v>424</v>
       </c>
       <c r="B280" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C280" t="s">
         <v>31</v>
@@ -10813,24 +10825,24 @@
         <v>81</v>
       </c>
       <c r="F280" t="s">
-        <v>304</v>
+        <v>329</v>
       </c>
       <c r="G280" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H280" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="I280" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J280">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="281" spans="1:10">
       <c r="A281">
-        <v>515</v>
+        <v>460</v>
       </c>
       <c r="B281" t="s">
         <v>16</v>
@@ -10845,24 +10857,24 @@
         <v>81</v>
       </c>
       <c r="F281" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G281" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H281" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="I281" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J281">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="282" spans="1:10">
       <c r="A282">
-        <v>516</v>
+        <v>461</v>
       </c>
       <c r="B282" t="s">
         <v>16</v>
@@ -10877,24 +10889,24 @@
         <v>81</v>
       </c>
       <c r="F282" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="G282" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H282" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="I282" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J282">
-        <v>91</v>
+        <v>104</v>
       </c>
     </row>
     <row r="283" spans="1:10">
       <c r="A283">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B283" t="s">
         <v>16</v>
@@ -10912,21 +10924,21 @@
         <v>331</v>
       </c>
       <c r="G283" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H283" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="I283" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J283">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="284" spans="1:10">
       <c r="A284">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B284" t="s">
         <v>16</v>
@@ -10944,15 +10956,79 @@
         <v>332</v>
       </c>
       <c r="G284" t="s">
+        <v>335</v>
+      </c>
+      <c r="H284" t="s">
+        <v>486</v>
+      </c>
+      <c r="I284" t="s">
+        <v>500</v>
+      </c>
+      <c r="J284">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10">
+      <c r="A285">
+        <v>517</v>
+      </c>
+      <c r="B285" t="s">
+        <v>16</v>
+      </c>
+      <c r="C285" t="s">
+        <v>31</v>
+      </c>
+      <c r="D285" t="s">
+        <v>32</v>
+      </c>
+      <c r="E285" t="s">
+        <v>81</v>
+      </c>
+      <c r="F285" t="s">
         <v>333</v>
       </c>
-      <c r="H284" t="s">
-        <v>482</v>
-      </c>
-      <c r="I284" t="s">
-        <v>496</v>
-      </c>
-      <c r="J284">
+      <c r="G285" t="s">
+        <v>335</v>
+      </c>
+      <c r="H285" t="s">
+        <v>486</v>
+      </c>
+      <c r="I285" t="s">
+        <v>500</v>
+      </c>
+      <c r="J285">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10">
+      <c r="A286">
+        <v>522</v>
+      </c>
+      <c r="B286" t="s">
+        <v>16</v>
+      </c>
+      <c r="C286" t="s">
+        <v>31</v>
+      </c>
+      <c r="D286" t="s">
+        <v>32</v>
+      </c>
+      <c r="E286" t="s">
+        <v>81</v>
+      </c>
+      <c r="F286" t="s">
+        <v>334</v>
+      </c>
+      <c r="G286" t="s">
+        <v>335</v>
+      </c>
+      <c r="H286" t="s">
+        <v>486</v>
+      </c>
+      <c r="I286" t="s">
+        <v>500</v>
+      </c>
+      <c r="J286">
         <v>93</v>
       </c>
     </row>
